--- a/documentación/Seguimiento Cartera auxiliar.xlsx
+++ b/documentación/Seguimiento Cartera auxiliar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/narcismagrinabalcells/Dropbox/1 - OFICINA/1-PROMOCIMA/02-CAPITAL PRIVADO/30 - Desarrollo/Préstamos/Claude Pro/promocima/documentación/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB80AD0-1A5C-3B43-93C9-F845C2B68714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95012D46-B828-0E4A-A5DE-FF48E960A3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26220" yWindow="4500" windowWidth="25960" windowHeight="22120" activeTab="2" xr2:uid="{7DA0983C-EA6B-584E-90AC-C5A5D261DBFA}"/>
+    <workbookView xWindow="25240" yWindow="4500" windowWidth="25960" windowHeight="22120" activeTab="2" xr2:uid="{7DA0983C-EA6B-584E-90AC-C5A5D261DBFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Préstamos participados" sheetId="1" r:id="rId1"/>
@@ -1308,16 +1308,11 @@
     <xf numFmtId="164" fontId="0" fillId="36" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="44" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="171" fontId="18" fillId="33" borderId="0" xfId="54" applyNumberFormat="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="171" fontId="25" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1389,6 +1384,11 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="44" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="171" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1917,20 +1917,15 @@
       <sheetName val="Claves CIRBE"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
       <sheetData sheetId="8">
-        <row r="8">
-          <cell r="C8" t="str">
-            <v>Americano</v>
-          </cell>
-        </row>
         <row r="9">
           <cell r="C9" t="str">
             <v>Mensual</v>
@@ -1942,16 +1937,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
-        <row r="9">
-          <cell r="E9">
-            <v>5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3792,18 +3781,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9">
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
     </row>
     <row r="2" spans="2:9" ht="15" customHeight="1">
       <c r="B2" s="8" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="8"/>
-      <c r="D2" s="73"/>
+      <c r="D2" s="72"/>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -3811,104 +3800,104 @@
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="2:9" ht="15" customHeight="1">
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1">
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="76"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="74"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="77" t="s">
+      <c r="F4" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="77"/>
+      <c r="G4" s="75"/>
     </row>
     <row r="5" spans="2:9" ht="15" customHeight="1">
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="78" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="107">
+      <c r="E5" s="105">
         <v>46023</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="H5" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="80">
+      <c r="I5" s="78">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="15" customHeight="1">
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="81"/>
-      <c r="H6" s="79" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="79"/>
+      <c r="H6" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="82" t="e">
+      <c r="I6" s="80" t="e">
         <f>IRR(I17:I137)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="15" customHeight="1">
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="78" t="s">
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="108">
+      <c r="E7" s="106">
         <v>0.02</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="I7" s="83" t="e">
+      <c r="I7" s="81" t="e">
         <f>(1+I6)^12-1</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" customHeight="1">
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="78" t="s">
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="109">
+      <c r="E8" s="107">
         <v>80000</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="77"/>
+      <c r="G8" s="75"/>
     </row>
     <row r="9" spans="2:9" ht="15" customHeight="1">
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="78" t="s">
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="110">
-        <v>1.5</v>
+      <c r="E9" s="108">
+        <v>3</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="2:9" ht="15" customHeight="1">
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="84" t="s">
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="110">
+      <c r="E10" s="108">
         <f>IF([2]Condiciones!C9="Trimestral",4,IF([2]Condiciones!C9="Anual",1,12))</f>
         <v>12</v>
       </c>
@@ -3916,81 +3905,81 @@
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="2:9" ht="15" customHeight="1">
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="84" t="s">
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="110">
-        <v>6</v>
+      <c r="E11" s="108">
+        <v>0</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1">
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
     </row>
     <row r="13" spans="2:9" ht="15" customHeight="1">
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="78" t="s">
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="108">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
+      <c r="E13" s="106">
+        <v>0.08</v>
+      </c>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
     </row>
     <row r="14" spans="2:9" ht="15" customHeight="1">
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="78" t="s">
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="88">
+      <c r="E14" s="86">
         <f>E13+0.03</f>
-        <v>0.1</v>
-      </c>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
+        <v>0.11</v>
+      </c>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
     </row>
     <row r="15" spans="2:9" ht="15" customHeight="1">
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="87"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="91" t="s">
+      <c r="B16" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="92" t="s">
+      <c r="D16" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" s="92" t="s">
+      <c r="F16" s="90" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="90" t="s">
         <v>96</v>
       </c>
-      <c r="H16" s="92" t="s">
+      <c r="H16" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="92" t="s">
+      <c r="I16" s="90" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4002,14 +3991,14 @@
         <f>E5</f>
         <v>46023</v>
       </c>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="93">
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="91">
         <f>$E$8</f>
         <v>80000</v>
       </c>
-      <c r="H17" s="95">
+      <c r="H17" s="93">
         <f>IF(B17=0,G17*E7,0)</f>
         <v>1600</v>
       </c>
@@ -4017,7 +4006,7 @@
         <f>E8-[2]Condiciones!C13</f>
         <v>52050</v>
       </c>
-      <c r="J17" s="96" t="s">
+      <c r="J17" s="94" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4032,27 +4021,27 @@
       </c>
       <c r="D18" s="56">
         <f t="shared" ref="D18:D81" si="0">IF(B18&lt;=$E$11,-CUMIPMT($E$13/$E$10,$E$9*$E$10-$E$11,$E$8,1,1,0),IF($E$9*$E$10&gt;=B18,-CUMIPMT($E$13/$E$10,$E$9*$E$10-$E$11,$E$8,B18-$E$11,B18-$E$11,0),""))</f>
-        <v>466.66666666666515</v>
+        <v>533.33333333333326</v>
       </c>
       <c r="E18" s="56">
         <f t="shared" ref="E18:E81" si="1">IF(B18&lt;=$E$11,0,IF($E$9*$E$10&gt;=B18,-CUMPRINC($E$13/$E$10,$E$9*$E$10-$E$11,$E$8,B18-$E$11,B18-$E$11,0),""))</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="97">
+        <v>1973.5759035811345</v>
+      </c>
+      <c r="F18" s="95">
         <f t="shared" ref="F18:F81" si="2">IF(OR(D18="",E18=""),"",D18+E18)</f>
-        <v>466.66666666666515</v>
-      </c>
-      <c r="G18" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G18" s="91">
         <f t="shared" ref="G18:G81" si="3">IF($E$9*$E$10&gt;=B18,G17-E18,"")</f>
-        <v>80000</v>
-      </c>
-      <c r="H18" s="95">
+        <v>78026.424096418865</v>
+      </c>
+      <c r="H18" s="93">
         <f t="shared" ref="H18:H81" si="4">IF(B18=0,G18*E8,0)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="96">
+      <c r="I18" s="94">
         <f>H18-F18</f>
-        <v>-466.66666666666515</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="19" spans="2:10">
@@ -4066,27 +4055,27 @@
       </c>
       <c r="D19" s="56">
         <f t="shared" si="0"/>
-        <v>466.66666666666515</v>
+        <v>520.17616064279241</v>
       </c>
       <c r="E19" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="97">
+        <v>1986.7330762716754</v>
+      </c>
+      <c r="F19" s="95">
         <f t="shared" si="2"/>
-        <v>466.66666666666515</v>
-      </c>
-      <c r="G19" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G19" s="91">
         <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="H19" s="95">
+        <v>76039.691020147191</v>
+      </c>
+      <c r="H19" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I19" s="96">
+      <c r="I19" s="94">
         <f t="shared" ref="I19:I77" si="7">H19-F19</f>
-        <v>-466.66666666666515</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="20" spans="2:10">
@@ -4100,27 +4089,27 @@
       </c>
       <c r="D20" s="56">
         <f t="shared" si="0"/>
-        <v>466.66666666666515</v>
+        <v>506.931273467648</v>
       </c>
       <c r="E20" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="97">
+        <v>1999.9779634468198</v>
+      </c>
+      <c r="F20" s="95">
         <f t="shared" si="2"/>
-        <v>466.66666666666515</v>
-      </c>
-      <c r="G20" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G20" s="91">
         <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="H20" s="95">
+        <v>74039.713056700377</v>
+      </c>
+      <c r="H20" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I20" s="96">
+      <c r="I20" s="94">
         <f t="shared" si="7"/>
-        <v>-466.66666666666515</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="21" spans="2:10">
@@ -4134,27 +4123,27 @@
       </c>
       <c r="D21" s="56">
         <f t="shared" si="0"/>
-        <v>466.66666666666515</v>
+        <v>493.59808704466923</v>
       </c>
       <c r="E21" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="97">
+        <v>2013.3111498697986</v>
+      </c>
+      <c r="F21" s="95">
         <f t="shared" si="2"/>
-        <v>466.66666666666515</v>
-      </c>
-      <c r="G21" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G21" s="91">
         <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="H21" s="95">
+        <v>72026.401906830579</v>
+      </c>
+      <c r="H21" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I21" s="96">
+      <c r="I21" s="94">
         <f t="shared" si="7"/>
-        <v>-466.66666666666515</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="22" spans="2:10">
@@ -4168,27 +4157,27 @@
       </c>
       <c r="D22" s="56">
         <f t="shared" si="0"/>
-        <v>466.66666666666515</v>
+        <v>480.17601271220406</v>
       </c>
       <c r="E22" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="97">
+        <v>2026.7332242022637</v>
+      </c>
+      <c r="F22" s="95">
         <f t="shared" si="2"/>
-        <v>466.66666666666515</v>
-      </c>
-      <c r="G22" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G22" s="91">
         <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="H22" s="95">
+        <v>69999.668682628311</v>
+      </c>
+      <c r="H22" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I22" s="96">
+      <c r="I22" s="94">
         <f t="shared" si="7"/>
-        <v>-466.66666666666515</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="23" spans="2:10">
@@ -4202,27 +4191,27 @@
       </c>
       <c r="D23" s="56">
         <f t="shared" si="0"/>
-        <v>466.66666666666515</v>
+        <v>466.66445788418901</v>
       </c>
       <c r="E23" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="97">
+        <v>2040.2447790302788</v>
+      </c>
+      <c r="F23" s="95">
         <f t="shared" si="2"/>
-        <v>466.66666666666515</v>
-      </c>
-      <c r="G23" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G23" s="91">
         <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="H23" s="95">
+        <v>67959.423903598028</v>
+      </c>
+      <c r="H23" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I23" s="96">
+      <c r="I23" s="94">
         <f t="shared" si="7"/>
-        <v>-466.66666666666515</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="24" spans="2:10">
@@ -4236,27 +4225,27 @@
       </c>
       <c r="D24" s="56">
         <f t="shared" si="0"/>
-        <v>466.66666666666515</v>
+        <v>453.06282602398687</v>
       </c>
       <c r="E24" s="56">
         <f t="shared" si="1"/>
-        <v>6455.4730211843789</v>
-      </c>
-      <c r="F24" s="97">
+        <v>2053.8464108904809</v>
+      </c>
+      <c r="F24" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G24" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G24" s="91">
         <f t="shared" si="3"/>
-        <v>73544.526978815615</v>
-      </c>
-      <c r="H24" s="95">
+        <v>65905.577492707554</v>
+      </c>
+      <c r="H24" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I24" s="96">
+      <c r="I24" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="25" spans="2:10">
@@ -4270,27 +4259,27 @@
       </c>
       <c r="D25" s="56">
         <f t="shared" si="0"/>
-        <v>429.00974070975735</v>
+        <v>439.37051661804981</v>
       </c>
       <c r="E25" s="56">
         <f t="shared" si="1"/>
-        <v>6493.1299471412867</v>
-      </c>
-      <c r="F25" s="97">
+        <v>2067.538720296418</v>
+      </c>
+      <c r="F25" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G25" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G25" s="91">
         <f t="shared" si="3"/>
-        <v>67051.397031674322</v>
-      </c>
-      <c r="H25" s="95">
+        <v>63838.038772411135</v>
+      </c>
+      <c r="H25" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I25" s="96">
+      <c r="I25" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="26" spans="2:10">
@@ -4304,27 +4293,27 @@
       </c>
       <c r="D26" s="56">
         <f t="shared" si="0"/>
-        <v>391.13314935143262</v>
+        <v>425.58692514940776</v>
       </c>
       <c r="E26" s="56">
         <f t="shared" si="1"/>
-        <v>6531.0065384996115</v>
-      </c>
-      <c r="F26" s="97">
+        <v>2081.32231176506</v>
+      </c>
+      <c r="F26" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G26" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G26" s="91">
         <f t="shared" si="3"/>
-        <v>60520.390493174709</v>
-      </c>
-      <c r="H26" s="95">
+        <v>61756.716460646072</v>
+      </c>
+      <c r="H26" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I26" s="96">
+      <c r="I26" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="27" spans="2:10">
@@ -4338,27 +4327,27 @@
       </c>
       <c r="D27" s="56">
         <f t="shared" si="0"/>
-        <v>353.03561121018447</v>
+        <v>411.71144307097438</v>
       </c>
       <c r="E27" s="56">
         <f t="shared" si="1"/>
-        <v>6569.1040766408596</v>
-      </c>
-      <c r="F27" s="97">
+        <v>2095.1977938434934</v>
+      </c>
+      <c r="F27" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G27" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G27" s="91">
         <f t="shared" si="3"/>
-        <v>53951.286416533847</v>
-      </c>
-      <c r="H27" s="95">
+        <v>59661.518666802578</v>
+      </c>
+      <c r="H27" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I27" s="96">
+      <c r="I27" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="28" spans="2:10">
@@ -4372,27 +4361,27 @@
       </c>
       <c r="D28" s="56">
         <f t="shared" si="0"/>
-        <v>314.71583742977964</v>
+        <v>397.74345777868393</v>
       </c>
       <c r="E28" s="56">
         <f t="shared" si="1"/>
-        <v>6607.4238504212644</v>
-      </c>
-      <c r="F28" s="97">
+        <v>2109.1657791357839</v>
+      </c>
+      <c r="F28" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G28" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G28" s="91">
         <f t="shared" si="3"/>
-        <v>47343.862566112584</v>
-      </c>
-      <c r="H28" s="95">
+        <v>57552.352887666792</v>
+      </c>
+      <c r="H28" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I28" s="96">
+      <c r="I28" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="29" spans="2:10">
@@ -4406,27 +4395,27 @@
       </c>
       <c r="D29" s="56">
         <f t="shared" si="0"/>
-        <v>276.1725316356551</v>
+        <v>383.68235258444565</v>
       </c>
       <c r="E29" s="56">
         <f t="shared" si="1"/>
-        <v>6645.967156215389</v>
-      </c>
-      <c r="F29" s="97">
+        <v>2123.2268843300221</v>
+      </c>
+      <c r="F29" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G29" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G29" s="91">
         <f t="shared" si="3"/>
-        <v>40697.895409897195</v>
-      </c>
-      <c r="H29" s="95">
+        <v>55429.126003336773</v>
+      </c>
+      <c r="H29" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I29" s="96">
+      <c r="I29" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="30" spans="2:10">
@@ -4440,27 +4429,27 @@
       </c>
       <c r="D30" s="56">
         <f t="shared" si="0"/>
-        <v>237.40438989106588</v>
+        <v>369.52750668891167</v>
       </c>
       <c r="E30" s="56">
         <f t="shared" si="1"/>
-        <v>6684.7352979599782</v>
-      </c>
-      <c r="F30" s="97">
+        <v>2137.3817302255561</v>
+      </c>
+      <c r="F30" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G30" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G30" s="91">
         <f t="shared" si="3"/>
-        <v>34013.160111937221</v>
-      </c>
-      <c r="H30" s="95">
+        <v>53291.744273111217</v>
+      </c>
+      <c r="H30" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="96">
+      <c r="I30" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="31" spans="2:10">
@@ -4474,27 +4463,27 @@
       </c>
       <c r="D31" s="56">
         <f t="shared" si="0"/>
-        <v>198.41010065296541</v>
+        <v>355.27829515407529</v>
       </c>
       <c r="E31" s="56">
         <f t="shared" si="1"/>
-        <v>6723.7295871980787</v>
-      </c>
-      <c r="F31" s="97">
+        <v>2151.6309417603925</v>
+      </c>
+      <c r="F31" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G31" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G31" s="91">
         <f t="shared" si="3"/>
-        <v>27289.430524739142</v>
-      </c>
-      <c r="H31" s="95">
+        <v>51140.113331350825</v>
+      </c>
+      <c r="H31" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I31" s="96">
+      <c r="I31" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="32" spans="2:10">
@@ -4508,27 +4497,27 @@
       </c>
       <c r="D32" s="56">
         <f t="shared" si="0"/>
-        <v>159.18834472764411</v>
+        <v>340.93408887567239</v>
       </c>
       <c r="E32" s="56">
         <f t="shared" si="1"/>
-        <v>6762.9513431234</v>
-      </c>
-      <c r="F32" s="97">
+        <v>2165.9751480387954</v>
+      </c>
+      <c r="F32" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G32" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G32" s="91">
         <f t="shared" si="3"/>
-        <v>20526.479181615741</v>
-      </c>
-      <c r="H32" s="95">
+        <v>48974.138183312032</v>
+      </c>
+      <c r="H32" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I32" s="96">
+      <c r="I32" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -4542,27 +4531,27 @@
       </c>
       <c r="D33" s="56">
         <f t="shared" si="0"/>
-        <v>119.73779522608947</v>
+        <v>326.49425455541359</v>
       </c>
       <c r="E33" s="56">
         <f t="shared" si="1"/>
-        <v>6802.4018926249546</v>
-      </c>
-      <c r="F33" s="97">
+        <v>2180.4149823590542</v>
+      </c>
+      <c r="F33" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G33" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G33" s="91">
         <f t="shared" si="3"/>
-        <v>13724.077288990786</v>
-      </c>
-      <c r="H33" s="95">
+        <v>46793.723200952976</v>
+      </c>
+      <c r="H33" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I33" s="96">
+      <c r="I33" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -4576,27 +4565,27 @@
       </c>
       <c r="D34" s="56">
         <f t="shared" si="0"/>
-        <v>80.057117519111671</v>
+        <v>311.95815467302009</v>
       </c>
       <c r="E34" s="56">
         <f t="shared" si="1"/>
-        <v>6842.0825703319324</v>
-      </c>
-      <c r="F34" s="97">
+        <v>2194.9510822414477</v>
+      </c>
+      <c r="F34" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G34" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G34" s="91">
         <f t="shared" si="3"/>
-        <v>6881.9947186588533</v>
-      </c>
-      <c r="H34" s="95">
+        <v>44598.772118711531</v>
+      </c>
+      <c r="H34" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I34" s="96">
+      <c r="I34" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="35" spans="2:9">
@@ -4610,639 +4599,639 @@
       </c>
       <c r="D35" s="56">
         <f t="shared" si="0"/>
-        <v>40.144969192174358</v>
+        <v>297.32514745807748</v>
       </c>
       <c r="E35" s="56">
         <f t="shared" si="1"/>
-        <v>6881.9947186588697</v>
-      </c>
-      <c r="F35" s="97">
+        <v>2209.5840894563903</v>
+      </c>
+      <c r="F35" s="95">
         <f t="shared" si="2"/>
-        <v>6922.1396878510441</v>
-      </c>
-      <c r="G35" s="93">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G35" s="91">
         <f t="shared" si="3"/>
-        <v>-1.6370904631912708E-11</v>
-      </c>
-      <c r="H35" s="95">
+        <v>42389.188029255143</v>
+      </c>
+      <c r="H35" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I35" s="96">
+      <c r="I35" s="94">
         <f t="shared" si="7"/>
-        <v>-6922.1396878510441</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="1" t="str">
+      <c r="B36" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C36" s="64" t="str">
+        <v>19</v>
+      </c>
+      <c r="C36" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D36" s="56" t="str">
+        <v>46600</v>
+      </c>
+      <c r="D36" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E36" s="56" t="str">
+        <v>282.59458686170137</v>
+      </c>
+      <c r="E36" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="97" t="str">
+        <v>2224.3146500527664</v>
+      </c>
+      <c r="F36" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G36" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G36" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H36" s="95">
+        <v>40164.873379202378</v>
+      </c>
+      <c r="H36" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I36" s="96" t="e">
+      <c r="I36" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="1" t="str">
+      <c r="B37" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C37" s="64" t="str">
+        <v>20</v>
+      </c>
+      <c r="C37" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D37" s="56" t="str">
+        <v>46631</v>
+      </c>
+      <c r="D37" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E37" s="56" t="str">
+        <v>267.76582252801609</v>
+      </c>
+      <c r="E37" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F37" s="97" t="str">
+        <v>2239.1434143864517</v>
+      </c>
+      <c r="F37" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G37" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G37" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H37" s="95">
+        <v>37925.729964815924</v>
+      </c>
+      <c r="H37" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I37" s="96" t="e">
+      <c r="I37" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="1" t="str">
+      <c r="B38" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C38" s="64" t="str">
+        <v>21</v>
+      </c>
+      <c r="C38" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D38" s="56" t="str">
+        <v>46661</v>
+      </c>
+      <c r="D38" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E38" s="56" t="str">
+        <v>252.83819976543964</v>
+      </c>
+      <c r="E38" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F38" s="97" t="str">
+        <v>2254.0710371490281</v>
+      </c>
+      <c r="F38" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G38" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G38" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H38" s="95">
+        <v>35671.658927666896</v>
+      </c>
+      <c r="H38" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I38" s="96" t="e">
+      <c r="I38" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="1" t="str">
+      <c r="B39" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C39" s="64" t="str">
+        <v>22</v>
+      </c>
+      <c r="C39" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D39" s="56" t="str">
+        <v>46692</v>
+      </c>
+      <c r="D39" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E39" s="56" t="str">
+        <v>237.81105951777954</v>
+      </c>
+      <c r="E39" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F39" s="97" t="str">
+        <v>2269.0981773966882</v>
+      </c>
+      <c r="F39" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G39" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G39" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H39" s="95">
+        <v>33402.560750270211</v>
+      </c>
+      <c r="H39" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I39" s="96" t="e">
+      <c r="I39" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="1" t="str">
+      <c r="B40" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C40" s="64" t="str">
+        <v>23</v>
+      </c>
+      <c r="C40" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D40" s="56" t="str">
+        <v>46722</v>
+      </c>
+      <c r="D40" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E40" s="56" t="str">
+        <v>222.68373833513442</v>
+      </c>
+      <c r="E40" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F40" s="97" t="str">
+        <v>2284.2254985793334</v>
+      </c>
+      <c r="F40" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G40" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G40" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H40" s="95">
+        <v>31118.335251690878</v>
+      </c>
+      <c r="H40" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="96" t="e">
+      <c r="I40" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="1" t="str">
+      <c r="B41" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C41" s="64" t="str">
+        <v>24</v>
+      </c>
+      <c r="C41" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D41" s="56" t="str">
+        <v>46753</v>
+      </c>
+      <c r="D41" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E41" s="56" t="str">
+        <v>207.45556834460558</v>
+      </c>
+      <c r="E41" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F41" s="97" t="str">
+        <v>2299.4536685698622</v>
+      </c>
+      <c r="F41" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G41" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G41" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H41" s="95">
+        <v>28818.881583121016</v>
+      </c>
+      <c r="H41" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I41" s="96" t="e">
+      <c r="I41" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="1" t="str">
+      <c r="B42" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C42" s="64" t="str">
+        <v>25</v>
+      </c>
+      <c r="C42" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D42" s="56" t="str">
+        <v>46784</v>
+      </c>
+      <c r="D42" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E42" s="56" t="str">
+        <v>192.12587722080661</v>
+      </c>
+      <c r="E42" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F42" s="97" t="str">
+        <v>2314.7833596936612</v>
+      </c>
+      <c r="F42" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G42" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G42" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H42" s="95">
+        <v>26504.098223427354</v>
+      </c>
+      <c r="H42" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I42" s="96" t="e">
+      <c r="I42" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="1" t="str">
+      <c r="B43" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C43" s="64" t="str">
+        <v>26</v>
+      </c>
+      <c r="C43" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D43" s="56" t="str">
+        <v>46813</v>
+      </c>
+      <c r="D43" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E43" s="56" t="str">
+        <v>176.69398815618251</v>
+      </c>
+      <c r="E43" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F43" s="97" t="str">
+        <v>2330.2152487582853</v>
+      </c>
+      <c r="F43" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G43" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G43" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H43" s="95">
+        <v>24173.882974669068</v>
+      </c>
+      <c r="H43" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I43" s="96" t="e">
+      <c r="I43" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="1" t="str">
+      <c r="B44" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C44" s="64" t="str">
+        <v>27</v>
+      </c>
+      <c r="C44" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D44" s="56" t="str">
+        <v>46844</v>
+      </c>
+      <c r="D44" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E44" s="56" t="str">
+        <v>161.15921983112685</v>
+      </c>
+      <c r="E44" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F44" s="97" t="str">
+        <v>2345.7500170833409</v>
+      </c>
+      <c r="F44" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G44" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G44" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H44" s="95">
+        <v>21828.132957585727</v>
+      </c>
+      <c r="H44" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I44" s="96" t="e">
+      <c r="I44" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="1" t="str">
+      <c r="B45" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C45" s="64" t="str">
+        <v>28</v>
+      </c>
+      <c r="C45" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D45" s="56" t="str">
+        <v>46874</v>
+      </c>
+      <c r="D45" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E45" s="56" t="str">
+        <v>145.52088638390478</v>
+      </c>
+      <c r="E45" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F45" s="97" t="str">
+        <v>2361.388350530563</v>
+      </c>
+      <c r="F45" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G45" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G45" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H45" s="95">
+        <v>19466.744607055163</v>
+      </c>
+      <c r="H45" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I45" s="96" t="e">
+      <c r="I45" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="1" t="str">
+      <c r="B46" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C46" s="64" t="str">
+        <v>29</v>
+      </c>
+      <c r="C46" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D46" s="56" t="str">
+        <v>46905</v>
+      </c>
+      <c r="D46" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E46" s="56" t="str">
+        <v>129.7782973803678</v>
+      </c>
+      <c r="E46" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F46" s="97" t="str">
+        <v>2377.1309395341</v>
+      </c>
+      <c r="F46" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G46" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G46" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H46" s="95">
+        <v>17089.613667521062</v>
+      </c>
+      <c r="H46" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I46" s="96" t="e">
+      <c r="I46" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="1" t="str">
+      <c r="B47" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C47" s="64" t="str">
+        <v>30</v>
+      </c>
+      <c r="C47" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D47" s="56" t="str">
+        <v>46935</v>
+      </c>
+      <c r="D47" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E47" s="56" t="str">
+        <v>113.93075778347338</v>
+      </c>
+      <c r="E47" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F47" s="97" t="str">
+        <v>2392.9784791309944</v>
+      </c>
+      <c r="F47" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G47" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G47" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H47" s="95">
+        <v>14696.635188390068</v>
+      </c>
+      <c r="H47" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I47" s="96" t="e">
+      <c r="I47" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="1" t="str">
+      <c r="B48" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C48" s="64" t="str">
+        <v>31</v>
+      </c>
+      <c r="C48" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D48" s="56" t="str">
+        <v>46966</v>
+      </c>
+      <c r="D48" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E48" s="56" t="str">
+        <v>97.977567922600429</v>
+      </c>
+      <c r="E48" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F48" s="97" t="str">
+        <v>2408.9316689918674</v>
+      </c>
+      <c r="F48" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G48" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G48" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H48" s="95">
+        <v>12287.703519398201</v>
+      </c>
+      <c r="H48" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I48" s="96" t="e">
+      <c r="I48" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="1" t="str">
+      <c r="B49" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C49" s="64" t="str">
+        <v>32</v>
+      </c>
+      <c r="C49" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D49" s="56" t="str">
+        <v>46997</v>
+      </c>
+      <c r="D49" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E49" s="56" t="str">
+        <v>81.918023462654673</v>
+      </c>
+      <c r="E49" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F49" s="97" t="str">
+        <v>2424.9912134518131</v>
+      </c>
+      <c r="F49" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G49" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G49" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H49" s="95">
+        <v>9862.7123059463884</v>
+      </c>
+      <c r="H49" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I49" s="96" t="e">
+      <c r="I49" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="1" t="str">
+      <c r="B50" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C50" s="64" t="str">
+        <v>33</v>
+      </c>
+      <c r="C50" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D50" s="56" t="str">
+        <v>47027</v>
+      </c>
+      <c r="D50" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E50" s="56" t="str">
+        <v>65.751415372975771</v>
+      </c>
+      <c r="E50" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F50" s="97" t="str">
+        <v>2441.157821541492</v>
+      </c>
+      <c r="F50" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G50" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G50" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H50" s="95">
+        <v>7421.5544844048964</v>
+      </c>
+      <c r="H50" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I50" s="96" t="e">
+      <c r="I50" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="1" t="str">
+      <c r="B51" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C51" s="64" t="str">
+        <v>34</v>
+      </c>
+      <c r="C51" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D51" s="56" t="str">
+        <v>47058</v>
+      </c>
+      <c r="D51" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E51" s="56" t="str">
+        <v>49.477029896032491</v>
+      </c>
+      <c r="E51" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F51" s="97" t="str">
+        <v>2457.4322070184353</v>
+      </c>
+      <c r="F51" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G51" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G51" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H51" s="95">
+        <v>4964.1222773864611</v>
+      </c>
+      <c r="H51" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I51" s="96" t="e">
+      <c r="I51" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="52" spans="2:9">
-      <c r="B52" s="1" t="str">
+      <c r="B52" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C52" s="64" t="str">
+        <v>35</v>
+      </c>
+      <c r="C52" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D52" s="56" t="str">
+        <v>47088</v>
+      </c>
+      <c r="D52" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E52" s="56" t="str">
+        <v>33.094148515910092</v>
+      </c>
+      <c r="E52" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F52" s="97" t="str">
+        <v>2473.8150883985577</v>
+      </c>
+      <c r="F52" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G52" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G52" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H52" s="95">
+        <v>2490.3071889879034</v>
+      </c>
+      <c r="H52" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I52" s="96" t="e">
+      <c r="I52" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="53" spans="2:9">
-      <c r="B53" s="1" t="str">
+      <c r="B53" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="C53" s="64" t="str">
+        <v>36</v>
+      </c>
+      <c r="C53" s="64">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="D53" s="56" t="str">
+        <v>47119</v>
+      </c>
+      <c r="D53" s="56">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E53" s="56" t="str">
+        <v>16.602047926586238</v>
+      </c>
+      <c r="E53" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F53" s="97" t="str">
+        <v>2490.3071889878815</v>
+      </c>
+      <c r="F53" s="95">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G53" s="93" t="str">
+        <v>2506.9092369144678</v>
+      </c>
+      <c r="G53" s="91">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H53" s="95">
+        <v>2.1827872842550278E-11</v>
+      </c>
+      <c r="H53" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I53" s="96" t="e">
+      <c r="I53" s="94">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>-2506.9092369144678</v>
       </c>
     </row>
     <row r="54" spans="2:9">
@@ -5262,19 +5251,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F54" s="97" t="str">
+      <c r="F54" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G54" s="93" t="str">
+      <c r="G54" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H54" s="95">
+      <c r="H54" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I54" s="96" t="e">
+      <c r="I54" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5296,19 +5285,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F55" s="97" t="str">
+      <c r="F55" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G55" s="93" t="str">
+      <c r="G55" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H55" s="95">
+      <c r="H55" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I55" s="96" t="e">
+      <c r="I55" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5330,19 +5319,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F56" s="97" t="str">
+      <c r="F56" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G56" s="93" t="str">
+      <c r="G56" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H56" s="95">
+      <c r="H56" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I56" s="96" t="e">
+      <c r="I56" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5364,19 +5353,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F57" s="97" t="str">
+      <c r="F57" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G57" s="93" t="str">
+      <c r="G57" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H57" s="95">
+      <c r="H57" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I57" s="96" t="e">
+      <c r="I57" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5398,19 +5387,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F58" s="97" t="str">
+      <c r="F58" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G58" s="93" t="str">
+      <c r="G58" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H58" s="95">
+      <c r="H58" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I58" s="96" t="e">
+      <c r="I58" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5432,19 +5421,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F59" s="97" t="str">
+      <c r="F59" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G59" s="93" t="str">
+      <c r="G59" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H59" s="95">
+      <c r="H59" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I59" s="96" t="e">
+      <c r="I59" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5466,19 +5455,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F60" s="97" t="str">
+      <c r="F60" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G60" s="93" t="str">
+      <c r="G60" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H60" s="95">
+      <c r="H60" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I60" s="96" t="e">
+      <c r="I60" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5500,19 +5489,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F61" s="97" t="str">
+      <c r="F61" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G61" s="93" t="str">
+      <c r="G61" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H61" s="95">
+      <c r="H61" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I61" s="96" t="e">
+      <c r="I61" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5534,19 +5523,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F62" s="97" t="str">
+      <c r="F62" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G62" s="93" t="str">
+      <c r="G62" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H62" s="95">
+      <c r="H62" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I62" s="96" t="e">
+      <c r="I62" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5568,19 +5557,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F63" s="97" t="str">
+      <c r="F63" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G63" s="93" t="str">
+      <c r="G63" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H63" s="95">
+      <c r="H63" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I63" s="96" t="e">
+      <c r="I63" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5602,19 +5591,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F64" s="97" t="str">
+      <c r="F64" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G64" s="93" t="str">
+      <c r="G64" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H64" s="95">
+      <c r="H64" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I64" s="96" t="e">
+      <c r="I64" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5636,19 +5625,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F65" s="97" t="str">
+      <c r="F65" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G65" s="93" t="str">
+      <c r="G65" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H65" s="95">
+      <c r="H65" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I65" s="96" t="e">
+      <c r="I65" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5670,19 +5659,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F66" s="97" t="str">
+      <c r="F66" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G66" s="93" t="str">
+      <c r="G66" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H66" s="95">
+      <c r="H66" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I66" s="96" t="e">
+      <c r="I66" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5704,19 +5693,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F67" s="97" t="str">
+      <c r="F67" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G67" s="93" t="str">
+      <c r="G67" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H67" s="95">
+      <c r="H67" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I67" s="96" t="e">
+      <c r="I67" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5738,19 +5727,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F68" s="97" t="str">
+      <c r="F68" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G68" s="93" t="str">
+      <c r="G68" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H68" s="95">
+      <c r="H68" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I68" s="96" t="e">
+      <c r="I68" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5772,19 +5761,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F69" s="97" t="str">
+      <c r="F69" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G69" s="93" t="str">
+      <c r="G69" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H69" s="95">
+      <c r="H69" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I69" s="96" t="e">
+      <c r="I69" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5806,19 +5795,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F70" s="97" t="str">
+      <c r="F70" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G70" s="93" t="str">
+      <c r="G70" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H70" s="95">
+      <c r="H70" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I70" s="96" t="e">
+      <c r="I70" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5840,19 +5829,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F71" s="97" t="str">
+      <c r="F71" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G71" s="93" t="str">
+      <c r="G71" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H71" s="95">
+      <c r="H71" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I71" s="96" t="e">
+      <c r="I71" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5874,19 +5863,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F72" s="97" t="str">
+      <c r="F72" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G72" s="93" t="str">
+      <c r="G72" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H72" s="95">
+      <c r="H72" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I72" s="96" t="e">
+      <c r="I72" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5908,19 +5897,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F73" s="97" t="str">
+      <c r="F73" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G73" s="93" t="str">
+      <c r="G73" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H73" s="95">
+      <c r="H73" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I73" s="96" t="e">
+      <c r="I73" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5942,19 +5931,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F74" s="97" t="str">
+      <c r="F74" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G74" s="93" t="str">
+      <c r="G74" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H74" s="95">
+      <c r="H74" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I74" s="96" t="e">
+      <c r="I74" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -5976,19 +5965,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F75" s="97" t="str">
+      <c r="F75" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G75" s="93" t="str">
+      <c r="G75" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H75" s="95">
+      <c r="H75" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I75" s="96" t="e">
+      <c r="I75" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -6010,19 +5999,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F76" s="97" t="str">
+      <c r="F76" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G76" s="93" t="str">
+      <c r="G76" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H76" s="95">
+      <c r="H76" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I76" s="96" t="e">
+      <c r="I76" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -6044,19 +6033,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F77" s="97" t="str">
+      <c r="F77" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G77" s="93" t="str">
+      <c r="G77" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H77" s="95">
+      <c r="H77" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I77" s="96" t="e">
+      <c r="I77" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
@@ -6078,19 +6067,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F78" s="97" t="str">
+      <c r="F78" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G78" s="93" t="str">
+      <c r="G78" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H78" s="95">
+      <c r="H78" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I78" s="96" t="str">
+      <c r="I78" s="94" t="str">
         <f>IF(F78="","",H78-F78)</f>
         <v/>
       </c>
@@ -6112,19 +6101,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F79" s="97" t="str">
+      <c r="F79" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G79" s="93" t="str">
+      <c r="G79" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H79" s="95">
+      <c r="H79" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I79" s="96" t="str">
+      <c r="I79" s="94" t="str">
         <f t="shared" ref="I79:I137" si="8">IF(F79="","",H79-F79)</f>
         <v/>
       </c>
@@ -6146,19 +6135,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F80" s="97" t="str">
+      <c r="F80" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G80" s="93" t="str">
+      <c r="G80" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H80" s="95">
+      <c r="H80" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I80" s="96" t="str">
+      <c r="I80" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6180,19 +6169,19 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F81" s="97" t="str">
+      <c r="F81" s="95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G81" s="93" t="str">
+      <c r="G81" s="91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H81" s="95">
+      <c r="H81" s="93">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I81" s="96" t="str">
+      <c r="I81" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6214,19 +6203,19 @@
         <f t="shared" ref="E82:E137" si="10">IF(B82&lt;=$E$11,0,IF($E$9*$E$10&gt;=B82,-CUMPRINC($E$13/$E$10,$E$9*$E$10-$E$11,$E$8,B82-$E$11,B82-$E$11,0),""))</f>
         <v/>
       </c>
-      <c r="F82" s="97" t="str">
+      <c r="F82" s="95" t="str">
         <f t="shared" ref="F82:F137" si="11">IF(OR(D82="",E82=""),"",D82+E82)</f>
         <v/>
       </c>
-      <c r="G82" s="93" t="str">
+      <c r="G82" s="91" t="str">
         <f t="shared" ref="G82:G137" si="12">IF($E$9*$E$10&gt;=B82,G81-E82,"")</f>
         <v/>
       </c>
-      <c r="H82" s="95">
+      <c r="H82" s="93">
         <f t="shared" ref="H82:H137" si="13">IF(B82=0,G82*E72,0)</f>
         <v>0</v>
       </c>
-      <c r="I82" s="96" t="str">
+      <c r="I82" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6248,19 +6237,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F83" s="97" t="str">
+      <c r="F83" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G83" s="93" t="str">
+      <c r="G83" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H83" s="95">
+      <c r="H83" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I83" s="96" t="str">
+      <c r="I83" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6282,19 +6271,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F84" s="97" t="str">
+      <c r="F84" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G84" s="93" t="str">
+      <c r="G84" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H84" s="95">
+      <c r="H84" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I84" s="96" t="str">
+      <c r="I84" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6316,19 +6305,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F85" s="97" t="str">
+      <c r="F85" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G85" s="93" t="str">
+      <c r="G85" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H85" s="95">
+      <c r="H85" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I85" s="96" t="str">
+      <c r="I85" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6350,19 +6339,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F86" s="97" t="str">
+      <c r="F86" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G86" s="93" t="str">
+      <c r="G86" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H86" s="95">
+      <c r="H86" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I86" s="96" t="str">
+      <c r="I86" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6384,19 +6373,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F87" s="97" t="str">
+      <c r="F87" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G87" s="93" t="str">
+      <c r="G87" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H87" s="95">
+      <c r="H87" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I87" s="96" t="str">
+      <c r="I87" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6418,19 +6407,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F88" s="97" t="str">
+      <c r="F88" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G88" s="93" t="str">
+      <c r="G88" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H88" s="95">
+      <c r="H88" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I88" s="96" t="str">
+      <c r="I88" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6452,19 +6441,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F89" s="97" t="str">
+      <c r="F89" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G89" s="93" t="str">
+      <c r="G89" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H89" s="95">
+      <c r="H89" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I89" s="96" t="str">
+      <c r="I89" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6486,19 +6475,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F90" s="97" t="str">
+      <c r="F90" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G90" s="93" t="str">
+      <c r="G90" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H90" s="95">
+      <c r="H90" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I90" s="96" t="str">
+      <c r="I90" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6520,19 +6509,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F91" s="97" t="str">
+      <c r="F91" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G91" s="93" t="str">
+      <c r="G91" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H91" s="95">
+      <c r="H91" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I91" s="96" t="str">
+      <c r="I91" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6554,19 +6543,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F92" s="97" t="str">
+      <c r="F92" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G92" s="93" t="str">
+      <c r="G92" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H92" s="95">
+      <c r="H92" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I92" s="96" t="str">
+      <c r="I92" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6588,19 +6577,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F93" s="97" t="str">
+      <c r="F93" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G93" s="93" t="str">
+      <c r="G93" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H93" s="95">
+      <c r="H93" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I93" s="96" t="str">
+      <c r="I93" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6622,19 +6611,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F94" s="97" t="str">
+      <c r="F94" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G94" s="93" t="str">
+      <c r="G94" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H94" s="95">
+      <c r="H94" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I94" s="96" t="str">
+      <c r="I94" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6656,19 +6645,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F95" s="97" t="str">
+      <c r="F95" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G95" s="93" t="str">
+      <c r="G95" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H95" s="95">
+      <c r="H95" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I95" s="96" t="str">
+      <c r="I95" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6690,19 +6679,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F96" s="97" t="str">
+      <c r="F96" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G96" s="93" t="str">
+      <c r="G96" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H96" s="95">
+      <c r="H96" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I96" s="96" t="str">
+      <c r="I96" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6724,19 +6713,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F97" s="97" t="str">
+      <c r="F97" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G97" s="93" t="str">
+      <c r="G97" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H97" s="95">
+      <c r="H97" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I97" s="96" t="str">
+      <c r="I97" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6758,19 +6747,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F98" s="97" t="str">
+      <c r="F98" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G98" s="93" t="str">
+      <c r="G98" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H98" s="95">
+      <c r="H98" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I98" s="96" t="str">
+      <c r="I98" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6792,19 +6781,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F99" s="97" t="str">
+      <c r="F99" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G99" s="93" t="str">
+      <c r="G99" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H99" s="95">
+      <c r="H99" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I99" s="96" t="str">
+      <c r="I99" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6826,19 +6815,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F100" s="97" t="str">
+      <c r="F100" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G100" s="93" t="str">
+      <c r="G100" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H100" s="95">
+      <c r="H100" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I100" s="96" t="str">
+      <c r="I100" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6860,19 +6849,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F101" s="97" t="str">
+      <c r="F101" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G101" s="93" t="str">
+      <c r="G101" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H101" s="95">
+      <c r="H101" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I101" s="96" t="str">
+      <c r="I101" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6894,19 +6883,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F102" s="97" t="str">
+      <c r="F102" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G102" s="93" t="str">
+      <c r="G102" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H102" s="95">
+      <c r="H102" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I102" s="96" t="str">
+      <c r="I102" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6928,19 +6917,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F103" s="97" t="str">
+      <c r="F103" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G103" s="93" t="str">
+      <c r="G103" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H103" s="95">
+      <c r="H103" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I103" s="96" t="str">
+      <c r="I103" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6962,19 +6951,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F104" s="97" t="str">
+      <c r="F104" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G104" s="93" t="str">
+      <c r="G104" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H104" s="95">
+      <c r="H104" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I104" s="96" t="str">
+      <c r="I104" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6996,19 +6985,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F105" s="97" t="str">
+      <c r="F105" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G105" s="93" t="str">
+      <c r="G105" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H105" s="95">
+      <c r="H105" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I105" s="96" t="str">
+      <c r="I105" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7030,19 +7019,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F106" s="97" t="str">
+      <c r="F106" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G106" s="93" t="str">
+      <c r="G106" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H106" s="95">
+      <c r="H106" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I106" s="96" t="str">
+      <c r="I106" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7064,19 +7053,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F107" s="97" t="str">
+      <c r="F107" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G107" s="93" t="str">
+      <c r="G107" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H107" s="95">
+      <c r="H107" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I107" s="96" t="str">
+      <c r="I107" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7098,19 +7087,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F108" s="97" t="str">
+      <c r="F108" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G108" s="93" t="str">
+      <c r="G108" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H108" s="95">
+      <c r="H108" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I108" s="96" t="str">
+      <c r="I108" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7132,19 +7121,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F109" s="97" t="str">
+      <c r="F109" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G109" s="93" t="str">
+      <c r="G109" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H109" s="95">
+      <c r="H109" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I109" s="96" t="str">
+      <c r="I109" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7166,19 +7155,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F110" s="97" t="str">
+      <c r="F110" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G110" s="93" t="str">
+      <c r="G110" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H110" s="95">
+      <c r="H110" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I110" s="96" t="str">
+      <c r="I110" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7200,19 +7189,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F111" s="97" t="str">
+      <c r="F111" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G111" s="93" t="str">
+      <c r="G111" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H111" s="95">
+      <c r="H111" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I111" s="96" t="str">
+      <c r="I111" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7234,19 +7223,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F112" s="97" t="str">
+      <c r="F112" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G112" s="93" t="str">
+      <c r="G112" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H112" s="95">
+      <c r="H112" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I112" s="96" t="str">
+      <c r="I112" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7268,19 +7257,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F113" s="97" t="str">
+      <c r="F113" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G113" s="93" t="str">
+      <c r="G113" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H113" s="95">
+      <c r="H113" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I113" s="96" t="str">
+      <c r="I113" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7302,19 +7291,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F114" s="97" t="str">
+      <c r="F114" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G114" s="93" t="str">
+      <c r="G114" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H114" s="95">
+      <c r="H114" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I114" s="96" t="str">
+      <c r="I114" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7336,19 +7325,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F115" s="97" t="str">
+      <c r="F115" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G115" s="93" t="str">
+      <c r="G115" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H115" s="95">
+      <c r="H115" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I115" s="96" t="str">
+      <c r="I115" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7370,19 +7359,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F116" s="97" t="str">
+      <c r="F116" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G116" s="93" t="str">
+      <c r="G116" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H116" s="95">
+      <c r="H116" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I116" s="96" t="str">
+      <c r="I116" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7404,19 +7393,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F117" s="97" t="str">
+      <c r="F117" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G117" s="93" t="str">
+      <c r="G117" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H117" s="95">
+      <c r="H117" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I117" s="96" t="str">
+      <c r="I117" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7438,19 +7427,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F118" s="97" t="str">
+      <c r="F118" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G118" s="93" t="str">
+      <c r="G118" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H118" s="95">
+      <c r="H118" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I118" s="96" t="str">
+      <c r="I118" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7472,19 +7461,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F119" s="97" t="str">
+      <c r="F119" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G119" s="93" t="str">
+      <c r="G119" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H119" s="95">
+      <c r="H119" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I119" s="96" t="str">
+      <c r="I119" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7506,19 +7495,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F120" s="97" t="str">
+      <c r="F120" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G120" s="93" t="str">
+      <c r="G120" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H120" s="95">
+      <c r="H120" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I120" s="96" t="str">
+      <c r="I120" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7540,19 +7529,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F121" s="97" t="str">
+      <c r="F121" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G121" s="93" t="str">
+      <c r="G121" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H121" s="95">
+      <c r="H121" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I121" s="96" t="str">
+      <c r="I121" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7574,19 +7563,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F122" s="97" t="str">
+      <c r="F122" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G122" s="93" t="str">
+      <c r="G122" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H122" s="95">
+      <c r="H122" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I122" s="96" t="str">
+      <c r="I122" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7608,19 +7597,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F123" s="97" t="str">
+      <c r="F123" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G123" s="93" t="str">
+      <c r="G123" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H123" s="95">
+      <c r="H123" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I123" s="96" t="str">
+      <c r="I123" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7642,19 +7631,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F124" s="97" t="str">
+      <c r="F124" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G124" s="93" t="str">
+      <c r="G124" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H124" s="95">
+      <c r="H124" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I124" s="96" t="str">
+      <c r="I124" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7676,19 +7665,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F125" s="97" t="str">
+      <c r="F125" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G125" s="93" t="str">
+      <c r="G125" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H125" s="95">
+      <c r="H125" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I125" s="96" t="str">
+      <c r="I125" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7710,19 +7699,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F126" s="97" t="str">
+      <c r="F126" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G126" s="93" t="str">
+      <c r="G126" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H126" s="95">
+      <c r="H126" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I126" s="96" t="str">
+      <c r="I126" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7744,19 +7733,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F127" s="97" t="str">
+      <c r="F127" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G127" s="93" t="str">
+      <c r="G127" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H127" s="95">
+      <c r="H127" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I127" s="96" t="str">
+      <c r="I127" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7778,19 +7767,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F128" s="97" t="str">
+      <c r="F128" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G128" s="93" t="str">
+      <c r="G128" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H128" s="95">
+      <c r="H128" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I128" s="96" t="str">
+      <c r="I128" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7812,19 +7801,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F129" s="97" t="str">
+      <c r="F129" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G129" s="93" t="str">
+      <c r="G129" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H129" s="95">
+      <c r="H129" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I129" s="96" t="str">
+      <c r="I129" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7846,19 +7835,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F130" s="97" t="str">
+      <c r="F130" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G130" s="93" t="str">
+      <c r="G130" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H130" s="95">
+      <c r="H130" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I130" s="96" t="str">
+      <c r="I130" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7880,19 +7869,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F131" s="97" t="str">
+      <c r="F131" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G131" s="93" t="str">
+      <c r="G131" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H131" s="95">
+      <c r="H131" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I131" s="96" t="str">
+      <c r="I131" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7914,19 +7903,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F132" s="97" t="str">
+      <c r="F132" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G132" s="93" t="str">
+      <c r="G132" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H132" s="95">
+      <c r="H132" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I132" s="96" t="str">
+      <c r="I132" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7948,19 +7937,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F133" s="97" t="str">
+      <c r="F133" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G133" s="93" t="str">
+      <c r="G133" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H133" s="95">
+      <c r="H133" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I133" s="96" t="str">
+      <c r="I133" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -7982,19 +7971,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F134" s="97" t="str">
+      <c r="F134" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G134" s="93" t="str">
+      <c r="G134" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H134" s="95">
+      <c r="H134" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I134" s="96" t="str">
+      <c r="I134" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -8016,19 +8005,19 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F135" s="97" t="str">
+      <c r="F135" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G135" s="93" t="str">
+      <c r="G135" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H135" s="95">
+      <c r="H135" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I135" s="96" t="str">
+      <c r="I135" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -8050,53 +8039,53 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F136" s="97" t="str">
+      <c r="F136" s="95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G136" s="93" t="str">
+      <c r="G136" s="91" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H136" s="95">
+      <c r="H136" s="93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I136" s="96" t="str">
+      <c r="I136" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="137" spans="2:9">
-      <c r="B137" s="98" t="str">
+      <c r="B137" s="96" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="C137" s="99" t="str">
+      <c r="C137" s="97" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="D137" s="100" t="str">
+      <c r="D137" s="98" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="E137" s="100" t="str">
+      <c r="E137" s="98" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="F137" s="101" t="str">
+      <c r="F137" s="99" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="G137" s="102" t="str">
+      <c r="G137" s="100" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="H137" s="103">
+      <c r="H137" s="101">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I137" s="96" t="str">
+      <c r="I137" s="94" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -8104,3178 +8093,3178 @@
     <row r="138" spans="2:9">
       <c r="B138" s="1"/>
       <c r="C138" s="64"/>
-      <c r="D138" s="93"/>
-      <c r="E138" s="93"/>
-      <c r="F138" s="93"/>
-      <c r="G138" s="93"/>
-      <c r="H138" s="95"/>
+      <c r="D138" s="91"/>
+      <c r="E138" s="91"/>
+      <c r="F138" s="91"/>
+      <c r="G138" s="91"/>
+      <c r="H138" s="93"/>
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="1"/>
       <c r="C139" s="64"/>
-      <c r="D139" s="93"/>
-      <c r="E139" s="93"/>
-      <c r="F139" s="93"/>
-      <c r="G139" s="93"/>
-      <c r="H139" s="95"/>
+      <c r="D139" s="91"/>
+      <c r="E139" s="91"/>
+      <c r="F139" s="91"/>
+      <c r="G139" s="91"/>
+      <c r="H139" s="93"/>
     </row>
     <row r="140" spans="2:9">
       <c r="B140" s="1"/>
       <c r="C140" s="64"/>
-      <c r="D140" s="93"/>
-      <c r="E140" s="93"/>
-      <c r="F140" s="93"/>
-      <c r="G140" s="93"/>
-      <c r="H140" s="95"/>
+      <c r="D140" s="91"/>
+      <c r="E140" s="91"/>
+      <c r="F140" s="91"/>
+      <c r="G140" s="91"/>
+      <c r="H140" s="93"/>
     </row>
     <row r="141" spans="2:9">
       <c r="B141" s="1"/>
       <c r="C141" s="64"/>
-      <c r="D141" s="93"/>
-      <c r="E141" s="93"/>
-      <c r="F141" s="93"/>
-      <c r="G141" s="93"/>
-      <c r="H141" s="95"/>
+      <c r="D141" s="91"/>
+      <c r="E141" s="91"/>
+      <c r="F141" s="91"/>
+      <c r="G141" s="91"/>
+      <c r="H141" s="93"/>
     </row>
     <row r="142" spans="2:9">
       <c r="B142" s="1"/>
       <c r="C142" s="64"/>
-      <c r="D142" s="93"/>
-      <c r="E142" s="93"/>
-      <c r="F142" s="93"/>
-      <c r="G142" s="93"/>
-      <c r="H142" s="95"/>
+      <c r="D142" s="91"/>
+      <c r="E142" s="91"/>
+      <c r="F142" s="91"/>
+      <c r="G142" s="91"/>
+      <c r="H142" s="93"/>
     </row>
     <row r="143" spans="2:9">
       <c r="B143" s="1"/>
       <c r="C143" s="64"/>
-      <c r="D143" s="93"/>
-      <c r="E143" s="93"/>
-      <c r="F143" s="93"/>
-      <c r="G143" s="93"/>
-      <c r="H143" s="95"/>
+      <c r="D143" s="91"/>
+      <c r="E143" s="91"/>
+      <c r="F143" s="91"/>
+      <c r="G143" s="91"/>
+      <c r="H143" s="93"/>
     </row>
     <row r="144" spans="2:9">
       <c r="B144" s="1"/>
       <c r="C144" s="64"/>
-      <c r="D144" s="93"/>
-      <c r="E144" s="93"/>
-      <c r="F144" s="93"/>
-      <c r="G144" s="93"/>
-      <c r="H144" s="95"/>
+      <c r="D144" s="91"/>
+      <c r="E144" s="91"/>
+      <c r="F144" s="91"/>
+      <c r="G144" s="91"/>
+      <c r="H144" s="93"/>
     </row>
     <row r="145" spans="2:8">
       <c r="B145" s="1"/>
       <c r="C145" s="64"/>
-      <c r="D145" s="93"/>
-      <c r="E145" s="93"/>
-      <c r="F145" s="93"/>
-      <c r="G145" s="93"/>
-      <c r="H145" s="95"/>
+      <c r="D145" s="91"/>
+      <c r="E145" s="91"/>
+      <c r="F145" s="91"/>
+      <c r="G145" s="91"/>
+      <c r="H145" s="93"/>
     </row>
     <row r="146" spans="2:8">
       <c r="B146" s="1"/>
       <c r="C146" s="64"/>
-      <c r="D146" s="93"/>
-      <c r="E146" s="93"/>
-      <c r="F146" s="93"/>
-      <c r="G146" s="93"/>
-      <c r="H146" s="95"/>
+      <c r="D146" s="91"/>
+      <c r="E146" s="91"/>
+      <c r="F146" s="91"/>
+      <c r="G146" s="91"/>
+      <c r="H146" s="93"/>
     </row>
     <row r="147" spans="2:8">
       <c r="B147" s="1"/>
       <c r="C147" s="64"/>
-      <c r="D147" s="93"/>
-      <c r="E147" s="93"/>
-      <c r="F147" s="93"/>
-      <c r="G147" s="93"/>
-      <c r="H147" s="95"/>
+      <c r="D147" s="91"/>
+      <c r="E147" s="91"/>
+      <c r="F147" s="91"/>
+      <c r="G147" s="91"/>
+      <c r="H147" s="93"/>
     </row>
     <row r="148" spans="2:8">
       <c r="B148" s="1"/>
       <c r="C148" s="64"/>
-      <c r="D148" s="93"/>
-      <c r="E148" s="93"/>
-      <c r="F148" s="93"/>
-      <c r="G148" s="93"/>
-      <c r="H148" s="95"/>
+      <c r="D148" s="91"/>
+      <c r="E148" s="91"/>
+      <c r="F148" s="91"/>
+      <c r="G148" s="91"/>
+      <c r="H148" s="93"/>
     </row>
     <row r="149" spans="2:8">
       <c r="B149" s="1"/>
       <c r="C149" s="64"/>
-      <c r="D149" s="93"/>
-      <c r="E149" s="93"/>
-      <c r="F149" s="93"/>
-      <c r="G149" s="93"/>
-      <c r="H149" s="95"/>
+      <c r="D149" s="91"/>
+      <c r="E149" s="91"/>
+      <c r="F149" s="91"/>
+      <c r="G149" s="91"/>
+      <c r="H149" s="93"/>
     </row>
     <row r="150" spans="2:8">
       <c r="B150" s="1"/>
       <c r="C150" s="64"/>
-      <c r="D150" s="93"/>
-      <c r="E150" s="93"/>
-      <c r="F150" s="93"/>
-      <c r="G150" s="93"/>
-      <c r="H150" s="95"/>
+      <c r="D150" s="91"/>
+      <c r="E150" s="91"/>
+      <c r="F150" s="91"/>
+      <c r="G150" s="91"/>
+      <c r="H150" s="93"/>
     </row>
     <row r="151" spans="2:8">
       <c r="B151" s="1"/>
       <c r="C151" s="64"/>
-      <c r="D151" s="93"/>
-      <c r="E151" s="93"/>
-      <c r="F151" s="93"/>
-      <c r="G151" s="93"/>
-      <c r="H151" s="95"/>
+      <c r="D151" s="91"/>
+      <c r="E151" s="91"/>
+      <c r="F151" s="91"/>
+      <c r="G151" s="91"/>
+      <c r="H151" s="93"/>
     </row>
     <row r="152" spans="2:8">
       <c r="B152" s="1"/>
       <c r="C152" s="64"/>
-      <c r="D152" s="93"/>
-      <c r="E152" s="93"/>
-      <c r="F152" s="93"/>
-      <c r="G152" s="93"/>
-      <c r="H152" s="95"/>
+      <c r="D152" s="91"/>
+      <c r="E152" s="91"/>
+      <c r="F152" s="91"/>
+      <c r="G152" s="91"/>
+      <c r="H152" s="93"/>
     </row>
     <row r="153" spans="2:8">
       <c r="B153" s="1"/>
       <c r="C153" s="64"/>
-      <c r="D153" s="93"/>
-      <c r="E153" s="93"/>
-      <c r="F153" s="93"/>
-      <c r="G153" s="93"/>
-      <c r="H153" s="95"/>
+      <c r="D153" s="91"/>
+      <c r="E153" s="91"/>
+      <c r="F153" s="91"/>
+      <c r="G153" s="91"/>
+      <c r="H153" s="93"/>
     </row>
     <row r="154" spans="2:8">
       <c r="B154" s="1"/>
       <c r="C154" s="64"/>
-      <c r="D154" s="93"/>
-      <c r="E154" s="93"/>
-      <c r="F154" s="93"/>
-      <c r="G154" s="93"/>
-      <c r="H154" s="95"/>
+      <c r="D154" s="91"/>
+      <c r="E154" s="91"/>
+      <c r="F154" s="91"/>
+      <c r="G154" s="91"/>
+      <c r="H154" s="93"/>
     </row>
     <row r="155" spans="2:8">
       <c r="B155" s="1"/>
       <c r="C155" s="64"/>
-      <c r="D155" s="93"/>
-      <c r="E155" s="93"/>
-      <c r="F155" s="93"/>
-      <c r="G155" s="93"/>
-      <c r="H155" s="95"/>
+      <c r="D155" s="91"/>
+      <c r="E155" s="91"/>
+      <c r="F155" s="91"/>
+      <c r="G155" s="91"/>
+      <c r="H155" s="93"/>
     </row>
     <row r="156" spans="2:8">
       <c r="B156" s="1"/>
       <c r="C156" s="64"/>
-      <c r="D156" s="93"/>
-      <c r="E156" s="93"/>
-      <c r="F156" s="93"/>
-      <c r="G156" s="93"/>
-      <c r="H156" s="95"/>
+      <c r="D156" s="91"/>
+      <c r="E156" s="91"/>
+      <c r="F156" s="91"/>
+      <c r="G156" s="91"/>
+      <c r="H156" s="93"/>
     </row>
     <row r="157" spans="2:8">
       <c r="B157" s="1"/>
       <c r="C157" s="64"/>
-      <c r="D157" s="93"/>
-      <c r="E157" s="93"/>
-      <c r="F157" s="93"/>
-      <c r="G157" s="93"/>
-      <c r="H157" s="95"/>
+      <c r="D157" s="91"/>
+      <c r="E157" s="91"/>
+      <c r="F157" s="91"/>
+      <c r="G157" s="91"/>
+      <c r="H157" s="93"/>
     </row>
     <row r="158" spans="2:8">
       <c r="B158" s="1"/>
       <c r="C158" s="64"/>
-      <c r="D158" s="93"/>
-      <c r="E158" s="93"/>
-      <c r="F158" s="93"/>
-      <c r="G158" s="93"/>
-      <c r="H158" s="95"/>
+      <c r="D158" s="91"/>
+      <c r="E158" s="91"/>
+      <c r="F158" s="91"/>
+      <c r="G158" s="91"/>
+      <c r="H158" s="93"/>
     </row>
     <row r="159" spans="2:8">
       <c r="B159" s="1"/>
       <c r="C159" s="64"/>
-      <c r="D159" s="93"/>
-      <c r="E159" s="93"/>
-      <c r="F159" s="93"/>
-      <c r="G159" s="93"/>
-      <c r="H159" s="95"/>
+      <c r="D159" s="91"/>
+      <c r="E159" s="91"/>
+      <c r="F159" s="91"/>
+      <c r="G159" s="91"/>
+      <c r="H159" s="93"/>
     </row>
     <row r="160" spans="2:8">
       <c r="B160" s="1"/>
       <c r="C160" s="64"/>
-      <c r="D160" s="93"/>
-      <c r="E160" s="93"/>
-      <c r="F160" s="93"/>
-      <c r="G160" s="93"/>
-      <c r="H160" s="95"/>
+      <c r="D160" s="91"/>
+      <c r="E160" s="91"/>
+      <c r="F160" s="91"/>
+      <c r="G160" s="91"/>
+      <c r="H160" s="93"/>
     </row>
     <row r="161" spans="2:8">
       <c r="B161" s="1"/>
       <c r="C161" s="64"/>
-      <c r="D161" s="93"/>
-      <c r="E161" s="93"/>
-      <c r="F161" s="93"/>
-      <c r="G161" s="93"/>
-      <c r="H161" s="95"/>
+      <c r="D161" s="91"/>
+      <c r="E161" s="91"/>
+      <c r="F161" s="91"/>
+      <c r="G161" s="91"/>
+      <c r="H161" s="93"/>
     </row>
     <row r="162" spans="2:8">
       <c r="B162" s="1"/>
       <c r="C162" s="64"/>
-      <c r="D162" s="93"/>
-      <c r="E162" s="93"/>
-      <c r="F162" s="93"/>
-      <c r="G162" s="93"/>
-      <c r="H162" s="95"/>
+      <c r="D162" s="91"/>
+      <c r="E162" s="91"/>
+      <c r="F162" s="91"/>
+      <c r="G162" s="91"/>
+      <c r="H162" s="93"/>
     </row>
     <row r="163" spans="2:8">
       <c r="B163" s="1"/>
       <c r="C163" s="64"/>
-      <c r="D163" s="93"/>
-      <c r="E163" s="93"/>
-      <c r="F163" s="93"/>
-      <c r="G163" s="93"/>
-      <c r="H163" s="95"/>
+      <c r="D163" s="91"/>
+      <c r="E163" s="91"/>
+      <c r="F163" s="91"/>
+      <c r="G163" s="91"/>
+      <c r="H163" s="93"/>
     </row>
     <row r="164" spans="2:8">
       <c r="B164" s="1"/>
       <c r="C164" s="64"/>
-      <c r="D164" s="93"/>
-      <c r="E164" s="93"/>
-      <c r="F164" s="93"/>
-      <c r="G164" s="93"/>
-      <c r="H164" s="95"/>
+      <c r="D164" s="91"/>
+      <c r="E164" s="91"/>
+      <c r="F164" s="91"/>
+      <c r="G164" s="91"/>
+      <c r="H164" s="93"/>
     </row>
     <row r="165" spans="2:8">
       <c r="B165" s="1"/>
       <c r="C165" s="64"/>
-      <c r="D165" s="93"/>
-      <c r="E165" s="93"/>
-      <c r="F165" s="93"/>
-      <c r="G165" s="93"/>
-      <c r="H165" s="95"/>
+      <c r="D165" s="91"/>
+      <c r="E165" s="91"/>
+      <c r="F165" s="91"/>
+      <c r="G165" s="91"/>
+      <c r="H165" s="93"/>
     </row>
     <row r="166" spans="2:8">
       <c r="B166" s="1"/>
       <c r="C166" s="64"/>
-      <c r="D166" s="93"/>
-      <c r="E166" s="93"/>
-      <c r="F166" s="93"/>
-      <c r="G166" s="93"/>
-      <c r="H166" s="95"/>
+      <c r="D166" s="91"/>
+      <c r="E166" s="91"/>
+      <c r="F166" s="91"/>
+      <c r="G166" s="91"/>
+      <c r="H166" s="93"/>
     </row>
     <row r="167" spans="2:8">
       <c r="B167" s="1"/>
       <c r="C167" s="64"/>
-      <c r="D167" s="93"/>
-      <c r="E167" s="93"/>
-      <c r="F167" s="93"/>
-      <c r="G167" s="93"/>
-      <c r="H167" s="95"/>
+      <c r="D167" s="91"/>
+      <c r="E167" s="91"/>
+      <c r="F167" s="91"/>
+      <c r="G167" s="91"/>
+      <c r="H167" s="93"/>
     </row>
     <row r="168" spans="2:8">
       <c r="B168" s="1"/>
       <c r="C168" s="64"/>
-      <c r="D168" s="93"/>
-      <c r="E168" s="93"/>
-      <c r="F168" s="93"/>
-      <c r="G168" s="93"/>
-      <c r="H168" s="95"/>
+      <c r="D168" s="91"/>
+      <c r="E168" s="91"/>
+      <c r="F168" s="91"/>
+      <c r="G168" s="91"/>
+      <c r="H168" s="93"/>
     </row>
     <row r="169" spans="2:8">
       <c r="B169" s="1"/>
       <c r="C169" s="64"/>
-      <c r="D169" s="93"/>
-      <c r="E169" s="93"/>
-      <c r="F169" s="93"/>
-      <c r="G169" s="93"/>
-      <c r="H169" s="95"/>
+      <c r="D169" s="91"/>
+      <c r="E169" s="91"/>
+      <c r="F169" s="91"/>
+      <c r="G169" s="91"/>
+      <c r="H169" s="93"/>
     </row>
     <row r="170" spans="2:8">
       <c r="B170" s="1"/>
       <c r="C170" s="64"/>
-      <c r="D170" s="93"/>
-      <c r="E170" s="93"/>
-      <c r="F170" s="93"/>
-      <c r="G170" s="93"/>
-      <c r="H170" s="95"/>
+      <c r="D170" s="91"/>
+      <c r="E170" s="91"/>
+      <c r="F170" s="91"/>
+      <c r="G170" s="91"/>
+      <c r="H170" s="93"/>
     </row>
     <row r="171" spans="2:8">
       <c r="B171" s="1"/>
       <c r="C171" s="64"/>
-      <c r="D171" s="93"/>
-      <c r="E171" s="93"/>
-      <c r="F171" s="93"/>
-      <c r="G171" s="93"/>
-      <c r="H171" s="95"/>
+      <c r="D171" s="91"/>
+      <c r="E171" s="91"/>
+      <c r="F171" s="91"/>
+      <c r="G171" s="91"/>
+      <c r="H171" s="93"/>
     </row>
     <row r="172" spans="2:8">
       <c r="B172" s="1"/>
       <c r="C172" s="64"/>
-      <c r="D172" s="93"/>
-      <c r="E172" s="93"/>
-      <c r="F172" s="93"/>
-      <c r="G172" s="93"/>
-      <c r="H172" s="95"/>
+      <c r="D172" s="91"/>
+      <c r="E172" s="91"/>
+      <c r="F172" s="91"/>
+      <c r="G172" s="91"/>
+      <c r="H172" s="93"/>
     </row>
     <row r="173" spans="2:8">
       <c r="B173" s="1"/>
       <c r="C173" s="64"/>
-      <c r="D173" s="93"/>
-      <c r="E173" s="93"/>
-      <c r="F173" s="93"/>
-      <c r="G173" s="93"/>
-      <c r="H173" s="95"/>
+      <c r="D173" s="91"/>
+      <c r="E173" s="91"/>
+      <c r="F173" s="91"/>
+      <c r="G173" s="91"/>
+      <c r="H173" s="93"/>
     </row>
     <row r="174" spans="2:8">
       <c r="B174" s="1"/>
       <c r="C174" s="64"/>
-      <c r="D174" s="93"/>
-      <c r="E174" s="93"/>
-      <c r="F174" s="93"/>
-      <c r="G174" s="93"/>
-      <c r="H174" s="95"/>
+      <c r="D174" s="91"/>
+      <c r="E174" s="91"/>
+      <c r="F174" s="91"/>
+      <c r="G174" s="91"/>
+      <c r="H174" s="93"/>
     </row>
     <row r="175" spans="2:8">
       <c r="B175" s="1"/>
       <c r="C175" s="64"/>
-      <c r="D175" s="93"/>
-      <c r="E175" s="93"/>
-      <c r="F175" s="93"/>
-      <c r="G175" s="93"/>
-      <c r="H175" s="95"/>
+      <c r="D175" s="91"/>
+      <c r="E175" s="91"/>
+      <c r="F175" s="91"/>
+      <c r="G175" s="91"/>
+      <c r="H175" s="93"/>
     </row>
     <row r="176" spans="2:8">
       <c r="B176" s="1"/>
       <c r="C176" s="64"/>
-      <c r="D176" s="93"/>
-      <c r="E176" s="93"/>
-      <c r="F176" s="93"/>
-      <c r="G176" s="93"/>
-      <c r="H176" s="95"/>
+      <c r="D176" s="91"/>
+      <c r="E176" s="91"/>
+      <c r="F176" s="91"/>
+      <c r="G176" s="91"/>
+      <c r="H176" s="93"/>
     </row>
     <row r="177" spans="2:8">
       <c r="B177" s="1"/>
       <c r="C177" s="64"/>
-      <c r="D177" s="93"/>
-      <c r="E177" s="93"/>
-      <c r="F177" s="93"/>
-      <c r="G177" s="93"/>
-      <c r="H177" s="95"/>
+      <c r="D177" s="91"/>
+      <c r="E177" s="91"/>
+      <c r="F177" s="91"/>
+      <c r="G177" s="91"/>
+      <c r="H177" s="93"/>
     </row>
     <row r="178" spans="2:8">
       <c r="B178" s="1"/>
       <c r="C178" s="64"/>
-      <c r="D178" s="93"/>
-      <c r="E178" s="93"/>
-      <c r="F178" s="93"/>
-      <c r="G178" s="93"/>
-      <c r="H178" s="95"/>
+      <c r="D178" s="91"/>
+      <c r="E178" s="91"/>
+      <c r="F178" s="91"/>
+      <c r="G178" s="91"/>
+      <c r="H178" s="93"/>
     </row>
     <row r="179" spans="2:8">
       <c r="B179" s="1"/>
       <c r="C179" s="64"/>
-      <c r="D179" s="93"/>
-      <c r="E179" s="93"/>
-      <c r="F179" s="93"/>
-      <c r="G179" s="93"/>
-      <c r="H179" s="95"/>
+      <c r="D179" s="91"/>
+      <c r="E179" s="91"/>
+      <c r="F179" s="91"/>
+      <c r="G179" s="91"/>
+      <c r="H179" s="93"/>
     </row>
     <row r="180" spans="2:8">
       <c r="B180" s="1"/>
       <c r="C180" s="64"/>
-      <c r="D180" s="93"/>
-      <c r="E180" s="93"/>
-      <c r="F180" s="93"/>
-      <c r="G180" s="93"/>
-      <c r="H180" s="95"/>
+      <c r="D180" s="91"/>
+      <c r="E180" s="91"/>
+      <c r="F180" s="91"/>
+      <c r="G180" s="91"/>
+      <c r="H180" s="93"/>
     </row>
     <row r="181" spans="2:8">
       <c r="B181" s="1"/>
       <c r="C181" s="64"/>
-      <c r="D181" s="93"/>
-      <c r="E181" s="93"/>
-      <c r="F181" s="93"/>
-      <c r="G181" s="93"/>
-      <c r="H181" s="95"/>
+      <c r="D181" s="91"/>
+      <c r="E181" s="91"/>
+      <c r="F181" s="91"/>
+      <c r="G181" s="91"/>
+      <c r="H181" s="93"/>
     </row>
     <row r="182" spans="2:8">
       <c r="B182" s="1"/>
       <c r="C182" s="64"/>
-      <c r="D182" s="93"/>
-      <c r="E182" s="93"/>
-      <c r="F182" s="93"/>
-      <c r="G182" s="93"/>
-      <c r="H182" s="95"/>
+      <c r="D182" s="91"/>
+      <c r="E182" s="91"/>
+      <c r="F182" s="91"/>
+      <c r="G182" s="91"/>
+      <c r="H182" s="93"/>
     </row>
     <row r="183" spans="2:8">
       <c r="B183" s="1"/>
       <c r="C183" s="64"/>
-      <c r="D183" s="93"/>
-      <c r="E183" s="93"/>
-      <c r="F183" s="94"/>
-      <c r="G183" s="93"/>
-      <c r="H183" s="95"/>
+      <c r="D183" s="91"/>
+      <c r="E183" s="91"/>
+      <c r="F183" s="92"/>
+      <c r="G183" s="91"/>
+      <c r="H183" s="93"/>
     </row>
     <row r="184" spans="2:8">
       <c r="B184" s="1"/>
       <c r="C184" s="64"/>
-      <c r="D184" s="93"/>
-      <c r="E184" s="93"/>
-      <c r="F184" s="94"/>
-      <c r="G184" s="93"/>
-      <c r="H184" s="95"/>
+      <c r="D184" s="91"/>
+      <c r="E184" s="91"/>
+      <c r="F184" s="92"/>
+      <c r="G184" s="91"/>
+      <c r="H184" s="93"/>
     </row>
     <row r="185" spans="2:8">
       <c r="B185" s="1"/>
       <c r="C185" s="64"/>
-      <c r="D185" s="93"/>
-      <c r="E185" s="93"/>
-      <c r="F185" s="94"/>
-      <c r="G185" s="93"/>
-      <c r="H185" s="95"/>
+      <c r="D185" s="91"/>
+      <c r="E185" s="91"/>
+      <c r="F185" s="92"/>
+      <c r="G185" s="91"/>
+      <c r="H185" s="93"/>
     </row>
     <row r="186" spans="2:8">
       <c r="B186" s="1"/>
       <c r="C186" s="64"/>
-      <c r="D186" s="93"/>
-      <c r="E186" s="93"/>
-      <c r="F186" s="94"/>
-      <c r="G186" s="93"/>
-      <c r="H186" s="95"/>
+      <c r="D186" s="91"/>
+      <c r="E186" s="91"/>
+      <c r="F186" s="92"/>
+      <c r="G186" s="91"/>
+      <c r="H186" s="93"/>
     </row>
     <row r="187" spans="2:8">
       <c r="B187" s="1"/>
       <c r="C187" s="64"/>
-      <c r="D187" s="93"/>
-      <c r="E187" s="93"/>
-      <c r="F187" s="94"/>
-      <c r="G187" s="93"/>
-      <c r="H187" s="95"/>
+      <c r="D187" s="91"/>
+      <c r="E187" s="91"/>
+      <c r="F187" s="92"/>
+      <c r="G187" s="91"/>
+      <c r="H187" s="93"/>
     </row>
     <row r="188" spans="2:8">
       <c r="B188" s="1"/>
       <c r="C188" s="64"/>
-      <c r="D188" s="93"/>
-      <c r="E188" s="93"/>
-      <c r="F188" s="94"/>
-      <c r="G188" s="93"/>
-      <c r="H188" s="95"/>
+      <c r="D188" s="91"/>
+      <c r="E188" s="91"/>
+      <c r="F188" s="92"/>
+      <c r="G188" s="91"/>
+      <c r="H188" s="93"/>
     </row>
     <row r="189" spans="2:8">
       <c r="B189" s="1"/>
       <c r="C189" s="64"/>
-      <c r="D189" s="93"/>
-      <c r="E189" s="93"/>
-      <c r="F189" s="94"/>
-      <c r="G189" s="93"/>
-      <c r="H189" s="95"/>
+      <c r="D189" s="91"/>
+      <c r="E189" s="91"/>
+      <c r="F189" s="92"/>
+      <c r="G189" s="91"/>
+      <c r="H189" s="93"/>
     </row>
     <row r="190" spans="2:8">
       <c r="B190" s="1"/>
       <c r="C190" s="64"/>
-      <c r="D190" s="93"/>
-      <c r="E190" s="93"/>
-      <c r="F190" s="94"/>
-      <c r="G190" s="93"/>
-      <c r="H190" s="95"/>
+      <c r="D190" s="91"/>
+      <c r="E190" s="91"/>
+      <c r="F190" s="92"/>
+      <c r="G190" s="91"/>
+      <c r="H190" s="93"/>
     </row>
     <row r="191" spans="2:8">
       <c r="B191" s="1"/>
       <c r="C191" s="64"/>
-      <c r="D191" s="93"/>
-      <c r="E191" s="93"/>
-      <c r="F191" s="94"/>
-      <c r="G191" s="93"/>
-      <c r="H191" s="95"/>
+      <c r="D191" s="91"/>
+      <c r="E191" s="91"/>
+      <c r="F191" s="92"/>
+      <c r="G191" s="91"/>
+      <c r="H191" s="93"/>
     </row>
     <row r="192" spans="2:8">
       <c r="B192" s="1"/>
       <c r="C192" s="64"/>
-      <c r="D192" s="93"/>
-      <c r="E192" s="93"/>
-      <c r="F192" s="94"/>
-      <c r="G192" s="93"/>
-      <c r="H192" s="95"/>
+      <c r="D192" s="91"/>
+      <c r="E192" s="91"/>
+      <c r="F192" s="92"/>
+      <c r="G192" s="91"/>
+      <c r="H192" s="93"/>
     </row>
     <row r="193" spans="2:8">
       <c r="B193" s="1"/>
       <c r="C193" s="64"/>
-      <c r="D193" s="93"/>
-      <c r="E193" s="93"/>
-      <c r="F193" s="94"/>
-      <c r="G193" s="93"/>
-      <c r="H193" s="95"/>
+      <c r="D193" s="91"/>
+      <c r="E193" s="91"/>
+      <c r="F193" s="92"/>
+      <c r="G193" s="91"/>
+      <c r="H193" s="93"/>
     </row>
     <row r="194" spans="2:8">
       <c r="B194" s="1"/>
       <c r="C194" s="64"/>
-      <c r="D194" s="93"/>
-      <c r="E194" s="93"/>
-      <c r="F194" s="94"/>
-      <c r="G194" s="93"/>
-      <c r="H194" s="95"/>
+      <c r="D194" s="91"/>
+      <c r="E194" s="91"/>
+      <c r="F194" s="92"/>
+      <c r="G194" s="91"/>
+      <c r="H194" s="93"/>
     </row>
     <row r="195" spans="2:8">
       <c r="B195" s="1"/>
       <c r="C195" s="64"/>
-      <c r="D195" s="93"/>
-      <c r="E195" s="93"/>
-      <c r="F195" s="94"/>
-      <c r="G195" s="93"/>
-      <c r="H195" s="95"/>
+      <c r="D195" s="91"/>
+      <c r="E195" s="91"/>
+      <c r="F195" s="92"/>
+      <c r="G195" s="91"/>
+      <c r="H195" s="93"/>
     </row>
     <row r="196" spans="2:8">
       <c r="B196" s="1"/>
       <c r="C196" s="64"/>
-      <c r="D196" s="93"/>
-      <c r="E196" s="93"/>
-      <c r="F196" s="94"/>
-      <c r="G196" s="93"/>
-      <c r="H196" s="95"/>
+      <c r="D196" s="91"/>
+      <c r="E196" s="91"/>
+      <c r="F196" s="92"/>
+      <c r="G196" s="91"/>
+      <c r="H196" s="93"/>
     </row>
     <row r="197" spans="2:8">
       <c r="B197" s="1"/>
       <c r="C197" s="64"/>
-      <c r="D197" s="93"/>
-      <c r="E197" s="93"/>
-      <c r="F197" s="94"/>
-      <c r="G197" s="93"/>
-      <c r="H197" s="95"/>
+      <c r="D197" s="91"/>
+      <c r="E197" s="91"/>
+      <c r="F197" s="92"/>
+      <c r="G197" s="91"/>
+      <c r="H197" s="93"/>
     </row>
     <row r="198" spans="2:8">
       <c r="B198" s="1"/>
       <c r="C198" s="64"/>
-      <c r="D198" s="93"/>
-      <c r="E198" s="93"/>
-      <c r="F198" s="94"/>
-      <c r="G198" s="93"/>
-      <c r="H198" s="95"/>
+      <c r="D198" s="91"/>
+      <c r="E198" s="91"/>
+      <c r="F198" s="92"/>
+      <c r="G198" s="91"/>
+      <c r="H198" s="93"/>
     </row>
     <row r="199" spans="2:8">
       <c r="B199" s="1"/>
       <c r="C199" s="64"/>
-      <c r="D199" s="93"/>
-      <c r="E199" s="93"/>
-      <c r="F199" s="94"/>
-      <c r="G199" s="93"/>
-      <c r="H199" s="95"/>
+      <c r="D199" s="91"/>
+      <c r="E199" s="91"/>
+      <c r="F199" s="92"/>
+      <c r="G199" s="91"/>
+      <c r="H199" s="93"/>
     </row>
     <row r="200" spans="2:8">
       <c r="B200" s="1"/>
       <c r="C200" s="64"/>
-      <c r="D200" s="104"/>
-      <c r="E200" s="104"/>
-      <c r="F200" s="105"/>
-      <c r="G200" s="106"/>
-      <c r="H200" s="95"/>
+      <c r="D200" s="102"/>
+      <c r="E200" s="102"/>
+      <c r="F200" s="103"/>
+      <c r="G200" s="104"/>
+      <c r="H200" s="93"/>
     </row>
     <row r="201" spans="2:8">
       <c r="B201" s="1"/>
       <c r="C201" s="64"/>
-      <c r="D201" s="104"/>
-      <c r="E201" s="104"/>
-      <c r="F201" s="105"/>
-      <c r="G201" s="106"/>
-      <c r="H201" s="95"/>
+      <c r="D201" s="102"/>
+      <c r="E201" s="102"/>
+      <c r="F201" s="103"/>
+      <c r="G201" s="104"/>
+      <c r="H201" s="93"/>
     </row>
     <row r="202" spans="2:8">
       <c r="B202" s="1"/>
       <c r="C202" s="64"/>
-      <c r="D202" s="104"/>
-      <c r="E202" s="104"/>
-      <c r="F202" s="105"/>
-      <c r="G202" s="106"/>
-      <c r="H202" s="95"/>
+      <c r="D202" s="102"/>
+      <c r="E202" s="102"/>
+      <c r="F202" s="103"/>
+      <c r="G202" s="104"/>
+      <c r="H202" s="93"/>
     </row>
     <row r="203" spans="2:8">
       <c r="B203" s="1"/>
       <c r="C203" s="64"/>
-      <c r="D203" s="104"/>
-      <c r="E203" s="104"/>
-      <c r="F203" s="105"/>
-      <c r="G203" s="106"/>
-      <c r="H203" s="95"/>
+      <c r="D203" s="102"/>
+      <c r="E203" s="102"/>
+      <c r="F203" s="103"/>
+      <c r="G203" s="104"/>
+      <c r="H203" s="93"/>
     </row>
     <row r="204" spans="2:8">
       <c r="B204" s="1"/>
       <c r="C204" s="64"/>
-      <c r="D204" s="104"/>
-      <c r="E204" s="104"/>
-      <c r="F204" s="105"/>
-      <c r="G204" s="106"/>
-      <c r="H204" s="95"/>
+      <c r="D204" s="102"/>
+      <c r="E204" s="102"/>
+      <c r="F204" s="103"/>
+      <c r="G204" s="104"/>
+      <c r="H204" s="93"/>
     </row>
     <row r="205" spans="2:8">
       <c r="B205" s="1"/>
       <c r="C205" s="64"/>
-      <c r="D205" s="104"/>
-      <c r="E205" s="104"/>
-      <c r="F205" s="105"/>
-      <c r="G205" s="106"/>
-      <c r="H205" s="95"/>
+      <c r="D205" s="102"/>
+      <c r="E205" s="102"/>
+      <c r="F205" s="103"/>
+      <c r="G205" s="104"/>
+      <c r="H205" s="93"/>
     </row>
     <row r="206" spans="2:8">
       <c r="B206" s="1"/>
       <c r="C206" s="64"/>
-      <c r="D206" s="104"/>
-      <c r="E206" s="104"/>
-      <c r="F206" s="105"/>
-      <c r="G206" s="106"/>
-      <c r="H206" s="95"/>
+      <c r="D206" s="102"/>
+      <c r="E206" s="102"/>
+      <c r="F206" s="103"/>
+      <c r="G206" s="104"/>
+      <c r="H206" s="93"/>
     </row>
     <row r="207" spans="2:8">
       <c r="B207" s="1"/>
       <c r="C207" s="64"/>
-      <c r="D207" s="104"/>
-      <c r="E207" s="104"/>
-      <c r="F207" s="105"/>
-      <c r="G207" s="106"/>
-      <c r="H207" s="95"/>
+      <c r="D207" s="102"/>
+      <c r="E207" s="102"/>
+      <c r="F207" s="103"/>
+      <c r="G207" s="104"/>
+      <c r="H207" s="93"/>
     </row>
     <row r="208" spans="2:8">
       <c r="B208" s="1"/>
       <c r="C208" s="64"/>
-      <c r="D208" s="104"/>
-      <c r="E208" s="104"/>
-      <c r="F208" s="105"/>
-      <c r="G208" s="106"/>
-      <c r="H208" s="95"/>
+      <c r="D208" s="102"/>
+      <c r="E208" s="102"/>
+      <c r="F208" s="103"/>
+      <c r="G208" s="104"/>
+      <c r="H208" s="93"/>
     </row>
     <row r="209" spans="2:8">
       <c r="B209" s="1"/>
       <c r="C209" s="64"/>
-      <c r="D209" s="104"/>
-      <c r="E209" s="104"/>
-      <c r="F209" s="105"/>
-      <c r="G209" s="106"/>
-      <c r="H209" s="95"/>
+      <c r="D209" s="102"/>
+      <c r="E209" s="102"/>
+      <c r="F209" s="103"/>
+      <c r="G209" s="104"/>
+      <c r="H209" s="93"/>
     </row>
     <row r="210" spans="2:8">
       <c r="B210" s="1"/>
       <c r="C210" s="64"/>
-      <c r="D210" s="104"/>
-      <c r="E210" s="104"/>
-      <c r="F210" s="105"/>
-      <c r="G210" s="106"/>
-      <c r="H210" s="95"/>
+      <c r="D210" s="102"/>
+      <c r="E210" s="102"/>
+      <c r="F210" s="103"/>
+      <c r="G210" s="104"/>
+      <c r="H210" s="93"/>
     </row>
     <row r="211" spans="2:8">
       <c r="B211" s="1"/>
       <c r="C211" s="64"/>
-      <c r="D211" s="104"/>
-      <c r="E211" s="104"/>
-      <c r="F211" s="105"/>
-      <c r="G211" s="106"/>
-      <c r="H211" s="95"/>
+      <c r="D211" s="102"/>
+      <c r="E211" s="102"/>
+      <c r="F211" s="103"/>
+      <c r="G211" s="104"/>
+      <c r="H211" s="93"/>
     </row>
     <row r="212" spans="2:8">
       <c r="B212" s="1"/>
       <c r="C212" s="64"/>
-      <c r="D212" s="104"/>
-      <c r="E212" s="104"/>
-      <c r="F212" s="105"/>
-      <c r="G212" s="106"/>
-      <c r="H212" s="95"/>
+      <c r="D212" s="102"/>
+      <c r="E212" s="102"/>
+      <c r="F212" s="103"/>
+      <c r="G212" s="104"/>
+      <c r="H212" s="93"/>
     </row>
     <row r="213" spans="2:8">
       <c r="B213" s="1"/>
       <c r="C213" s="64"/>
-      <c r="D213" s="104"/>
-      <c r="E213" s="104"/>
-      <c r="F213" s="105"/>
-      <c r="G213" s="106"/>
-      <c r="H213" s="95"/>
+      <c r="D213" s="102"/>
+      <c r="E213" s="102"/>
+      <c r="F213" s="103"/>
+      <c r="G213" s="104"/>
+      <c r="H213" s="93"/>
     </row>
     <row r="214" spans="2:8">
       <c r="B214" s="1"/>
       <c r="C214" s="64"/>
-      <c r="D214" s="104"/>
-      <c r="E214" s="104"/>
-      <c r="F214" s="105"/>
-      <c r="G214" s="106"/>
-      <c r="H214" s="95"/>
+      <c r="D214" s="102"/>
+      <c r="E214" s="102"/>
+      <c r="F214" s="103"/>
+      <c r="G214" s="104"/>
+      <c r="H214" s="93"/>
     </row>
     <row r="215" spans="2:8">
       <c r="B215" s="1"/>
       <c r="C215" s="64"/>
-      <c r="D215" s="104"/>
-      <c r="E215" s="104"/>
-      <c r="F215" s="105"/>
-      <c r="G215" s="106"/>
-      <c r="H215" s="95"/>
+      <c r="D215" s="102"/>
+      <c r="E215" s="102"/>
+      <c r="F215" s="103"/>
+      <c r="G215" s="104"/>
+      <c r="H215" s="93"/>
     </row>
     <row r="216" spans="2:8">
       <c r="B216" s="1"/>
       <c r="C216" s="64"/>
-      <c r="D216" s="104"/>
-      <c r="E216" s="104"/>
-      <c r="F216" s="105"/>
-      <c r="G216" s="106"/>
-      <c r="H216" s="95"/>
+      <c r="D216" s="102"/>
+      <c r="E216" s="102"/>
+      <c r="F216" s="103"/>
+      <c r="G216" s="104"/>
+      <c r="H216" s="93"/>
     </row>
     <row r="217" spans="2:8">
       <c r="B217" s="1"/>
       <c r="C217" s="64"/>
-      <c r="D217" s="104"/>
-      <c r="E217" s="104"/>
-      <c r="F217" s="105"/>
-      <c r="G217" s="106"/>
-      <c r="H217" s="95"/>
+      <c r="D217" s="102"/>
+      <c r="E217" s="102"/>
+      <c r="F217" s="103"/>
+      <c r="G217" s="104"/>
+      <c r="H217" s="93"/>
     </row>
     <row r="218" spans="2:8">
       <c r="B218" s="1"/>
       <c r="C218" s="64"/>
-      <c r="E218" s="104"/>
-      <c r="F218" s="104"/>
-      <c r="G218" s="105"/>
-      <c r="H218" s="95"/>
+      <c r="E218" s="102"/>
+      <c r="F218" s="102"/>
+      <c r="G218" s="103"/>
+      <c r="H218" s="93"/>
     </row>
     <row r="219" spans="2:8">
       <c r="B219" s="1"/>
       <c r="C219" s="64"/>
-      <c r="E219" s="104"/>
-      <c r="F219" s="104"/>
-      <c r="G219" s="105"/>
-      <c r="H219" s="95"/>
+      <c r="E219" s="102"/>
+      <c r="F219" s="102"/>
+      <c r="G219" s="103"/>
+      <c r="H219" s="93"/>
     </row>
     <row r="220" spans="2:8">
       <c r="B220" s="1"/>
       <c r="C220" s="64"/>
-      <c r="E220" s="104"/>
-      <c r="F220" s="104"/>
-      <c r="G220" s="105"/>
-      <c r="H220" s="95"/>
+      <c r="E220" s="102"/>
+      <c r="F220" s="102"/>
+      <c r="G220" s="103"/>
+      <c r="H220" s="93"/>
     </row>
     <row r="221" spans="2:8">
       <c r="B221" s="1"/>
       <c r="C221" s="64"/>
-      <c r="E221" s="104"/>
-      <c r="F221" s="104"/>
-      <c r="G221" s="105"/>
-      <c r="H221" s="95"/>
+      <c r="E221" s="102"/>
+      <c r="F221" s="102"/>
+      <c r="G221" s="103"/>
+      <c r="H221" s="93"/>
     </row>
     <row r="222" spans="2:8">
       <c r="B222" s="1"/>
       <c r="C222" s="64"/>
-      <c r="E222" s="104"/>
-      <c r="F222" s="104"/>
-      <c r="G222" s="105"/>
-      <c r="H222" s="95"/>
+      <c r="E222" s="102"/>
+      <c r="F222" s="102"/>
+      <c r="G222" s="103"/>
+      <c r="H222" s="93"/>
     </row>
     <row r="223" spans="2:8">
       <c r="B223" s="1"/>
       <c r="C223" s="64"/>
-      <c r="E223" s="104"/>
-      <c r="F223" s="104"/>
-      <c r="G223" s="105"/>
-      <c r="H223" s="95"/>
+      <c r="E223" s="102"/>
+      <c r="F223" s="102"/>
+      <c r="G223" s="103"/>
+      <c r="H223" s="93"/>
     </row>
     <row r="224" spans="2:8">
       <c r="B224" s="1"/>
       <c r="C224" s="64"/>
-      <c r="E224" s="104"/>
-      <c r="F224" s="104"/>
-      <c r="G224" s="105"/>
-      <c r="H224" s="95"/>
+      <c r="E224" s="102"/>
+      <c r="F224" s="102"/>
+      <c r="G224" s="103"/>
+      <c r="H224" s="93"/>
     </row>
     <row r="225" spans="2:8">
       <c r="B225" s="1"/>
       <c r="C225" s="64"/>
-      <c r="E225" s="104"/>
-      <c r="F225" s="104"/>
-      <c r="G225" s="105"/>
-      <c r="H225" s="95"/>
+      <c r="E225" s="102"/>
+      <c r="F225" s="102"/>
+      <c r="G225" s="103"/>
+      <c r="H225" s="93"/>
     </row>
     <row r="226" spans="2:8">
       <c r="B226" s="1"/>
       <c r="C226" s="64"/>
-      <c r="E226" s="104"/>
-      <c r="F226" s="104"/>
-      <c r="G226" s="105"/>
-      <c r="H226" s="95"/>
+      <c r="E226" s="102"/>
+      <c r="F226" s="102"/>
+      <c r="G226" s="103"/>
+      <c r="H226" s="93"/>
     </row>
     <row r="227" spans="2:8">
       <c r="B227" s="1"/>
       <c r="C227" s="64"/>
-      <c r="E227" s="104"/>
-      <c r="F227" s="104"/>
-      <c r="G227" s="105"/>
-      <c r="H227" s="95"/>
+      <c r="E227" s="102"/>
+      <c r="F227" s="102"/>
+      <c r="G227" s="103"/>
+      <c r="H227" s="93"/>
     </row>
     <row r="228" spans="2:8">
       <c r="B228" s="1"/>
       <c r="C228" s="64"/>
-      <c r="E228" s="104"/>
-      <c r="F228" s="104"/>
-      <c r="G228" s="105"/>
-      <c r="H228" s="95"/>
+      <c r="E228" s="102"/>
+      <c r="F228" s="102"/>
+      <c r="G228" s="103"/>
+      <c r="H228" s="93"/>
     </row>
     <row r="229" spans="2:8">
       <c r="B229" s="1"/>
       <c r="C229" s="64"/>
-      <c r="E229" s="104"/>
-      <c r="F229" s="104"/>
-      <c r="G229" s="105"/>
-      <c r="H229" s="95"/>
+      <c r="E229" s="102"/>
+      <c r="F229" s="102"/>
+      <c r="G229" s="103"/>
+      <c r="H229" s="93"/>
     </row>
     <row r="230" spans="2:8">
       <c r="B230" s="1"/>
       <c r="C230" s="64"/>
-      <c r="E230" s="104"/>
-      <c r="F230" s="104"/>
-      <c r="G230" s="105"/>
-      <c r="H230" s="95"/>
+      <c r="E230" s="102"/>
+      <c r="F230" s="102"/>
+      <c r="G230" s="103"/>
+      <c r="H230" s="93"/>
     </row>
     <row r="231" spans="2:8">
       <c r="B231" s="1"/>
       <c r="C231" s="64"/>
-      <c r="E231" s="104"/>
-      <c r="F231" s="104"/>
-      <c r="G231" s="105"/>
-      <c r="H231" s="95"/>
+      <c r="E231" s="102"/>
+      <c r="F231" s="102"/>
+      <c r="G231" s="103"/>
+      <c r="H231" s="93"/>
     </row>
     <row r="232" spans="2:8">
       <c r="B232" s="1"/>
       <c r="C232" s="64"/>
-      <c r="E232" s="104"/>
-      <c r="F232" s="104"/>
-      <c r="G232" s="105"/>
-      <c r="H232" s="95"/>
+      <c r="E232" s="102"/>
+      <c r="F232" s="102"/>
+      <c r="G232" s="103"/>
+      <c r="H232" s="93"/>
     </row>
     <row r="233" spans="2:8">
       <c r="B233" s="1"/>
       <c r="C233" s="64"/>
-      <c r="E233" s="104"/>
-      <c r="F233" s="104"/>
-      <c r="G233" s="105"/>
-      <c r="H233" s="95"/>
+      <c r="E233" s="102"/>
+      <c r="F233" s="102"/>
+      <c r="G233" s="103"/>
+      <c r="H233" s="93"/>
     </row>
     <row r="234" spans="2:8">
       <c r="B234" s="1"/>
       <c r="C234" s="64"/>
-      <c r="E234" s="104"/>
-      <c r="F234" s="104"/>
-      <c r="G234" s="105"/>
-      <c r="H234" s="95"/>
+      <c r="E234" s="102"/>
+      <c r="F234" s="102"/>
+      <c r="G234" s="103"/>
+      <c r="H234" s="93"/>
     </row>
     <row r="235" spans="2:8">
       <c r="B235" s="1"/>
       <c r="C235" s="64"/>
-      <c r="E235" s="104"/>
-      <c r="F235" s="104"/>
-      <c r="G235" s="105"/>
-      <c r="H235" s="95"/>
+      <c r="E235" s="102"/>
+      <c r="F235" s="102"/>
+      <c r="G235" s="103"/>
+      <c r="H235" s="93"/>
     </row>
     <row r="236" spans="2:8">
       <c r="B236" s="1"/>
       <c r="C236" s="64"/>
-      <c r="E236" s="104"/>
-      <c r="F236" s="104"/>
-      <c r="G236" s="105"/>
-      <c r="H236" s="95"/>
+      <c r="E236" s="102"/>
+      <c r="F236" s="102"/>
+      <c r="G236" s="103"/>
+      <c r="H236" s="93"/>
     </row>
     <row r="237" spans="2:8">
       <c r="B237" s="1"/>
       <c r="C237" s="64"/>
-      <c r="E237" s="104"/>
-      <c r="F237" s="104"/>
-      <c r="G237" s="105"/>
-      <c r="H237" s="95"/>
+      <c r="E237" s="102"/>
+      <c r="F237" s="102"/>
+      <c r="G237" s="103"/>
+      <c r="H237" s="93"/>
     </row>
     <row r="238" spans="2:8">
       <c r="B238" s="1"/>
       <c r="C238" s="64"/>
-      <c r="E238" s="104"/>
-      <c r="F238" s="104"/>
-      <c r="G238" s="105"/>
-      <c r="H238" s="95"/>
+      <c r="E238" s="102"/>
+      <c r="F238" s="102"/>
+      <c r="G238" s="103"/>
+      <c r="H238" s="93"/>
     </row>
     <row r="239" spans="2:8">
       <c r="B239" s="1"/>
       <c r="C239" s="64"/>
-      <c r="E239" s="104"/>
-      <c r="F239" s="104"/>
-      <c r="G239" s="105"/>
-      <c r="H239" s="95"/>
+      <c r="E239" s="102"/>
+      <c r="F239" s="102"/>
+      <c r="G239" s="103"/>
+      <c r="H239" s="93"/>
     </row>
     <row r="240" spans="2:8">
       <c r="B240" s="1"/>
       <c r="C240" s="64"/>
-      <c r="E240" s="104"/>
-      <c r="F240" s="104"/>
-      <c r="G240" s="105"/>
-      <c r="H240" s="95"/>
+      <c r="E240" s="102"/>
+      <c r="F240" s="102"/>
+      <c r="G240" s="103"/>
+      <c r="H240" s="93"/>
     </row>
     <row r="241" spans="2:8">
       <c r="B241" s="1"/>
       <c r="C241" s="64"/>
-      <c r="E241" s="104"/>
-      <c r="F241" s="104"/>
-      <c r="G241" s="105"/>
-      <c r="H241" s="95"/>
+      <c r="E241" s="102"/>
+      <c r="F241" s="102"/>
+      <c r="G241" s="103"/>
+      <c r="H241" s="93"/>
     </row>
     <row r="242" spans="2:8">
       <c r="B242" s="1"/>
       <c r="C242" s="64"/>
-      <c r="E242" s="104"/>
-      <c r="F242" s="104"/>
-      <c r="G242" s="105"/>
-      <c r="H242" s="95"/>
+      <c r="E242" s="102"/>
+      <c r="F242" s="102"/>
+      <c r="G242" s="103"/>
+      <c r="H242" s="93"/>
     </row>
     <row r="243" spans="2:8">
       <c r="B243" s="1"/>
       <c r="C243" s="64"/>
-      <c r="E243" s="104"/>
-      <c r="F243" s="104"/>
-      <c r="G243" s="105"/>
-      <c r="H243" s="95"/>
+      <c r="E243" s="102"/>
+      <c r="F243" s="102"/>
+      <c r="G243" s="103"/>
+      <c r="H243" s="93"/>
     </row>
     <row r="244" spans="2:8">
       <c r="B244" s="1"/>
       <c r="C244" s="64"/>
-      <c r="E244" s="104"/>
-      <c r="F244" s="104"/>
-      <c r="G244" s="105"/>
-      <c r="H244" s="95"/>
+      <c r="E244" s="102"/>
+      <c r="F244" s="102"/>
+      <c r="G244" s="103"/>
+      <c r="H244" s="93"/>
     </row>
     <row r="245" spans="2:8">
       <c r="B245" s="1"/>
       <c r="C245" s="64"/>
-      <c r="E245" s="104"/>
-      <c r="F245" s="104"/>
-      <c r="G245" s="105"/>
-      <c r="H245" s="95"/>
+      <c r="E245" s="102"/>
+      <c r="F245" s="102"/>
+      <c r="G245" s="103"/>
+      <c r="H245" s="93"/>
     </row>
     <row r="246" spans="2:8">
       <c r="B246" s="1"/>
       <c r="C246" s="64"/>
-      <c r="E246" s="104"/>
-      <c r="F246" s="104"/>
-      <c r="G246" s="105"/>
-      <c r="H246" s="95"/>
+      <c r="E246" s="102"/>
+      <c r="F246" s="102"/>
+      <c r="G246" s="103"/>
+      <c r="H246" s="93"/>
     </row>
     <row r="247" spans="2:8">
       <c r="B247" s="1"/>
       <c r="C247" s="64"/>
-      <c r="E247" s="104"/>
-      <c r="F247" s="104"/>
-      <c r="G247" s="105"/>
-      <c r="H247" s="95"/>
+      <c r="E247" s="102"/>
+      <c r="F247" s="102"/>
+      <c r="G247" s="103"/>
+      <c r="H247" s="93"/>
     </row>
     <row r="248" spans="2:8">
       <c r="B248" s="1"/>
       <c r="C248" s="64"/>
-      <c r="E248" s="104"/>
-      <c r="F248" s="104"/>
-      <c r="G248" s="105"/>
-      <c r="H248" s="95"/>
+      <c r="E248" s="102"/>
+      <c r="F248" s="102"/>
+      <c r="G248" s="103"/>
+      <c r="H248" s="93"/>
     </row>
     <row r="249" spans="2:8">
       <c r="B249" s="1"/>
       <c r="C249" s="64"/>
-      <c r="E249" s="104"/>
-      <c r="F249" s="104"/>
-      <c r="G249" s="105"/>
-      <c r="H249" s="95"/>
+      <c r="E249" s="102"/>
+      <c r="F249" s="102"/>
+      <c r="G249" s="103"/>
+      <c r="H249" s="93"/>
     </row>
     <row r="250" spans="2:8">
       <c r="B250" s="1"/>
       <c r="C250" s="64"/>
-      <c r="E250" s="104"/>
-      <c r="F250" s="104"/>
-      <c r="G250" s="105"/>
-      <c r="H250" s="95"/>
+      <c r="E250" s="102"/>
+      <c r="F250" s="102"/>
+      <c r="G250" s="103"/>
+      <c r="H250" s="93"/>
     </row>
     <row r="251" spans="2:8">
       <c r="B251" s="1"/>
       <c r="C251" s="64"/>
-      <c r="E251" s="104"/>
-      <c r="F251" s="104"/>
-      <c r="G251" s="105"/>
-      <c r="H251" s="95"/>
+      <c r="E251" s="102"/>
+      <c r="F251" s="102"/>
+      <c r="G251" s="103"/>
+      <c r="H251" s="93"/>
     </row>
     <row r="252" spans="2:8">
       <c r="B252" s="1"/>
       <c r="C252" s="64"/>
-      <c r="E252" s="104"/>
-      <c r="F252" s="104"/>
-      <c r="G252" s="105"/>
-      <c r="H252" s="95"/>
+      <c r="E252" s="102"/>
+      <c r="F252" s="102"/>
+      <c r="G252" s="103"/>
+      <c r="H252" s="93"/>
     </row>
     <row r="253" spans="2:8">
       <c r="B253" s="1"/>
       <c r="C253" s="64"/>
-      <c r="E253" s="104"/>
-      <c r="F253" s="104"/>
-      <c r="G253" s="105"/>
-      <c r="H253" s="95"/>
+      <c r="E253" s="102"/>
+      <c r="F253" s="102"/>
+      <c r="G253" s="103"/>
+      <c r="H253" s="93"/>
     </row>
     <row r="254" spans="2:8">
       <c r="B254" s="1"/>
       <c r="C254" s="64"/>
-      <c r="E254" s="104"/>
-      <c r="F254" s="104"/>
-      <c r="G254" s="105"/>
-      <c r="H254" s="95"/>
+      <c r="E254" s="102"/>
+      <c r="F254" s="102"/>
+      <c r="G254" s="103"/>
+      <c r="H254" s="93"/>
     </row>
     <row r="255" spans="2:8">
       <c r="B255" s="1"/>
       <c r="C255" s="64"/>
-      <c r="E255" s="104"/>
-      <c r="F255" s="104"/>
-      <c r="G255" s="105"/>
-      <c r="H255" s="95"/>
+      <c r="E255" s="102"/>
+      <c r="F255" s="102"/>
+      <c r="G255" s="103"/>
+      <c r="H255" s="93"/>
     </row>
     <row r="256" spans="2:8">
       <c r="B256" s="1"/>
       <c r="C256" s="64"/>
-      <c r="E256" s="104"/>
-      <c r="F256" s="104"/>
-      <c r="G256" s="105"/>
-      <c r="H256" s="95"/>
+      <c r="E256" s="102"/>
+      <c r="F256" s="102"/>
+      <c r="G256" s="103"/>
+      <c r="H256" s="93"/>
     </row>
     <row r="257" spans="2:8">
       <c r="B257" s="1"/>
       <c r="C257" s="64"/>
-      <c r="E257" s="104"/>
-      <c r="F257" s="104"/>
-      <c r="G257" s="105"/>
-      <c r="H257" s="95"/>
+      <c r="E257" s="102"/>
+      <c r="F257" s="102"/>
+      <c r="G257" s="103"/>
+      <c r="H257" s="93"/>
     </row>
     <row r="258" spans="2:8">
       <c r="B258" s="1"/>
       <c r="C258" s="64"/>
-      <c r="E258" s="104"/>
-      <c r="F258" s="104"/>
-      <c r="G258" s="105"/>
-      <c r="H258" s="95"/>
+      <c r="E258" s="102"/>
+      <c r="F258" s="102"/>
+      <c r="G258" s="103"/>
+      <c r="H258" s="93"/>
     </row>
     <row r="259" spans="2:8">
       <c r="B259" s="1"/>
       <c r="C259" s="64"/>
-      <c r="E259" s="104"/>
-      <c r="F259" s="104"/>
-      <c r="G259" s="105"/>
-      <c r="H259" s="95"/>
+      <c r="E259" s="102"/>
+      <c r="F259" s="102"/>
+      <c r="G259" s="103"/>
+      <c r="H259" s="93"/>
     </row>
     <row r="260" spans="2:8">
       <c r="B260" s="1"/>
       <c r="C260" s="64"/>
-      <c r="E260" s="104"/>
-      <c r="F260" s="104"/>
-      <c r="G260" s="105"/>
-      <c r="H260" s="95"/>
+      <c r="E260" s="102"/>
+      <c r="F260" s="102"/>
+      <c r="G260" s="103"/>
+      <c r="H260" s="93"/>
     </row>
     <row r="261" spans="2:8">
       <c r="B261" s="1"/>
       <c r="C261" s="64"/>
-      <c r="E261" s="104"/>
-      <c r="F261" s="104"/>
-      <c r="G261" s="105"/>
-      <c r="H261" s="95"/>
+      <c r="E261" s="102"/>
+      <c r="F261" s="102"/>
+      <c r="G261" s="103"/>
+      <c r="H261" s="93"/>
     </row>
     <row r="262" spans="2:8">
       <c r="B262" s="1"/>
       <c r="C262" s="64"/>
-      <c r="E262" s="104"/>
-      <c r="F262" s="104"/>
-      <c r="G262" s="105"/>
-      <c r="H262" s="95"/>
+      <c r="E262" s="102"/>
+      <c r="F262" s="102"/>
+      <c r="G262" s="103"/>
+      <c r="H262" s="93"/>
     </row>
     <row r="263" spans="2:8">
       <c r="B263" s="1"/>
       <c r="C263" s="64"/>
-      <c r="E263" s="104"/>
-      <c r="F263" s="104"/>
-      <c r="G263" s="105"/>
-      <c r="H263" s="95"/>
+      <c r="E263" s="102"/>
+      <c r="F263" s="102"/>
+      <c r="G263" s="103"/>
+      <c r="H263" s="93"/>
     </row>
     <row r="264" spans="2:8">
       <c r="B264" s="1"/>
       <c r="C264" s="64"/>
-      <c r="E264" s="104"/>
-      <c r="F264" s="104"/>
-      <c r="G264" s="105"/>
-      <c r="H264" s="95"/>
+      <c r="E264" s="102"/>
+      <c r="F264" s="102"/>
+      <c r="G264" s="103"/>
+      <c r="H264" s="93"/>
     </row>
     <row r="265" spans="2:8">
       <c r="B265" s="1"/>
       <c r="C265" s="64"/>
-      <c r="E265" s="104"/>
-      <c r="F265" s="104"/>
-      <c r="G265" s="105"/>
-      <c r="H265" s="95"/>
+      <c r="E265" s="102"/>
+      <c r="F265" s="102"/>
+      <c r="G265" s="103"/>
+      <c r="H265" s="93"/>
     </row>
     <row r="266" spans="2:8">
       <c r="B266" s="1"/>
       <c r="C266" s="64"/>
-      <c r="E266" s="104"/>
-      <c r="F266" s="104"/>
-      <c r="G266" s="105"/>
-      <c r="H266" s="95"/>
+      <c r="E266" s="102"/>
+      <c r="F266" s="102"/>
+      <c r="G266" s="103"/>
+      <c r="H266" s="93"/>
     </row>
     <row r="267" spans="2:8">
       <c r="B267" s="1"/>
       <c r="C267" s="64"/>
-      <c r="E267" s="104"/>
-      <c r="F267" s="104"/>
-      <c r="G267" s="105"/>
-      <c r="H267" s="95"/>
+      <c r="E267" s="102"/>
+      <c r="F267" s="102"/>
+      <c r="G267" s="103"/>
+      <c r="H267" s="93"/>
     </row>
     <row r="268" spans="2:8">
       <c r="B268" s="1"/>
       <c r="C268" s="64"/>
-      <c r="E268" s="104"/>
-      <c r="F268" s="104"/>
-      <c r="G268" s="105"/>
-      <c r="H268" s="95"/>
+      <c r="E268" s="102"/>
+      <c r="F268" s="102"/>
+      <c r="G268" s="103"/>
+      <c r="H268" s="93"/>
     </row>
     <row r="269" spans="2:8">
       <c r="B269" s="1"/>
       <c r="C269" s="64"/>
-      <c r="E269" s="104"/>
-      <c r="F269" s="104"/>
-      <c r="G269" s="105"/>
-      <c r="H269" s="95"/>
+      <c r="E269" s="102"/>
+      <c r="F269" s="102"/>
+      <c r="G269" s="103"/>
+      <c r="H269" s="93"/>
     </row>
     <row r="270" spans="2:8">
       <c r="B270" s="1"/>
       <c r="C270" s="64"/>
-      <c r="E270" s="104"/>
-      <c r="F270" s="104"/>
-      <c r="G270" s="105"/>
-      <c r="H270" s="95"/>
+      <c r="E270" s="102"/>
+      <c r="F270" s="102"/>
+      <c r="G270" s="103"/>
+      <c r="H270" s="93"/>
     </row>
     <row r="271" spans="2:8">
       <c r="B271" s="1"/>
       <c r="C271" s="64"/>
-      <c r="E271" s="104"/>
-      <c r="F271" s="104"/>
-      <c r="G271" s="105"/>
-      <c r="H271" s="95"/>
+      <c r="E271" s="102"/>
+      <c r="F271" s="102"/>
+      <c r="G271" s="103"/>
+      <c r="H271" s="93"/>
     </row>
     <row r="272" spans="2:8">
       <c r="B272" s="1"/>
       <c r="C272" s="64"/>
-      <c r="E272" s="104"/>
-      <c r="F272" s="104"/>
-      <c r="G272" s="105"/>
-      <c r="H272" s="95"/>
+      <c r="E272" s="102"/>
+      <c r="F272" s="102"/>
+      <c r="G272" s="103"/>
+      <c r="H272" s="93"/>
     </row>
     <row r="273" spans="2:8">
       <c r="B273" s="1"/>
       <c r="C273" s="64"/>
-      <c r="E273" s="104"/>
-      <c r="F273" s="104"/>
-      <c r="G273" s="105"/>
-      <c r="H273" s="95"/>
+      <c r="E273" s="102"/>
+      <c r="F273" s="102"/>
+      <c r="G273" s="103"/>
+      <c r="H273" s="93"/>
     </row>
     <row r="274" spans="2:8">
       <c r="B274" s="1"/>
       <c r="C274" s="64"/>
-      <c r="E274" s="104"/>
-      <c r="F274" s="104"/>
-      <c r="G274" s="105"/>
-      <c r="H274" s="95"/>
+      <c r="E274" s="102"/>
+      <c r="F274" s="102"/>
+      <c r="G274" s="103"/>
+      <c r="H274" s="93"/>
     </row>
     <row r="275" spans="2:8">
       <c r="B275" s="1"/>
       <c r="C275" s="64"/>
-      <c r="E275" s="104"/>
-      <c r="F275" s="104"/>
-      <c r="G275" s="105"/>
-      <c r="H275" s="95"/>
+      <c r="E275" s="102"/>
+      <c r="F275" s="102"/>
+      <c r="G275" s="103"/>
+      <c r="H275" s="93"/>
     </row>
     <row r="276" spans="2:8">
       <c r="B276" s="1"/>
       <c r="C276" s="64"/>
-      <c r="E276" s="104"/>
-      <c r="F276" s="104"/>
-      <c r="G276" s="105"/>
-      <c r="H276" s="95"/>
+      <c r="E276" s="102"/>
+      <c r="F276" s="102"/>
+      <c r="G276" s="103"/>
+      <c r="H276" s="93"/>
     </row>
     <row r="277" spans="2:8">
       <c r="B277" s="1"/>
       <c r="C277" s="64"/>
-      <c r="E277" s="104"/>
-      <c r="F277" s="104"/>
-      <c r="G277" s="105"/>
-      <c r="H277" s="95"/>
+      <c r="E277" s="102"/>
+      <c r="F277" s="102"/>
+      <c r="G277" s="103"/>
+      <c r="H277" s="93"/>
     </row>
     <row r="278" spans="2:8">
       <c r="B278" s="1"/>
       <c r="C278" s="64"/>
-      <c r="E278" s="104"/>
-      <c r="F278" s="104"/>
-      <c r="G278" s="105"/>
-      <c r="H278" s="95"/>
+      <c r="E278" s="102"/>
+      <c r="F278" s="102"/>
+      <c r="G278" s="103"/>
+      <c r="H278" s="93"/>
     </row>
     <row r="279" spans="2:8">
       <c r="B279" s="1"/>
       <c r="C279" s="64"/>
-      <c r="E279" s="104"/>
-      <c r="F279" s="104"/>
-      <c r="G279" s="105"/>
-      <c r="H279" s="95"/>
+      <c r="E279" s="102"/>
+      <c r="F279" s="102"/>
+      <c r="G279" s="103"/>
+      <c r="H279" s="93"/>
     </row>
     <row r="280" spans="2:8">
       <c r="B280" s="1"/>
       <c r="C280" s="64"/>
-      <c r="E280" s="104"/>
-      <c r="F280" s="104"/>
-      <c r="G280" s="105"/>
-      <c r="H280" s="95"/>
+      <c r="E280" s="102"/>
+      <c r="F280" s="102"/>
+      <c r="G280" s="103"/>
+      <c r="H280" s="93"/>
     </row>
     <row r="281" spans="2:8">
       <c r="B281" s="1"/>
       <c r="C281" s="64"/>
-      <c r="E281" s="104"/>
-      <c r="F281" s="104"/>
-      <c r="G281" s="105"/>
-      <c r="H281" s="95"/>
+      <c r="E281" s="102"/>
+      <c r="F281" s="102"/>
+      <c r="G281" s="103"/>
+      <c r="H281" s="93"/>
     </row>
     <row r="282" spans="2:8">
       <c r="B282" s="1"/>
       <c r="C282" s="64"/>
-      <c r="D282" s="105"/>
-      <c r="E282" s="104"/>
-      <c r="F282" s="104"/>
-      <c r="G282" s="104"/>
-      <c r="H282" s="95"/>
+      <c r="D282" s="103"/>
+      <c r="E282" s="102"/>
+      <c r="F282" s="102"/>
+      <c r="G282" s="102"/>
+      <c r="H282" s="93"/>
     </row>
     <row r="283" spans="2:8">
       <c r="B283" s="1"/>
       <c r="C283" s="64"/>
-      <c r="D283" s="105"/>
-      <c r="E283" s="104"/>
-      <c r="F283" s="104"/>
-      <c r="G283" s="104"/>
-      <c r="H283" s="95"/>
+      <c r="D283" s="103"/>
+      <c r="E283" s="102"/>
+      <c r="F283" s="102"/>
+      <c r="G283" s="102"/>
+      <c r="H283" s="93"/>
     </row>
     <row r="284" spans="2:8">
       <c r="B284" s="1"/>
       <c r="C284" s="64"/>
-      <c r="D284" s="105"/>
-      <c r="E284" s="104"/>
-      <c r="F284" s="104"/>
-      <c r="G284" s="104"/>
-      <c r="H284" s="95"/>
+      <c r="D284" s="103"/>
+      <c r="E284" s="102"/>
+      <c r="F284" s="102"/>
+      <c r="G284" s="102"/>
+      <c r="H284" s="93"/>
     </row>
     <row r="285" spans="2:8">
       <c r="B285" s="1"/>
       <c r="C285" s="64"/>
-      <c r="D285" s="105"/>
-      <c r="E285" s="104"/>
-      <c r="F285" s="104"/>
-      <c r="G285" s="104"/>
-      <c r="H285" s="95"/>
+      <c r="D285" s="103"/>
+      <c r="E285" s="102"/>
+      <c r="F285" s="102"/>
+      <c r="G285" s="102"/>
+      <c r="H285" s="93"/>
     </row>
     <row r="286" spans="2:8">
       <c r="B286" s="1"/>
       <c r="C286" s="64"/>
-      <c r="D286" s="105"/>
-      <c r="E286" s="104"/>
-      <c r="F286" s="104"/>
-      <c r="G286" s="104"/>
-      <c r="H286" s="95"/>
+      <c r="D286" s="103"/>
+      <c r="E286" s="102"/>
+      <c r="F286" s="102"/>
+      <c r="G286" s="102"/>
+      <c r="H286" s="93"/>
     </row>
     <row r="287" spans="2:8">
       <c r="B287" s="1"/>
       <c r="C287" s="64"/>
-      <c r="D287" s="105"/>
-      <c r="E287" s="104"/>
-      <c r="F287" s="104"/>
-      <c r="G287" s="104"/>
-      <c r="H287" s="95"/>
+      <c r="D287" s="103"/>
+      <c r="E287" s="102"/>
+      <c r="F287" s="102"/>
+      <c r="G287" s="102"/>
+      <c r="H287" s="93"/>
     </row>
     <row r="288" spans="2:8">
       <c r="B288" s="1"/>
       <c r="C288" s="64"/>
-      <c r="D288" s="105"/>
-      <c r="E288" s="104"/>
-      <c r="F288" s="104"/>
-      <c r="G288" s="104"/>
-      <c r="H288" s="95"/>
+      <c r="D288" s="103"/>
+      <c r="E288" s="102"/>
+      <c r="F288" s="102"/>
+      <c r="G288" s="102"/>
+      <c r="H288" s="93"/>
     </row>
     <row r="289" spans="2:8">
       <c r="B289" s="1"/>
       <c r="C289" s="64"/>
-      <c r="D289" s="105"/>
-      <c r="E289" s="104"/>
-      <c r="F289" s="104"/>
-      <c r="G289" s="104"/>
-      <c r="H289" s="95"/>
+      <c r="D289" s="103"/>
+      <c r="E289" s="102"/>
+      <c r="F289" s="102"/>
+      <c r="G289" s="102"/>
+      <c r="H289" s="93"/>
     </row>
     <row r="290" spans="2:8">
       <c r="B290" s="1"/>
       <c r="C290" s="64"/>
-      <c r="D290" s="105"/>
-      <c r="E290" s="104"/>
-      <c r="F290" s="104"/>
-      <c r="G290" s="104"/>
-      <c r="H290" s="95"/>
+      <c r="D290" s="103"/>
+      <c r="E290" s="102"/>
+      <c r="F290" s="102"/>
+      <c r="G290" s="102"/>
+      <c r="H290" s="93"/>
     </row>
     <row r="291" spans="2:8">
       <c r="B291" s="1"/>
       <c r="C291" s="64"/>
-      <c r="D291" s="105"/>
-      <c r="E291" s="104"/>
-      <c r="F291" s="104"/>
-      <c r="G291" s="104"/>
-      <c r="H291" s="95"/>
+      <c r="D291" s="103"/>
+      <c r="E291" s="102"/>
+      <c r="F291" s="102"/>
+      <c r="G291" s="102"/>
+      <c r="H291" s="93"/>
     </row>
     <row r="292" spans="2:8">
       <c r="B292" s="1"/>
       <c r="C292" s="64"/>
-      <c r="D292" s="105"/>
-      <c r="E292" s="104"/>
-      <c r="F292" s="104"/>
-      <c r="G292" s="104"/>
-      <c r="H292" s="95"/>
+      <c r="D292" s="103"/>
+      <c r="E292" s="102"/>
+      <c r="F292" s="102"/>
+      <c r="G292" s="102"/>
+      <c r="H292" s="93"/>
     </row>
     <row r="293" spans="2:8">
       <c r="B293" s="1"/>
       <c r="C293" s="64"/>
-      <c r="D293" s="105"/>
-      <c r="E293" s="104"/>
-      <c r="F293" s="104"/>
-      <c r="G293" s="104"/>
-      <c r="H293" s="95"/>
+      <c r="D293" s="103"/>
+      <c r="E293" s="102"/>
+      <c r="F293" s="102"/>
+      <c r="G293" s="102"/>
+      <c r="H293" s="93"/>
     </row>
     <row r="294" spans="2:8">
       <c r="B294" s="1"/>
       <c r="C294" s="64"/>
-      <c r="D294" s="105"/>
-      <c r="E294" s="104"/>
-      <c r="F294" s="104"/>
-      <c r="G294" s="104"/>
-      <c r="H294" s="95"/>
+      <c r="D294" s="103"/>
+      <c r="E294" s="102"/>
+      <c r="F294" s="102"/>
+      <c r="G294" s="102"/>
+      <c r="H294" s="93"/>
     </row>
     <row r="295" spans="2:8">
       <c r="B295" s="1"/>
       <c r="C295" s="64"/>
-      <c r="D295" s="105"/>
-      <c r="E295" s="104"/>
-      <c r="F295" s="104"/>
-      <c r="G295" s="104"/>
-      <c r="H295" s="95"/>
+      <c r="D295" s="103"/>
+      <c r="E295" s="102"/>
+      <c r="F295" s="102"/>
+      <c r="G295" s="102"/>
+      <c r="H295" s="93"/>
     </row>
     <row r="296" spans="2:8">
       <c r="B296" s="1"/>
       <c r="C296" s="64"/>
-      <c r="D296" s="105"/>
-      <c r="E296" s="104"/>
-      <c r="F296" s="104"/>
-      <c r="G296" s="104"/>
-      <c r="H296" s="95"/>
+      <c r="D296" s="103"/>
+      <c r="E296" s="102"/>
+      <c r="F296" s="102"/>
+      <c r="G296" s="102"/>
+      <c r="H296" s="93"/>
     </row>
     <row r="297" spans="2:8">
       <c r="B297" s="1"/>
       <c r="C297" s="64"/>
-      <c r="D297" s="105"/>
-      <c r="E297" s="104"/>
-      <c r="F297" s="104"/>
-      <c r="G297" s="104"/>
-      <c r="H297" s="95"/>
+      <c r="D297" s="103"/>
+      <c r="E297" s="102"/>
+      <c r="F297" s="102"/>
+      <c r="G297" s="102"/>
+      <c r="H297" s="93"/>
     </row>
     <row r="298" spans="2:8">
       <c r="B298" s="1"/>
       <c r="C298" s="64"/>
-      <c r="D298" s="105"/>
-      <c r="E298" s="104"/>
-      <c r="F298" s="104"/>
-      <c r="G298" s="104"/>
-      <c r="H298" s="95"/>
+      <c r="D298" s="103"/>
+      <c r="E298" s="102"/>
+      <c r="F298" s="102"/>
+      <c r="G298" s="102"/>
+      <c r="H298" s="93"/>
     </row>
     <row r="299" spans="2:8">
       <c r="B299" s="1"/>
       <c r="C299" s="64"/>
-      <c r="D299" s="105"/>
-      <c r="E299" s="104"/>
-      <c r="F299" s="104"/>
-      <c r="G299" s="104"/>
-      <c r="H299" s="95"/>
+      <c r="D299" s="103"/>
+      <c r="E299" s="102"/>
+      <c r="F299" s="102"/>
+      <c r="G299" s="102"/>
+      <c r="H299" s="93"/>
     </row>
     <row r="300" spans="2:8">
       <c r="B300" s="1"/>
       <c r="C300" s="64"/>
-      <c r="D300" s="105"/>
-      <c r="E300" s="104"/>
-      <c r="F300" s="104"/>
-      <c r="G300" s="104"/>
-      <c r="H300" s="95"/>
+      <c r="D300" s="103"/>
+      <c r="E300" s="102"/>
+      <c r="F300" s="102"/>
+      <c r="G300" s="102"/>
+      <c r="H300" s="93"/>
     </row>
     <row r="301" spans="2:8">
       <c r="B301" s="1"/>
       <c r="C301" s="64"/>
-      <c r="D301" s="105"/>
-      <c r="E301" s="104"/>
-      <c r="F301" s="104"/>
-      <c r="G301" s="104"/>
-      <c r="H301" s="95"/>
+      <c r="D301" s="103"/>
+      <c r="E301" s="102"/>
+      <c r="F301" s="102"/>
+      <c r="G301" s="102"/>
+      <c r="H301" s="93"/>
     </row>
     <row r="302" spans="2:8">
       <c r="B302" s="1"/>
       <c r="C302" s="64"/>
-      <c r="D302" s="105"/>
-      <c r="E302" s="104"/>
-      <c r="F302" s="104"/>
-      <c r="G302" s="104"/>
-      <c r="H302" s="95"/>
+      <c r="D302" s="103"/>
+      <c r="E302" s="102"/>
+      <c r="F302" s="102"/>
+      <c r="G302" s="102"/>
+      <c r="H302" s="93"/>
     </row>
     <row r="303" spans="2:8">
       <c r="B303" s="1"/>
       <c r="C303" s="64"/>
-      <c r="D303" s="105"/>
-      <c r="E303" s="104"/>
-      <c r="F303" s="104"/>
-      <c r="G303" s="104"/>
-      <c r="H303" s="95"/>
+      <c r="D303" s="103"/>
+      <c r="E303" s="102"/>
+      <c r="F303" s="102"/>
+      <c r="G303" s="102"/>
+      <c r="H303" s="93"/>
     </row>
     <row r="304" spans="2:8">
       <c r="B304" s="1"/>
       <c r="C304" s="64"/>
-      <c r="D304" s="105"/>
-      <c r="E304" s="104"/>
-      <c r="F304" s="104"/>
-      <c r="G304" s="104"/>
-      <c r="H304" s="95"/>
+      <c r="D304" s="103"/>
+      <c r="E304" s="102"/>
+      <c r="F304" s="102"/>
+      <c r="G304" s="102"/>
+      <c r="H304" s="93"/>
     </row>
     <row r="305" spans="2:8">
       <c r="B305" s="1"/>
       <c r="C305" s="64"/>
-      <c r="D305" s="105"/>
-      <c r="E305" s="104"/>
-      <c r="F305" s="104"/>
-      <c r="G305" s="104"/>
-      <c r="H305" s="95"/>
+      <c r="D305" s="103"/>
+      <c r="E305" s="102"/>
+      <c r="F305" s="102"/>
+      <c r="G305" s="102"/>
+      <c r="H305" s="93"/>
     </row>
     <row r="306" spans="2:8">
       <c r="B306" s="1"/>
       <c r="C306" s="64"/>
-      <c r="D306" s="105"/>
-      <c r="E306" s="104"/>
-      <c r="F306" s="104"/>
-      <c r="G306" s="104"/>
-      <c r="H306" s="95"/>
+      <c r="D306" s="103"/>
+      <c r="E306" s="102"/>
+      <c r="F306" s="102"/>
+      <c r="G306" s="102"/>
+      <c r="H306" s="93"/>
     </row>
     <row r="307" spans="2:8">
       <c r="B307" s="1"/>
       <c r="C307" s="64"/>
-      <c r="D307" s="105"/>
-      <c r="E307" s="104"/>
-      <c r="F307" s="104"/>
-      <c r="G307" s="104"/>
-      <c r="H307" s="95"/>
+      <c r="D307" s="103"/>
+      <c r="E307" s="102"/>
+      <c r="F307" s="102"/>
+      <c r="G307" s="102"/>
+      <c r="H307" s="93"/>
     </row>
     <row r="308" spans="2:8">
       <c r="B308" s="1"/>
       <c r="C308" s="64"/>
-      <c r="D308" s="105"/>
-      <c r="E308" s="104"/>
-      <c r="F308" s="104"/>
-      <c r="G308" s="104"/>
-      <c r="H308" s="95"/>
+      <c r="D308" s="103"/>
+      <c r="E308" s="102"/>
+      <c r="F308" s="102"/>
+      <c r="G308" s="102"/>
+      <c r="H308" s="93"/>
     </row>
     <row r="309" spans="2:8">
       <c r="B309" s="1"/>
       <c r="C309" s="64"/>
-      <c r="D309" s="105"/>
-      <c r="E309" s="104"/>
-      <c r="F309" s="104"/>
-      <c r="G309" s="104"/>
-      <c r="H309" s="95"/>
+      <c r="D309" s="103"/>
+      <c r="E309" s="102"/>
+      <c r="F309" s="102"/>
+      <c r="G309" s="102"/>
+      <c r="H309" s="93"/>
     </row>
     <row r="310" spans="2:8">
       <c r="B310" s="1"/>
       <c r="C310" s="64"/>
-      <c r="D310" s="105"/>
-      <c r="E310" s="104"/>
-      <c r="F310" s="104"/>
-      <c r="G310" s="104"/>
-      <c r="H310" s="95"/>
+      <c r="D310" s="103"/>
+      <c r="E310" s="102"/>
+      <c r="F310" s="102"/>
+      <c r="G310" s="102"/>
+      <c r="H310" s="93"/>
     </row>
     <row r="311" spans="2:8">
       <c r="B311" s="1"/>
       <c r="C311" s="64"/>
-      <c r="D311" s="105"/>
-      <c r="E311" s="104"/>
-      <c r="F311" s="104"/>
-      <c r="G311" s="104"/>
-      <c r="H311" s="95"/>
+      <c r="D311" s="103"/>
+      <c r="E311" s="102"/>
+      <c r="F311" s="102"/>
+      <c r="G311" s="102"/>
+      <c r="H311" s="93"/>
     </row>
     <row r="312" spans="2:8">
       <c r="B312" s="1"/>
       <c r="C312" s="64"/>
-      <c r="D312" s="105"/>
-      <c r="E312" s="104"/>
-      <c r="F312" s="104"/>
-      <c r="G312" s="104"/>
-      <c r="H312" s="95"/>
+      <c r="D312" s="103"/>
+      <c r="E312" s="102"/>
+      <c r="F312" s="102"/>
+      <c r="G312" s="102"/>
+      <c r="H312" s="93"/>
     </row>
     <row r="313" spans="2:8">
       <c r="B313" s="1"/>
       <c r="C313" s="64"/>
-      <c r="D313" s="105"/>
-      <c r="E313" s="104"/>
-      <c r="F313" s="104"/>
-      <c r="G313" s="104"/>
-      <c r="H313" s="95"/>
+      <c r="D313" s="103"/>
+      <c r="E313" s="102"/>
+      <c r="F313" s="102"/>
+      <c r="G313" s="102"/>
+      <c r="H313" s="93"/>
     </row>
     <row r="314" spans="2:8">
       <c r="B314" s="1"/>
       <c r="C314" s="64"/>
-      <c r="D314" s="105"/>
-      <c r="E314" s="104"/>
-      <c r="F314" s="104"/>
-      <c r="G314" s="104"/>
-      <c r="H314" s="95"/>
+      <c r="D314" s="103"/>
+      <c r="E314" s="102"/>
+      <c r="F314" s="102"/>
+      <c r="G314" s="102"/>
+      <c r="H314" s="93"/>
     </row>
     <row r="315" spans="2:8">
       <c r="B315" s="1"/>
       <c r="C315" s="64"/>
-      <c r="D315" s="105"/>
-      <c r="E315" s="104"/>
-      <c r="F315" s="104"/>
-      <c r="G315" s="104"/>
-      <c r="H315" s="95"/>
+      <c r="D315" s="103"/>
+      <c r="E315" s="102"/>
+      <c r="F315" s="102"/>
+      <c r="G315" s="102"/>
+      <c r="H315" s="93"/>
     </row>
     <row r="316" spans="2:8">
       <c r="B316" s="1"/>
       <c r="C316" s="64"/>
-      <c r="D316" s="105"/>
-      <c r="E316" s="104"/>
-      <c r="F316" s="104"/>
-      <c r="G316" s="104"/>
-      <c r="H316" s="95"/>
+      <c r="D316" s="103"/>
+      <c r="E316" s="102"/>
+      <c r="F316" s="102"/>
+      <c r="G316" s="102"/>
+      <c r="H316" s="93"/>
     </row>
     <row r="317" spans="2:8">
       <c r="B317" s="1"/>
       <c r="C317" s="64"/>
-      <c r="D317" s="105"/>
-      <c r="E317" s="104"/>
-      <c r="F317" s="104"/>
-      <c r="G317" s="104"/>
-      <c r="H317" s="95"/>
+      <c r="D317" s="103"/>
+      <c r="E317" s="102"/>
+      <c r="F317" s="102"/>
+      <c r="G317" s="102"/>
+      <c r="H317" s="93"/>
     </row>
     <row r="318" spans="2:8">
       <c r="B318" s="1"/>
       <c r="C318" s="64"/>
-      <c r="D318" s="105"/>
-      <c r="E318" s="104"/>
-      <c r="F318" s="104"/>
-      <c r="G318" s="104"/>
-      <c r="H318" s="95"/>
+      <c r="D318" s="103"/>
+      <c r="E318" s="102"/>
+      <c r="F318" s="102"/>
+      <c r="G318" s="102"/>
+      <c r="H318" s="93"/>
     </row>
     <row r="319" spans="2:8">
       <c r="B319" s="1"/>
       <c r="C319" s="64"/>
-      <c r="D319" s="105"/>
-      <c r="E319" s="104"/>
-      <c r="F319" s="104"/>
-      <c r="G319" s="104"/>
-      <c r="H319" s="95"/>
+      <c r="D319" s="103"/>
+      <c r="E319" s="102"/>
+      <c r="F319" s="102"/>
+      <c r="G319" s="102"/>
+      <c r="H319" s="93"/>
     </row>
     <row r="320" spans="2:8">
       <c r="B320" s="1"/>
       <c r="C320" s="64"/>
-      <c r="D320" s="105"/>
-      <c r="E320" s="104"/>
-      <c r="F320" s="104"/>
-      <c r="G320" s="104"/>
-      <c r="H320" s="95"/>
+      <c r="D320" s="103"/>
+      <c r="E320" s="102"/>
+      <c r="F320" s="102"/>
+      <c r="G320" s="102"/>
+      <c r="H320" s="93"/>
     </row>
     <row r="321" spans="2:8">
       <c r="B321" s="1"/>
       <c r="C321" s="64"/>
-      <c r="D321" s="105"/>
-      <c r="E321" s="104"/>
-      <c r="F321" s="104"/>
-      <c r="G321" s="104"/>
-      <c r="H321" s="95"/>
+      <c r="D321" s="103"/>
+      <c r="E321" s="102"/>
+      <c r="F321" s="102"/>
+      <c r="G321" s="102"/>
+      <c r="H321" s="93"/>
     </row>
     <row r="322" spans="2:8">
       <c r="B322" s="1"/>
       <c r="C322" s="64"/>
-      <c r="D322" s="105"/>
-      <c r="E322" s="104"/>
-      <c r="F322" s="104"/>
-      <c r="G322" s="104"/>
-      <c r="H322" s="95"/>
+      <c r="D322" s="103"/>
+      <c r="E322" s="102"/>
+      <c r="F322" s="102"/>
+      <c r="G322" s="102"/>
+      <c r="H322" s="93"/>
     </row>
     <row r="323" spans="2:8">
       <c r="B323" s="1"/>
       <c r="C323" s="64"/>
-      <c r="D323" s="105"/>
-      <c r="E323" s="104"/>
-      <c r="F323" s="104"/>
-      <c r="G323" s="104"/>
-      <c r="H323" s="95"/>
+      <c r="D323" s="103"/>
+      <c r="E323" s="102"/>
+      <c r="F323" s="102"/>
+      <c r="G323" s="102"/>
+      <c r="H323" s="93"/>
     </row>
     <row r="324" spans="2:8">
       <c r="B324" s="1"/>
       <c r="C324" s="64"/>
-      <c r="D324" s="105"/>
-      <c r="E324" s="104"/>
-      <c r="F324" s="104"/>
-      <c r="G324" s="104"/>
-      <c r="H324" s="95"/>
+      <c r="D324" s="103"/>
+      <c r="E324" s="102"/>
+      <c r="F324" s="102"/>
+      <c r="G324" s="102"/>
+      <c r="H324" s="93"/>
     </row>
     <row r="325" spans="2:8">
       <c r="B325" s="1"/>
       <c r="C325" s="64"/>
-      <c r="D325" s="105"/>
-      <c r="E325" s="104"/>
-      <c r="F325" s="104"/>
-      <c r="G325" s="104"/>
-      <c r="H325" s="95"/>
+      <c r="D325" s="103"/>
+      <c r="E325" s="102"/>
+      <c r="F325" s="102"/>
+      <c r="G325" s="102"/>
+      <c r="H325" s="93"/>
     </row>
     <row r="326" spans="2:8">
       <c r="B326" s="1"/>
       <c r="C326" s="64"/>
-      <c r="D326" s="105"/>
-      <c r="E326" s="104"/>
-      <c r="F326" s="104"/>
-      <c r="G326" s="104"/>
-      <c r="H326" s="95"/>
+      <c r="D326" s="103"/>
+      <c r="E326" s="102"/>
+      <c r="F326" s="102"/>
+      <c r="G326" s="102"/>
+      <c r="H326" s="93"/>
     </row>
     <row r="327" spans="2:8">
       <c r="B327" s="1"/>
       <c r="C327" s="64"/>
-      <c r="D327" s="105"/>
-      <c r="E327" s="104"/>
-      <c r="F327" s="104"/>
-      <c r="G327" s="104"/>
-      <c r="H327" s="95"/>
+      <c r="D327" s="103"/>
+      <c r="E327" s="102"/>
+      <c r="F327" s="102"/>
+      <c r="G327" s="102"/>
+      <c r="H327" s="93"/>
     </row>
     <row r="328" spans="2:8">
       <c r="B328" s="1"/>
       <c r="C328" s="64"/>
-      <c r="D328" s="105"/>
-      <c r="E328" s="104"/>
-      <c r="F328" s="104"/>
-      <c r="G328" s="104"/>
-      <c r="H328" s="95"/>
+      <c r="D328" s="103"/>
+      <c r="E328" s="102"/>
+      <c r="F328" s="102"/>
+      <c r="G328" s="102"/>
+      <c r="H328" s="93"/>
     </row>
     <row r="329" spans="2:8">
       <c r="B329" s="1"/>
       <c r="C329" s="64"/>
-      <c r="D329" s="105"/>
-      <c r="E329" s="104"/>
-      <c r="F329" s="104"/>
-      <c r="G329" s="104"/>
-      <c r="H329" s="95"/>
+      <c r="D329" s="103"/>
+      <c r="E329" s="102"/>
+      <c r="F329" s="102"/>
+      <c r="G329" s="102"/>
+      <c r="H329" s="93"/>
     </row>
     <row r="330" spans="2:8">
       <c r="B330" s="1"/>
       <c r="C330" s="64"/>
-      <c r="D330" s="105"/>
-      <c r="E330" s="104"/>
-      <c r="F330" s="104"/>
-      <c r="G330" s="104"/>
-      <c r="H330" s="95"/>
+      <c r="D330" s="103"/>
+      <c r="E330" s="102"/>
+      <c r="F330" s="102"/>
+      <c r="G330" s="102"/>
+      <c r="H330" s="93"/>
     </row>
     <row r="331" spans="2:8">
       <c r="B331" s="1"/>
       <c r="C331" s="64"/>
-      <c r="D331" s="105"/>
-      <c r="E331" s="104"/>
-      <c r="F331" s="104"/>
-      <c r="G331" s="104"/>
-      <c r="H331" s="95"/>
+      <c r="D331" s="103"/>
+      <c r="E331" s="102"/>
+      <c r="F331" s="102"/>
+      <c r="G331" s="102"/>
+      <c r="H331" s="93"/>
     </row>
     <row r="332" spans="2:8">
       <c r="B332" s="1"/>
       <c r="C332" s="64"/>
-      <c r="D332" s="105"/>
-      <c r="E332" s="104"/>
-      <c r="F332" s="104"/>
-      <c r="G332" s="104"/>
-      <c r="H332" s="95"/>
+      <c r="D332" s="103"/>
+      <c r="E332" s="102"/>
+      <c r="F332" s="102"/>
+      <c r="G332" s="102"/>
+      <c r="H332" s="93"/>
     </row>
     <row r="333" spans="2:8">
       <c r="B333" s="1"/>
       <c r="C333" s="64"/>
-      <c r="D333" s="105"/>
-      <c r="E333" s="104"/>
-      <c r="F333" s="104"/>
-      <c r="G333" s="104"/>
-      <c r="H333" s="95"/>
+      <c r="D333" s="103"/>
+      <c r="E333" s="102"/>
+      <c r="F333" s="102"/>
+      <c r="G333" s="102"/>
+      <c r="H333" s="93"/>
     </row>
     <row r="334" spans="2:8">
       <c r="B334" s="1"/>
       <c r="C334" s="64"/>
-      <c r="D334" s="105"/>
-      <c r="E334" s="104"/>
-      <c r="F334" s="104"/>
-      <c r="G334" s="104"/>
-      <c r="H334" s="95"/>
+      <c r="D334" s="103"/>
+      <c r="E334" s="102"/>
+      <c r="F334" s="102"/>
+      <c r="G334" s="102"/>
+      <c r="H334" s="93"/>
     </row>
     <row r="335" spans="2:8">
       <c r="B335" s="1"/>
       <c r="C335" s="64"/>
-      <c r="D335" s="105"/>
-      <c r="E335" s="104"/>
-      <c r="F335" s="104"/>
-      <c r="G335" s="104"/>
-      <c r="H335" s="95"/>
+      <c r="D335" s="103"/>
+      <c r="E335" s="102"/>
+      <c r="F335" s="102"/>
+      <c r="G335" s="102"/>
+      <c r="H335" s="93"/>
     </row>
     <row r="336" spans="2:8">
       <c r="B336" s="1"/>
       <c r="C336" s="64"/>
-      <c r="D336" s="105"/>
-      <c r="E336" s="104"/>
-      <c r="F336" s="104"/>
-      <c r="G336" s="104"/>
-      <c r="H336" s="95"/>
+      <c r="D336" s="103"/>
+      <c r="E336" s="102"/>
+      <c r="F336" s="102"/>
+      <c r="G336" s="102"/>
+      <c r="H336" s="93"/>
     </row>
     <row r="337" spans="2:8">
       <c r="B337" s="1"/>
       <c r="C337" s="64"/>
-      <c r="D337" s="105"/>
-      <c r="E337" s="104"/>
-      <c r="F337" s="104"/>
-      <c r="G337" s="104"/>
-      <c r="H337" s="95"/>
+      <c r="D337" s="103"/>
+      <c r="E337" s="102"/>
+      <c r="F337" s="102"/>
+      <c r="G337" s="102"/>
+      <c r="H337" s="93"/>
     </row>
     <row r="338" spans="2:8">
       <c r="B338" s="1"/>
       <c r="C338" s="64"/>
-      <c r="D338" s="105"/>
-      <c r="E338" s="104"/>
-      <c r="F338" s="104"/>
-      <c r="G338" s="104"/>
-      <c r="H338" s="95"/>
+      <c r="D338" s="103"/>
+      <c r="E338" s="102"/>
+      <c r="F338" s="102"/>
+      <c r="G338" s="102"/>
+      <c r="H338" s="93"/>
     </row>
     <row r="339" spans="2:8">
       <c r="B339" s="1"/>
       <c r="C339" s="64"/>
-      <c r="D339" s="105"/>
-      <c r="E339" s="104"/>
-      <c r="F339" s="104"/>
-      <c r="G339" s="104"/>
-      <c r="H339" s="95"/>
+      <c r="D339" s="103"/>
+      <c r="E339" s="102"/>
+      <c r="F339" s="102"/>
+      <c r="G339" s="102"/>
+      <c r="H339" s="93"/>
     </row>
     <row r="340" spans="2:8">
       <c r="B340" s="1"/>
       <c r="C340" s="64"/>
-      <c r="D340" s="105"/>
-      <c r="E340" s="104"/>
-      <c r="F340" s="104"/>
-      <c r="G340" s="104"/>
-      <c r="H340" s="95"/>
+      <c r="D340" s="103"/>
+      <c r="E340" s="102"/>
+      <c r="F340" s="102"/>
+      <c r="G340" s="102"/>
+      <c r="H340" s="93"/>
     </row>
     <row r="341" spans="2:8">
       <c r="B341" s="1"/>
       <c r="C341" s="64"/>
-      <c r="D341" s="105"/>
-      <c r="E341" s="104"/>
-      <c r="F341" s="104"/>
-      <c r="G341" s="104"/>
-      <c r="H341" s="95"/>
+      <c r="D341" s="103"/>
+      <c r="E341" s="102"/>
+      <c r="F341" s="102"/>
+      <c r="G341" s="102"/>
+      <c r="H341" s="93"/>
     </row>
     <row r="342" spans="2:8">
       <c r="B342" s="1"/>
       <c r="C342" s="64"/>
-      <c r="D342" s="105"/>
-      <c r="E342" s="104"/>
-      <c r="F342" s="104"/>
-      <c r="G342" s="104"/>
-      <c r="H342" s="95"/>
+      <c r="D342" s="103"/>
+      <c r="E342" s="102"/>
+      <c r="F342" s="102"/>
+      <c r="G342" s="102"/>
+      <c r="H342" s="93"/>
     </row>
     <row r="343" spans="2:8">
       <c r="B343" s="1"/>
       <c r="C343" s="64"/>
-      <c r="D343" s="105"/>
-      <c r="E343" s="104"/>
-      <c r="F343" s="104"/>
-      <c r="G343" s="104"/>
-      <c r="H343" s="95"/>
+      <c r="D343" s="103"/>
+      <c r="E343" s="102"/>
+      <c r="F343" s="102"/>
+      <c r="G343" s="102"/>
+      <c r="H343" s="93"/>
     </row>
     <row r="344" spans="2:8">
       <c r="B344" s="1"/>
       <c r="C344" s="64"/>
-      <c r="D344" s="105"/>
-      <c r="E344" s="104"/>
-      <c r="F344" s="104"/>
-      <c r="G344" s="104"/>
-      <c r="H344" s="95"/>
+      <c r="D344" s="103"/>
+      <c r="E344" s="102"/>
+      <c r="F344" s="102"/>
+      <c r="G344" s="102"/>
+      <c r="H344" s="93"/>
     </row>
     <row r="345" spans="2:8">
       <c r="B345" s="1"/>
       <c r="C345" s="64"/>
-      <c r="D345" s="105"/>
-      <c r="E345" s="104"/>
-      <c r="F345" s="104"/>
-      <c r="G345" s="104"/>
-      <c r="H345" s="95"/>
+      <c r="D345" s="103"/>
+      <c r="E345" s="102"/>
+      <c r="F345" s="102"/>
+      <c r="G345" s="102"/>
+      <c r="H345" s="93"/>
     </row>
     <row r="346" spans="2:8">
       <c r="B346" s="1"/>
       <c r="C346" s="64"/>
-      <c r="D346" s="105"/>
-      <c r="E346" s="104"/>
-      <c r="F346" s="104"/>
-      <c r="G346" s="104"/>
-      <c r="H346" s="95"/>
+      <c r="D346" s="103"/>
+      <c r="E346" s="102"/>
+      <c r="F346" s="102"/>
+      <c r="G346" s="102"/>
+      <c r="H346" s="93"/>
     </row>
     <row r="347" spans="2:8">
       <c r="B347" s="1"/>
       <c r="C347" s="64"/>
-      <c r="D347" s="105"/>
-      <c r="E347" s="104"/>
-      <c r="F347" s="104"/>
-      <c r="G347" s="104"/>
-      <c r="H347" s="95"/>
+      <c r="D347" s="103"/>
+      <c r="E347" s="102"/>
+      <c r="F347" s="102"/>
+      <c r="G347" s="102"/>
+      <c r="H347" s="93"/>
     </row>
     <row r="348" spans="2:8">
       <c r="B348" s="1"/>
       <c r="C348" s="64"/>
-      <c r="D348" s="105"/>
-      <c r="E348" s="104"/>
-      <c r="F348" s="104"/>
-      <c r="G348" s="104"/>
-      <c r="H348" s="95"/>
+      <c r="D348" s="103"/>
+      <c r="E348" s="102"/>
+      <c r="F348" s="102"/>
+      <c r="G348" s="102"/>
+      <c r="H348" s="93"/>
     </row>
     <row r="349" spans="2:8">
       <c r="B349" s="1"/>
       <c r="C349" s="64"/>
-      <c r="D349" s="105"/>
-      <c r="E349" s="104"/>
-      <c r="F349" s="104"/>
-      <c r="G349" s="104"/>
-      <c r="H349" s="95"/>
+      <c r="D349" s="103"/>
+      <c r="E349" s="102"/>
+      <c r="F349" s="102"/>
+      <c r="G349" s="102"/>
+      <c r="H349" s="93"/>
     </row>
     <row r="350" spans="2:8">
       <c r="B350" s="1"/>
       <c r="C350" s="64"/>
-      <c r="D350" s="105"/>
-      <c r="E350" s="104"/>
-      <c r="F350" s="104"/>
-      <c r="G350" s="104"/>
-      <c r="H350" s="95"/>
+      <c r="D350" s="103"/>
+      <c r="E350" s="102"/>
+      <c r="F350" s="102"/>
+      <c r="G350" s="102"/>
+      <c r="H350" s="93"/>
     </row>
     <row r="351" spans="2:8">
       <c r="B351" s="1"/>
       <c r="C351" s="64"/>
-      <c r="D351" s="105"/>
-      <c r="E351" s="104"/>
-      <c r="F351" s="104"/>
-      <c r="G351" s="104"/>
-      <c r="H351" s="95"/>
+      <c r="D351" s="103"/>
+      <c r="E351" s="102"/>
+      <c r="F351" s="102"/>
+      <c r="G351" s="102"/>
+      <c r="H351" s="93"/>
     </row>
     <row r="352" spans="2:8">
       <c r="B352" s="1"/>
       <c r="C352" s="64"/>
-      <c r="D352" s="105"/>
-      <c r="E352" s="104"/>
-      <c r="F352" s="104"/>
-      <c r="G352" s="104"/>
-      <c r="H352" s="95"/>
+      <c r="D352" s="103"/>
+      <c r="E352" s="102"/>
+      <c r="F352" s="102"/>
+      <c r="G352" s="102"/>
+      <c r="H352" s="93"/>
     </row>
     <row r="353" spans="2:8">
       <c r="B353" s="1"/>
       <c r="C353" s="64"/>
-      <c r="D353" s="105"/>
-      <c r="E353" s="104"/>
-      <c r="F353" s="104"/>
-      <c r="G353" s="104"/>
-      <c r="H353" s="95"/>
+      <c r="D353" s="103"/>
+      <c r="E353" s="102"/>
+      <c r="F353" s="102"/>
+      <c r="G353" s="102"/>
+      <c r="H353" s="93"/>
     </row>
     <row r="354" spans="2:8">
       <c r="B354" s="1"/>
       <c r="C354" s="64"/>
-      <c r="D354" s="105"/>
-      <c r="E354" s="104"/>
-      <c r="F354" s="104"/>
-      <c r="G354" s="104"/>
-      <c r="H354" s="95"/>
+      <c r="D354" s="103"/>
+      <c r="E354" s="102"/>
+      <c r="F354" s="102"/>
+      <c r="G354" s="102"/>
+      <c r="H354" s="93"/>
     </row>
     <row r="355" spans="2:8">
       <c r="B355" s="1"/>
       <c r="C355" s="64"/>
-      <c r="D355" s="105"/>
-      <c r="E355" s="104"/>
-      <c r="F355" s="104"/>
-      <c r="G355" s="104"/>
-      <c r="H355" s="95"/>
+      <c r="D355" s="103"/>
+      <c r="E355" s="102"/>
+      <c r="F355" s="102"/>
+      <c r="G355" s="102"/>
+      <c r="H355" s="93"/>
     </row>
     <row r="356" spans="2:8">
       <c r="B356" s="1"/>
       <c r="C356" s="64"/>
-      <c r="D356" s="105"/>
-      <c r="E356" s="104"/>
-      <c r="F356" s="104"/>
-      <c r="G356" s="104"/>
-      <c r="H356" s="95"/>
+      <c r="D356" s="103"/>
+      <c r="E356" s="102"/>
+      <c r="F356" s="102"/>
+      <c r="G356" s="102"/>
+      <c r="H356" s="93"/>
     </row>
     <row r="357" spans="2:8">
       <c r="B357" s="1"/>
       <c r="C357" s="64"/>
-      <c r="D357" s="105"/>
-      <c r="E357" s="104"/>
-      <c r="F357" s="104"/>
-      <c r="G357" s="104"/>
-      <c r="H357" s="95"/>
+      <c r="D357" s="103"/>
+      <c r="E357" s="102"/>
+      <c r="F357" s="102"/>
+      <c r="G357" s="102"/>
+      <c r="H357" s="93"/>
     </row>
     <row r="358" spans="2:8">
       <c r="B358" s="1"/>
       <c r="C358" s="64"/>
-      <c r="D358" s="105"/>
-      <c r="E358" s="104"/>
-      <c r="F358" s="104"/>
-      <c r="G358" s="104"/>
-      <c r="H358" s="95"/>
+      <c r="D358" s="103"/>
+      <c r="E358" s="102"/>
+      <c r="F358" s="102"/>
+      <c r="G358" s="102"/>
+      <c r="H358" s="93"/>
     </row>
     <row r="359" spans="2:8">
       <c r="B359" s="1"/>
       <c r="C359" s="64"/>
-      <c r="D359" s="105"/>
-      <c r="E359" s="104"/>
-      <c r="F359" s="104"/>
-      <c r="G359" s="104"/>
-      <c r="H359" s="95"/>
+      <c r="D359" s="103"/>
+      <c r="E359" s="102"/>
+      <c r="F359" s="102"/>
+      <c r="G359" s="102"/>
+      <c r="H359" s="93"/>
     </row>
     <row r="360" spans="2:8">
       <c r="B360" s="1"/>
       <c r="C360" s="64"/>
-      <c r="D360" s="105"/>
-      <c r="E360" s="104"/>
-      <c r="F360" s="104"/>
-      <c r="G360" s="104"/>
-      <c r="H360" s="95"/>
+      <c r="D360" s="103"/>
+      <c r="E360" s="102"/>
+      <c r="F360" s="102"/>
+      <c r="G360" s="102"/>
+      <c r="H360" s="93"/>
     </row>
     <row r="361" spans="2:8">
       <c r="B361" s="1"/>
       <c r="C361" s="64"/>
-      <c r="D361" s="105"/>
-      <c r="E361" s="104"/>
-      <c r="F361" s="104"/>
-      <c r="G361" s="104"/>
-      <c r="H361" s="95"/>
+      <c r="D361" s="103"/>
+      <c r="E361" s="102"/>
+      <c r="F361" s="102"/>
+      <c r="G361" s="102"/>
+      <c r="H361" s="93"/>
     </row>
     <row r="362" spans="2:8">
       <c r="B362" s="1"/>
       <c r="C362" s="64"/>
-      <c r="D362" s="105"/>
-      <c r="E362" s="104"/>
-      <c r="F362" s="104"/>
-      <c r="G362" s="104"/>
-      <c r="H362" s="95"/>
+      <c r="D362" s="103"/>
+      <c r="E362" s="102"/>
+      <c r="F362" s="102"/>
+      <c r="G362" s="102"/>
+      <c r="H362" s="93"/>
     </row>
     <row r="363" spans="2:8">
       <c r="B363" s="1"/>
       <c r="C363" s="64"/>
-      <c r="D363" s="105"/>
-      <c r="E363" s="104"/>
-      <c r="F363" s="104"/>
-      <c r="G363" s="104"/>
-      <c r="H363" s="95"/>
+      <c r="D363" s="103"/>
+      <c r="E363" s="102"/>
+      <c r="F363" s="102"/>
+      <c r="G363" s="102"/>
+      <c r="H363" s="93"/>
     </row>
     <row r="364" spans="2:8">
       <c r="B364" s="1"/>
       <c r="C364" s="64"/>
-      <c r="D364" s="105"/>
-      <c r="E364" s="104"/>
-      <c r="F364" s="104"/>
-      <c r="G364" s="104"/>
-      <c r="H364" s="95"/>
+      <c r="D364" s="103"/>
+      <c r="E364" s="102"/>
+      <c r="F364" s="102"/>
+      <c r="G364" s="102"/>
+      <c r="H364" s="93"/>
     </row>
     <row r="365" spans="2:8">
       <c r="B365" s="1"/>
       <c r="C365" s="64"/>
-      <c r="D365" s="105"/>
-      <c r="E365" s="104"/>
-      <c r="F365" s="104"/>
-      <c r="G365" s="104"/>
-      <c r="H365" s="95"/>
+      <c r="D365" s="103"/>
+      <c r="E365" s="102"/>
+      <c r="F365" s="102"/>
+      <c r="G365" s="102"/>
+      <c r="H365" s="93"/>
     </row>
     <row r="366" spans="2:8">
       <c r="B366" s="1"/>
       <c r="C366" s="64"/>
-      <c r="D366" s="105"/>
-      <c r="E366" s="104"/>
-      <c r="F366" s="104"/>
-      <c r="G366" s="104"/>
-      <c r="H366" s="95"/>
+      <c r="D366" s="103"/>
+      <c r="E366" s="102"/>
+      <c r="F366" s="102"/>
+      <c r="G366" s="102"/>
+      <c r="H366" s="93"/>
     </row>
     <row r="367" spans="2:8">
       <c r="B367" s="1"/>
       <c r="C367" s="64"/>
-      <c r="D367" s="105"/>
-      <c r="E367" s="104"/>
-      <c r="F367" s="104"/>
-      <c r="G367" s="104"/>
-      <c r="H367" s="95"/>
+      <c r="D367" s="103"/>
+      <c r="E367" s="102"/>
+      <c r="F367" s="102"/>
+      <c r="G367" s="102"/>
+      <c r="H367" s="93"/>
     </row>
     <row r="368" spans="2:8">
       <c r="B368" s="1"/>
       <c r="C368" s="64"/>
-      <c r="D368" s="105"/>
-      <c r="E368" s="104"/>
-      <c r="F368" s="104"/>
-      <c r="G368" s="104"/>
-      <c r="H368" s="95"/>
+      <c r="D368" s="103"/>
+      <c r="E368" s="102"/>
+      <c r="F368" s="102"/>
+      <c r="G368" s="102"/>
+      <c r="H368" s="93"/>
     </row>
     <row r="369" spans="2:8">
       <c r="B369" s="1"/>
       <c r="C369" s="64"/>
-      <c r="D369" s="105"/>
-      <c r="E369" s="104"/>
-      <c r="F369" s="104"/>
-      <c r="G369" s="104"/>
-      <c r="H369" s="95"/>
+      <c r="D369" s="103"/>
+      <c r="E369" s="102"/>
+      <c r="F369" s="102"/>
+      <c r="G369" s="102"/>
+      <c r="H369" s="93"/>
     </row>
     <row r="370" spans="2:8">
       <c r="B370" s="1"/>
       <c r="C370" s="64"/>
-      <c r="D370" s="105"/>
-      <c r="E370" s="104"/>
-      <c r="F370" s="104"/>
-      <c r="G370" s="104"/>
-      <c r="H370" s="95"/>
+      <c r="D370" s="103"/>
+      <c r="E370" s="102"/>
+      <c r="F370" s="102"/>
+      <c r="G370" s="102"/>
+      <c r="H370" s="93"/>
     </row>
     <row r="371" spans="2:8">
       <c r="B371" s="1"/>
       <c r="C371" s="64"/>
-      <c r="D371" s="105"/>
-      <c r="E371" s="104"/>
-      <c r="F371" s="104"/>
-      <c r="G371" s="104"/>
-      <c r="H371" s="95"/>
+      <c r="D371" s="103"/>
+      <c r="E371" s="102"/>
+      <c r="F371" s="102"/>
+      <c r="G371" s="102"/>
+      <c r="H371" s="93"/>
     </row>
     <row r="372" spans="2:8">
       <c r="B372" s="1"/>
       <c r="C372" s="64"/>
-      <c r="D372" s="105"/>
-      <c r="E372" s="104"/>
-      <c r="F372" s="104"/>
-      <c r="G372" s="104"/>
-      <c r="H372" s="95"/>
+      <c r="D372" s="103"/>
+      <c r="E372" s="102"/>
+      <c r="F372" s="102"/>
+      <c r="G372" s="102"/>
+      <c r="H372" s="93"/>
     </row>
     <row r="373" spans="2:8">
       <c r="B373" s="1"/>
       <c r="C373" s="64"/>
-      <c r="D373" s="105"/>
-      <c r="E373" s="104"/>
-      <c r="F373" s="104"/>
-      <c r="G373" s="104"/>
-      <c r="H373" s="95"/>
+      <c r="D373" s="103"/>
+      <c r="E373" s="102"/>
+      <c r="F373" s="102"/>
+      <c r="G373" s="102"/>
+      <c r="H373" s="93"/>
     </row>
     <row r="374" spans="2:8">
       <c r="B374" s="1"/>
       <c r="C374" s="64"/>
-      <c r="D374" s="105"/>
-      <c r="E374" s="104"/>
-      <c r="F374" s="104"/>
-      <c r="G374" s="104"/>
-      <c r="H374" s="95"/>
+      <c r="D374" s="103"/>
+      <c r="E374" s="102"/>
+      <c r="F374" s="102"/>
+      <c r="G374" s="102"/>
+      <c r="H374" s="93"/>
     </row>
     <row r="375" spans="2:8">
       <c r="B375" s="1"/>
       <c r="C375" s="64"/>
-      <c r="D375" s="105"/>
-      <c r="E375" s="104"/>
-      <c r="F375" s="104"/>
-      <c r="G375" s="104"/>
-      <c r="H375" s="95"/>
+      <c r="D375" s="103"/>
+      <c r="E375" s="102"/>
+      <c r="F375" s="102"/>
+      <c r="G375" s="102"/>
+      <c r="H375" s="93"/>
     </row>
     <row r="376" spans="2:8">
       <c r="B376" s="1"/>
       <c r="C376" s="64"/>
-      <c r="D376" s="105"/>
-      <c r="E376" s="104"/>
-      <c r="F376" s="104"/>
-      <c r="G376" s="104"/>
-      <c r="H376" s="95"/>
+      <c r="D376" s="103"/>
+      <c r="E376" s="102"/>
+      <c r="F376" s="102"/>
+      <c r="G376" s="102"/>
+      <c r="H376" s="93"/>
     </row>
     <row r="377" spans="2:8">
       <c r="B377" s="1"/>
       <c r="C377" s="64"/>
-      <c r="D377" s="105"/>
-      <c r="E377" s="104"/>
-      <c r="F377" s="104"/>
-      <c r="G377" s="104"/>
-      <c r="H377" s="95"/>
+      <c r="D377" s="103"/>
+      <c r="E377" s="102"/>
+      <c r="F377" s="102"/>
+      <c r="G377" s="102"/>
+      <c r="H377" s="93"/>
     </row>
     <row r="378" spans="2:8">
       <c r="B378" s="1"/>
       <c r="C378" s="64"/>
-      <c r="D378" s="105"/>
-      <c r="E378" s="104"/>
-      <c r="F378" s="104"/>
-      <c r="G378" s="104"/>
-      <c r="H378" s="95"/>
+      <c r="D378" s="103"/>
+      <c r="E378" s="102"/>
+      <c r="F378" s="102"/>
+      <c r="G378" s="102"/>
+      <c r="H378" s="93"/>
     </row>
     <row r="379" spans="2:8">
       <c r="B379" s="1"/>
       <c r="C379" s="64"/>
-      <c r="D379" s="105"/>
-      <c r="E379" s="104"/>
-      <c r="F379" s="104"/>
-      <c r="G379" s="104"/>
-      <c r="H379" s="95"/>
+      <c r="D379" s="103"/>
+      <c r="E379" s="102"/>
+      <c r="F379" s="102"/>
+      <c r="G379" s="102"/>
+      <c r="H379" s="93"/>
     </row>
     <row r="380" spans="2:8">
       <c r="B380" s="1"/>
       <c r="C380" s="64"/>
-      <c r="D380" s="105"/>
-      <c r="E380" s="104"/>
-      <c r="F380" s="104"/>
-      <c r="G380" s="104"/>
-      <c r="H380" s="95"/>
+      <c r="D380" s="103"/>
+      <c r="E380" s="102"/>
+      <c r="F380" s="102"/>
+      <c r="G380" s="102"/>
+      <c r="H380" s="93"/>
     </row>
     <row r="381" spans="2:8">
       <c r="B381" s="1"/>
       <c r="C381" s="64"/>
-      <c r="D381" s="105"/>
-      <c r="E381" s="104"/>
-      <c r="F381" s="104"/>
-      <c r="G381" s="104"/>
-      <c r="H381" s="95"/>
+      <c r="D381" s="103"/>
+      <c r="E381" s="102"/>
+      <c r="F381" s="102"/>
+      <c r="G381" s="102"/>
+      <c r="H381" s="93"/>
     </row>
     <row r="382" spans="2:8">
       <c r="B382" s="1"/>
       <c r="C382" s="64"/>
-      <c r="D382" s="105"/>
-      <c r="E382" s="104"/>
-      <c r="F382" s="104"/>
-      <c r="G382" s="104"/>
-      <c r="H382" s="95"/>
+      <c r="D382" s="103"/>
+      <c r="E382" s="102"/>
+      <c r="F382" s="102"/>
+      <c r="G382" s="102"/>
+      <c r="H382" s="93"/>
     </row>
     <row r="383" spans="2:8">
       <c r="B383" s="1"/>
       <c r="C383" s="64"/>
-      <c r="D383" s="105"/>
-      <c r="E383" s="104"/>
-      <c r="F383" s="104"/>
-      <c r="G383" s="104"/>
-      <c r="H383" s="95"/>
+      <c r="D383" s="103"/>
+      <c r="E383" s="102"/>
+      <c r="F383" s="102"/>
+      <c r="G383" s="102"/>
+      <c r="H383" s="93"/>
     </row>
     <row r="384" spans="2:8">
       <c r="B384" s="1"/>
       <c r="C384" s="64"/>
-      <c r="D384" s="105"/>
-      <c r="E384" s="104"/>
-      <c r="F384" s="104"/>
-      <c r="G384" s="104"/>
-      <c r="H384" s="95"/>
+      <c r="D384" s="103"/>
+      <c r="E384" s="102"/>
+      <c r="F384" s="102"/>
+      <c r="G384" s="102"/>
+      <c r="H384" s="93"/>
     </row>
     <row r="385" spans="2:8">
       <c r="B385" s="1"/>
       <c r="C385" s="64"/>
-      <c r="D385" s="105"/>
-      <c r="E385" s="104"/>
-      <c r="F385" s="104"/>
-      <c r="G385" s="104"/>
-      <c r="H385" s="95"/>
+      <c r="D385" s="103"/>
+      <c r="E385" s="102"/>
+      <c r="F385" s="102"/>
+      <c r="G385" s="102"/>
+      <c r="H385" s="93"/>
     </row>
     <row r="386" spans="2:8">
       <c r="B386" s="1"/>
       <c r="C386" s="64"/>
-      <c r="D386" s="105"/>
-      <c r="E386" s="104"/>
-      <c r="F386" s="104"/>
-      <c r="G386" s="104"/>
-      <c r="H386" s="95"/>
+      <c r="D386" s="103"/>
+      <c r="E386" s="102"/>
+      <c r="F386" s="102"/>
+      <c r="G386" s="102"/>
+      <c r="H386" s="93"/>
     </row>
     <row r="387" spans="2:8">
       <c r="B387" s="1"/>
       <c r="C387" s="64"/>
-      <c r="D387" s="105"/>
-      <c r="E387" s="104"/>
-      <c r="F387" s="104"/>
-      <c r="G387" s="104"/>
-      <c r="H387" s="95"/>
+      <c r="D387" s="103"/>
+      <c r="E387" s="102"/>
+      <c r="F387" s="102"/>
+      <c r="G387" s="102"/>
+      <c r="H387" s="93"/>
     </row>
     <row r="388" spans="2:8">
       <c r="B388" s="1"/>
       <c r="C388" s="64"/>
-      <c r="D388" s="105"/>
-      <c r="E388" s="104"/>
-      <c r="F388" s="104"/>
-      <c r="G388" s="104"/>
-      <c r="H388" s="95"/>
+      <c r="D388" s="103"/>
+      <c r="E388" s="102"/>
+      <c r="F388" s="102"/>
+      <c r="G388" s="102"/>
+      <c r="H388" s="93"/>
     </row>
     <row r="389" spans="2:8">
       <c r="B389" s="1"/>
       <c r="C389" s="64"/>
-      <c r="D389" s="105"/>
-      <c r="E389" s="104"/>
-      <c r="F389" s="104"/>
-      <c r="G389" s="104"/>
-      <c r="H389" s="95"/>
+      <c r="D389" s="103"/>
+      <c r="E389" s="102"/>
+      <c r="F389" s="102"/>
+      <c r="G389" s="102"/>
+      <c r="H389" s="93"/>
     </row>
     <row r="390" spans="2:8">
       <c r="B390" s="1"/>
       <c r="C390" s="64"/>
-      <c r="D390" s="105"/>
-      <c r="E390" s="104"/>
-      <c r="F390" s="104"/>
-      <c r="G390" s="104"/>
-      <c r="H390" s="95"/>
+      <c r="D390" s="103"/>
+      <c r="E390" s="102"/>
+      <c r="F390" s="102"/>
+      <c r="G390" s="102"/>
+      <c r="H390" s="93"/>
     </row>
     <row r="391" spans="2:8">
       <c r="B391" s="1"/>
       <c r="C391" s="64"/>
-      <c r="D391" s="105"/>
-      <c r="E391" s="104"/>
-      <c r="F391" s="104"/>
-      <c r="G391" s="104"/>
-      <c r="H391" s="95"/>
+      <c r="D391" s="103"/>
+      <c r="E391" s="102"/>
+      <c r="F391" s="102"/>
+      <c r="G391" s="102"/>
+      <c r="H391" s="93"/>
     </row>
     <row r="392" spans="2:8">
       <c r="B392" s="1"/>
       <c r="C392" s="64"/>
-      <c r="D392" s="105"/>
-      <c r="E392" s="104"/>
-      <c r="F392" s="104"/>
-      <c r="G392" s="104"/>
-      <c r="H392" s="95"/>
+      <c r="D392" s="103"/>
+      <c r="E392" s="102"/>
+      <c r="F392" s="102"/>
+      <c r="G392" s="102"/>
+      <c r="H392" s="93"/>
     </row>
     <row r="393" spans="2:8">
       <c r="B393" s="1"/>
       <c r="C393" s="64"/>
-      <c r="D393" s="105"/>
-      <c r="E393" s="104"/>
-      <c r="F393" s="104"/>
-      <c r="G393" s="104"/>
-      <c r="H393" s="95"/>
+      <c r="D393" s="103"/>
+      <c r="E393" s="102"/>
+      <c r="F393" s="102"/>
+      <c r="G393" s="102"/>
+      <c r="H393" s="93"/>
     </row>
     <row r="394" spans="2:8">
       <c r="B394" s="1"/>
       <c r="C394" s="64"/>
-      <c r="D394" s="105"/>
-      <c r="E394" s="104"/>
-      <c r="F394" s="104"/>
-      <c r="G394" s="104"/>
-      <c r="H394" s="95"/>
+      <c r="D394" s="103"/>
+      <c r="E394" s="102"/>
+      <c r="F394" s="102"/>
+      <c r="G394" s="102"/>
+      <c r="H394" s="93"/>
     </row>
     <row r="395" spans="2:8">
       <c r="B395" s="1"/>
       <c r="C395" s="64"/>
-      <c r="D395" s="105"/>
-      <c r="E395" s="104"/>
-      <c r="F395" s="104"/>
-      <c r="G395" s="104"/>
-      <c r="H395" s="95"/>
+      <c r="D395" s="103"/>
+      <c r="E395" s="102"/>
+      <c r="F395" s="102"/>
+      <c r="G395" s="102"/>
+      <c r="H395" s="93"/>
     </row>
     <row r="396" spans="2:8">
       <c r="B396" s="1"/>
       <c r="C396" s="64"/>
-      <c r="D396" s="105"/>
-      <c r="E396" s="104"/>
-      <c r="F396" s="104"/>
-      <c r="G396" s="104"/>
-      <c r="H396" s="95"/>
+      <c r="D396" s="103"/>
+      <c r="E396" s="102"/>
+      <c r="F396" s="102"/>
+      <c r="G396" s="102"/>
+      <c r="H396" s="93"/>
     </row>
     <row r="397" spans="2:8">
       <c r="B397" s="1"/>
       <c r="C397" s="64"/>
-      <c r="D397" s="105"/>
-      <c r="E397" s="104"/>
-      <c r="F397" s="104"/>
-      <c r="G397" s="104"/>
-      <c r="H397" s="95"/>
+      <c r="D397" s="103"/>
+      <c r="E397" s="102"/>
+      <c r="F397" s="102"/>
+      <c r="G397" s="102"/>
+      <c r="H397" s="93"/>
     </row>
     <row r="398" spans="2:8">
       <c r="B398" s="1"/>
       <c r="C398" s="64"/>
-      <c r="D398" s="105"/>
-      <c r="E398" s="104"/>
-      <c r="F398" s="104"/>
-      <c r="G398" s="104"/>
-      <c r="H398" s="95"/>
+      <c r="D398" s="103"/>
+      <c r="E398" s="102"/>
+      <c r="F398" s="102"/>
+      <c r="G398" s="102"/>
+      <c r="H398" s="93"/>
     </row>
     <row r="399" spans="2:8">
       <c r="B399" s="1"/>
       <c r="C399" s="64"/>
-      <c r="D399" s="105"/>
-      <c r="E399" s="104"/>
-      <c r="F399" s="104"/>
-      <c r="G399" s="104"/>
-      <c r="H399" s="95"/>
+      <c r="D399" s="103"/>
+      <c r="E399" s="102"/>
+      <c r="F399" s="102"/>
+      <c r="G399" s="102"/>
+      <c r="H399" s="93"/>
     </row>
     <row r="400" spans="2:8">
       <c r="B400" s="1"/>
       <c r="C400" s="64"/>
-      <c r="D400" s="105"/>
-      <c r="E400" s="104"/>
-      <c r="F400" s="104"/>
-      <c r="G400" s="104"/>
-      <c r="H400" s="95"/>
+      <c r="D400" s="103"/>
+      <c r="E400" s="102"/>
+      <c r="F400" s="102"/>
+      <c r="G400" s="102"/>
+      <c r="H400" s="93"/>
     </row>
     <row r="401" spans="2:8">
       <c r="B401" s="1"/>
       <c r="C401" s="64"/>
-      <c r="D401" s="105"/>
-      <c r="E401" s="104"/>
-      <c r="F401" s="104"/>
-      <c r="G401" s="104"/>
-      <c r="H401" s="95"/>
+      <c r="D401" s="103"/>
+      <c r="E401" s="102"/>
+      <c r="F401" s="102"/>
+      <c r="G401" s="102"/>
+      <c r="H401" s="93"/>
     </row>
     <row r="402" spans="2:8">
       <c r="B402" s="1"/>
       <c r="C402" s="64"/>
-      <c r="D402" s="105"/>
-      <c r="E402" s="104"/>
-      <c r="F402" s="104"/>
-      <c r="G402" s="104"/>
-      <c r="H402" s="95"/>
+      <c r="D402" s="103"/>
+      <c r="E402" s="102"/>
+      <c r="F402" s="102"/>
+      <c r="G402" s="102"/>
+      <c r="H402" s="93"/>
     </row>
     <row r="403" spans="2:8">
       <c r="B403" s="1"/>
       <c r="C403" s="64"/>
-      <c r="D403" s="105"/>
-      <c r="E403" s="104"/>
-      <c r="F403" s="104"/>
-      <c r="G403" s="104"/>
-      <c r="H403" s="95"/>
+      <c r="D403" s="103"/>
+      <c r="E403" s="102"/>
+      <c r="F403" s="102"/>
+      <c r="G403" s="102"/>
+      <c r="H403" s="93"/>
     </row>
     <row r="404" spans="2:8">
       <c r="B404" s="1"/>
       <c r="C404" s="64"/>
-      <c r="D404" s="105"/>
-      <c r="E404" s="104"/>
-      <c r="F404" s="104"/>
-      <c r="G404" s="104"/>
-      <c r="H404" s="95"/>
+      <c r="D404" s="103"/>
+      <c r="E404" s="102"/>
+      <c r="F404" s="102"/>
+      <c r="G404" s="102"/>
+      <c r="H404" s="93"/>
     </row>
     <row r="405" spans="2:8">
       <c r="B405" s="1"/>
       <c r="C405" s="64"/>
-      <c r="D405" s="105"/>
-      <c r="E405" s="104"/>
-      <c r="F405" s="104"/>
-      <c r="G405" s="104"/>
-      <c r="H405" s="95"/>
+      <c r="D405" s="103"/>
+      <c r="E405" s="102"/>
+      <c r="F405" s="102"/>
+      <c r="G405" s="102"/>
+      <c r="H405" s="93"/>
     </row>
     <row r="406" spans="2:8">
       <c r="B406" s="1"/>
       <c r="C406" s="64"/>
-      <c r="D406" s="105"/>
-      <c r="E406" s="104"/>
-      <c r="F406" s="104"/>
-      <c r="G406" s="104"/>
-      <c r="H406" s="95"/>
+      <c r="D406" s="103"/>
+      <c r="E406" s="102"/>
+      <c r="F406" s="102"/>
+      <c r="G406" s="102"/>
+      <c r="H406" s="93"/>
     </row>
     <row r="407" spans="2:8">
       <c r="B407" s="1"/>
       <c r="C407" s="64"/>
-      <c r="D407" s="105"/>
-      <c r="E407" s="104"/>
-      <c r="F407" s="104"/>
-      <c r="G407" s="104"/>
-      <c r="H407" s="95"/>
+      <c r="D407" s="103"/>
+      <c r="E407" s="102"/>
+      <c r="F407" s="102"/>
+      <c r="G407" s="102"/>
+      <c r="H407" s="93"/>
     </row>
     <row r="408" spans="2:8">
       <c r="B408" s="1"/>
       <c r="C408" s="64"/>
-      <c r="D408" s="105"/>
-      <c r="E408" s="104"/>
-      <c r="F408" s="104"/>
-      <c r="G408" s="104"/>
-      <c r="H408" s="95"/>
+      <c r="D408" s="103"/>
+      <c r="E408" s="102"/>
+      <c r="F408" s="102"/>
+      <c r="G408" s="102"/>
+      <c r="H408" s="93"/>
     </row>
     <row r="409" spans="2:8">
       <c r="B409" s="1"/>
       <c r="C409" s="64"/>
-      <c r="D409" s="105"/>
-      <c r="E409" s="104"/>
-      <c r="F409" s="104"/>
-      <c r="G409" s="104"/>
-      <c r="H409" s="95"/>
+      <c r="D409" s="103"/>
+      <c r="E409" s="102"/>
+      <c r="F409" s="102"/>
+      <c r="G409" s="102"/>
+      <c r="H409" s="93"/>
     </row>
     <row r="410" spans="2:8">
       <c r="B410" s="1"/>
       <c r="C410" s="64"/>
-      <c r="D410" s="105"/>
-      <c r="E410" s="104"/>
-      <c r="F410" s="104"/>
-      <c r="G410" s="104"/>
-      <c r="H410" s="95"/>
+      <c r="D410" s="103"/>
+      <c r="E410" s="102"/>
+      <c r="F410" s="102"/>
+      <c r="G410" s="102"/>
+      <c r="H410" s="93"/>
     </row>
     <row r="411" spans="2:8">
       <c r="B411" s="1"/>
       <c r="C411" s="64"/>
-      <c r="D411" s="105"/>
-      <c r="E411" s="104"/>
-      <c r="F411" s="104"/>
-      <c r="G411" s="104"/>
-      <c r="H411" s="95"/>
+      <c r="D411" s="103"/>
+      <c r="E411" s="102"/>
+      <c r="F411" s="102"/>
+      <c r="G411" s="102"/>
+      <c r="H411" s="93"/>
     </row>
     <row r="412" spans="2:8">
       <c r="B412" s="1"/>
       <c r="C412" s="64"/>
-      <c r="D412" s="105"/>
-      <c r="E412" s="104"/>
-      <c r="F412" s="104"/>
-      <c r="G412" s="104"/>
-      <c r="H412" s="95"/>
+      <c r="D412" s="103"/>
+      <c r="E412" s="102"/>
+      <c r="F412" s="102"/>
+      <c r="G412" s="102"/>
+      <c r="H412" s="93"/>
     </row>
     <row r="413" spans="2:8">
       <c r="B413" s="1"/>
       <c r="C413" s="64"/>
-      <c r="D413" s="105"/>
-      <c r="E413" s="104"/>
-      <c r="F413" s="104"/>
-      <c r="G413" s="104"/>
-      <c r="H413" s="95"/>
+      <c r="D413" s="103"/>
+      <c r="E413" s="102"/>
+      <c r="F413" s="102"/>
+      <c r="G413" s="102"/>
+      <c r="H413" s="93"/>
     </row>
     <row r="414" spans="2:8">
       <c r="B414" s="1"/>
       <c r="C414" s="64"/>
-      <c r="D414" s="105"/>
-      <c r="E414" s="104"/>
-      <c r="F414" s="104"/>
-      <c r="G414" s="104"/>
-      <c r="H414" s="95"/>
+      <c r="D414" s="103"/>
+      <c r="E414" s="102"/>
+      <c r="F414" s="102"/>
+      <c r="G414" s="102"/>
+      <c r="H414" s="93"/>
     </row>
     <row r="415" spans="2:8">
       <c r="B415" s="1"/>
       <c r="C415" s="64"/>
-      <c r="D415" s="105"/>
-      <c r="E415" s="104"/>
-      <c r="F415" s="104"/>
-      <c r="G415" s="104"/>
-      <c r="H415" s="95"/>
+      <c r="D415" s="103"/>
+      <c r="E415" s="102"/>
+      <c r="F415" s="102"/>
+      <c r="G415" s="102"/>
+      <c r="H415" s="93"/>
     </row>
     <row r="416" spans="2:8">
       <c r="B416" s="1"/>
       <c r="C416" s="64"/>
-      <c r="D416" s="105"/>
-      <c r="E416" s="104"/>
-      <c r="F416" s="104"/>
-      <c r="G416" s="104"/>
-      <c r="H416" s="95"/>
+      <c r="D416" s="103"/>
+      <c r="E416" s="102"/>
+      <c r="F416" s="102"/>
+      <c r="G416" s="102"/>
+      <c r="H416" s="93"/>
     </row>
     <row r="417" spans="2:8">
       <c r="B417" s="1"/>
       <c r="C417" s="64"/>
-      <c r="D417" s="105"/>
-      <c r="E417" s="104"/>
-      <c r="F417" s="104"/>
-      <c r="G417" s="104"/>
-      <c r="H417" s="95"/>
+      <c r="D417" s="103"/>
+      <c r="E417" s="102"/>
+      <c r="F417" s="102"/>
+      <c r="G417" s="102"/>
+      <c r="H417" s="93"/>
     </row>
     <row r="418" spans="2:8">
       <c r="B418" s="1"/>
       <c r="C418" s="64"/>
-      <c r="D418" s="105"/>
-      <c r="E418" s="104"/>
-      <c r="F418" s="104"/>
-      <c r="G418" s="104"/>
-      <c r="H418" s="95"/>
+      <c r="D418" s="103"/>
+      <c r="E418" s="102"/>
+      <c r="F418" s="102"/>
+      <c r="G418" s="102"/>
+      <c r="H418" s="93"/>
     </row>
     <row r="419" spans="2:8">
       <c r="B419" s="1"/>
       <c r="C419" s="64"/>
-      <c r="D419" s="105"/>
-      <c r="E419" s="104"/>
-      <c r="F419" s="104"/>
-      <c r="G419" s="104"/>
-      <c r="H419" s="95"/>
+      <c r="D419" s="103"/>
+      <c r="E419" s="102"/>
+      <c r="F419" s="102"/>
+      <c r="G419" s="102"/>
+      <c r="H419" s="93"/>
     </row>
     <row r="420" spans="2:8">
       <c r="B420" s="1"/>
       <c r="C420" s="64"/>
-      <c r="D420" s="105"/>
-      <c r="E420" s="104"/>
-      <c r="F420" s="104"/>
-      <c r="G420" s="104"/>
-      <c r="H420" s="95"/>
+      <c r="D420" s="103"/>
+      <c r="E420" s="102"/>
+      <c r="F420" s="102"/>
+      <c r="G420" s="102"/>
+      <c r="H420" s="93"/>
     </row>
     <row r="421" spans="2:8">
       <c r="B421" s="1"/>
       <c r="C421" s="64"/>
-      <c r="D421" s="105"/>
-      <c r="E421" s="104"/>
-      <c r="F421" s="104"/>
-      <c r="G421" s="104"/>
-      <c r="H421" s="95"/>
+      <c r="D421" s="103"/>
+      <c r="E421" s="102"/>
+      <c r="F421" s="102"/>
+      <c r="G421" s="102"/>
+      <c r="H421" s="93"/>
     </row>
     <row r="422" spans="2:8">
       <c r="B422" s="1"/>
       <c r="C422" s="64"/>
-      <c r="D422" s="105"/>
-      <c r="E422" s="104"/>
-      <c r="F422" s="104"/>
-      <c r="G422" s="104"/>
-      <c r="H422" s="95"/>
+      <c r="D422" s="103"/>
+      <c r="E422" s="102"/>
+      <c r="F422" s="102"/>
+      <c r="G422" s="102"/>
+      <c r="H422" s="93"/>
     </row>
     <row r="423" spans="2:8">
       <c r="B423" s="1"/>
       <c r="C423" s="64"/>
-      <c r="D423" s="105"/>
-      <c r="E423" s="104"/>
-      <c r="F423" s="104"/>
-      <c r="G423" s="104"/>
-      <c r="H423" s="95"/>
+      <c r="D423" s="103"/>
+      <c r="E423" s="102"/>
+      <c r="F423" s="102"/>
+      <c r="G423" s="102"/>
+      <c r="H423" s="93"/>
     </row>
     <row r="424" spans="2:8">
       <c r="B424" s="1"/>
       <c r="C424" s="64"/>
-      <c r="D424" s="105"/>
-      <c r="E424" s="104"/>
-      <c r="F424" s="104"/>
-      <c r="G424" s="104"/>
-      <c r="H424" s="95"/>
+      <c r="D424" s="103"/>
+      <c r="E424" s="102"/>
+      <c r="F424" s="102"/>
+      <c r="G424" s="102"/>
+      <c r="H424" s="93"/>
     </row>
     <row r="425" spans="2:8">
       <c r="B425" s="1"/>
       <c r="C425" s="64"/>
-      <c r="D425" s="105"/>
-      <c r="E425" s="104"/>
-      <c r="F425" s="104"/>
-      <c r="G425" s="104"/>
-      <c r="H425" s="95"/>
+      <c r="D425" s="103"/>
+      <c r="E425" s="102"/>
+      <c r="F425" s="102"/>
+      <c r="G425" s="102"/>
+      <c r="H425" s="93"/>
     </row>
     <row r="426" spans="2:8">
       <c r="B426" s="1"/>
       <c r="C426" s="64"/>
-      <c r="D426" s="105"/>
-      <c r="E426" s="104"/>
-      <c r="F426" s="104"/>
-      <c r="G426" s="104"/>
-      <c r="H426" s="95"/>
+      <c r="D426" s="103"/>
+      <c r="E426" s="102"/>
+      <c r="F426" s="102"/>
+      <c r="G426" s="102"/>
+      <c r="H426" s="93"/>
     </row>
     <row r="427" spans="2:8">
       <c r="B427" s="1"/>
       <c r="C427" s="64"/>
-      <c r="D427" s="105"/>
-      <c r="E427" s="104"/>
-      <c r="F427" s="104"/>
-      <c r="G427" s="104"/>
-      <c r="H427" s="95"/>
+      <c r="D427" s="103"/>
+      <c r="E427" s="102"/>
+      <c r="F427" s="102"/>
+      <c r="G427" s="102"/>
+      <c r="H427" s="93"/>
     </row>
     <row r="428" spans="2:8">
       <c r="B428" s="1"/>
       <c r="C428" s="64"/>
-      <c r="D428" s="105"/>
-      <c r="E428" s="104"/>
-      <c r="F428" s="104"/>
-      <c r="G428" s="104"/>
-      <c r="H428" s="95"/>
+      <c r="D428" s="103"/>
+      <c r="E428" s="102"/>
+      <c r="F428" s="102"/>
+      <c r="G428" s="102"/>
+      <c r="H428" s="93"/>
     </row>
     <row r="429" spans="2:8">
       <c r="B429" s="1"/>
       <c r="C429" s="64"/>
-      <c r="D429" s="105"/>
-      <c r="E429" s="104"/>
-      <c r="F429" s="104"/>
-      <c r="G429" s="104"/>
-      <c r="H429" s="95"/>
+      <c r="D429" s="103"/>
+      <c r="E429" s="102"/>
+      <c r="F429" s="102"/>
+      <c r="G429" s="102"/>
+      <c r="H429" s="93"/>
     </row>
     <row r="430" spans="2:8">
       <c r="B430" s="1"/>
       <c r="C430" s="64"/>
-      <c r="D430" s="105"/>
-      <c r="E430" s="104"/>
-      <c r="F430" s="104"/>
-      <c r="G430" s="104"/>
-      <c r="H430" s="95"/>
+      <c r="D430" s="103"/>
+      <c r="E430" s="102"/>
+      <c r="F430" s="102"/>
+      <c r="G430" s="102"/>
+      <c r="H430" s="93"/>
     </row>
     <row r="431" spans="2:8">
       <c r="B431" s="1"/>
       <c r="C431" s="64"/>
-      <c r="D431" s="105"/>
-      <c r="E431" s="104"/>
-      <c r="F431" s="104"/>
-      <c r="G431" s="104"/>
-      <c r="H431" s="95"/>
+      <c r="D431" s="103"/>
+      <c r="E431" s="102"/>
+      <c r="F431" s="102"/>
+      <c r="G431" s="102"/>
+      <c r="H431" s="93"/>
     </row>
     <row r="432" spans="2:8">
       <c r="B432" s="1"/>
       <c r="C432" s="64"/>
-      <c r="D432" s="105"/>
-      <c r="E432" s="104"/>
-      <c r="F432" s="104"/>
-      <c r="G432" s="104"/>
-      <c r="H432" s="95"/>
+      <c r="D432" s="103"/>
+      <c r="E432" s="102"/>
+      <c r="F432" s="102"/>
+      <c r="G432" s="102"/>
+      <c r="H432" s="93"/>
     </row>
     <row r="433" spans="2:8">
       <c r="B433" s="1"/>
       <c r="C433" s="64"/>
-      <c r="D433" s="105"/>
-      <c r="E433" s="104"/>
-      <c r="F433" s="104"/>
-      <c r="G433" s="104"/>
-      <c r="H433" s="95"/>
+      <c r="D433" s="103"/>
+      <c r="E433" s="102"/>
+      <c r="F433" s="102"/>
+      <c r="G433" s="102"/>
+      <c r="H433" s="93"/>
     </row>
     <row r="434" spans="2:8">
       <c r="B434" s="1"/>
       <c r="C434" s="64"/>
-      <c r="D434" s="105"/>
-      <c r="E434" s="104"/>
-      <c r="F434" s="104"/>
-      <c r="G434" s="104"/>
-      <c r="H434" s="95"/>
+      <c r="D434" s="103"/>
+      <c r="E434" s="102"/>
+      <c r="F434" s="102"/>
+      <c r="G434" s="102"/>
+      <c r="H434" s="93"/>
     </row>
     <row r="435" spans="2:8">
       <c r="B435" s="1"/>
       <c r="C435" s="64"/>
-      <c r="D435" s="105"/>
-      <c r="E435" s="104"/>
-      <c r="F435" s="104"/>
-      <c r="G435" s="104"/>
-      <c r="H435" s="95"/>
+      <c r="D435" s="103"/>
+      <c r="E435" s="102"/>
+      <c r="F435" s="102"/>
+      <c r="G435" s="102"/>
+      <c r="H435" s="93"/>
     </row>
     <row r="436" spans="2:8">
       <c r="B436" s="1"/>
       <c r="C436" s="64"/>
-      <c r="D436" s="105"/>
-      <c r="E436" s="104"/>
-      <c r="F436" s="104"/>
-      <c r="G436" s="104"/>
-      <c r="H436" s="95"/>
+      <c r="D436" s="103"/>
+      <c r="E436" s="102"/>
+      <c r="F436" s="102"/>
+      <c r="G436" s="102"/>
+      <c r="H436" s="93"/>
     </row>
     <row r="437" spans="2:8">
       <c r="B437" s="1"/>
       <c r="C437" s="64"/>
-      <c r="D437" s="105"/>
-      <c r="E437" s="104"/>
-      <c r="F437" s="104"/>
-      <c r="G437" s="104"/>
-      <c r="H437" s="95"/>
+      <c r="D437" s="103"/>
+      <c r="E437" s="102"/>
+      <c r="F437" s="102"/>
+      <c r="G437" s="102"/>
+      <c r="H437" s="93"/>
     </row>
     <row r="438" spans="2:8">
       <c r="B438" s="1"/>
       <c r="C438" s="64"/>
-      <c r="D438" s="105"/>
-      <c r="E438" s="104"/>
-      <c r="F438" s="104"/>
-      <c r="G438" s="104"/>
-      <c r="H438" s="95"/>
+      <c r="D438" s="103"/>
+      <c r="E438" s="102"/>
+      <c r="F438" s="102"/>
+      <c r="G438" s="102"/>
+      <c r="H438" s="93"/>
     </row>
     <row r="439" spans="2:8">
       <c r="B439" s="1"/>
       <c r="C439" s="64"/>
-      <c r="D439" s="105"/>
-      <c r="E439" s="104"/>
-      <c r="F439" s="104"/>
-      <c r="G439" s="104"/>
-      <c r="H439" s="95"/>
+      <c r="D439" s="103"/>
+      <c r="E439" s="102"/>
+      <c r="F439" s="102"/>
+      <c r="G439" s="102"/>
+      <c r="H439" s="93"/>
     </row>
     <row r="440" spans="2:8">
       <c r="B440" s="1"/>
       <c r="C440" s="64"/>
-      <c r="D440" s="105"/>
-      <c r="E440" s="104"/>
-      <c r="F440" s="104"/>
-      <c r="G440" s="104"/>
-      <c r="H440" s="95"/>
+      <c r="D440" s="103"/>
+      <c r="E440" s="102"/>
+      <c r="F440" s="102"/>
+      <c r="G440" s="102"/>
+      <c r="H440" s="93"/>
     </row>
     <row r="441" spans="2:8">
       <c r="B441" s="1"/>
       <c r="C441" s="64"/>
-      <c r="D441" s="105"/>
-      <c r="E441" s="104"/>
-      <c r="F441" s="104"/>
-      <c r="G441" s="104"/>
-      <c r="H441" s="95"/>
+      <c r="D441" s="103"/>
+      <c r="E441" s="102"/>
+      <c r="F441" s="102"/>
+      <c r="G441" s="102"/>
+      <c r="H441" s="93"/>
     </row>
     <row r="442" spans="2:8">
       <c r="B442" s="1"/>
       <c r="C442" s="64"/>
-      <c r="D442" s="105"/>
-      <c r="E442" s="104"/>
-      <c r="F442" s="104"/>
-      <c r="G442" s="104"/>
-      <c r="H442" s="95"/>
+      <c r="D442" s="103"/>
+      <c r="E442" s="102"/>
+      <c r="F442" s="102"/>
+      <c r="G442" s="102"/>
+      <c r="H442" s="93"/>
     </row>
     <row r="443" spans="2:8">
       <c r="B443" s="1"/>
       <c r="C443" s="64"/>
-      <c r="D443" s="105"/>
-      <c r="E443" s="104"/>
-      <c r="F443" s="104"/>
-      <c r="G443" s="104"/>
-      <c r="H443" s="95"/>
+      <c r="D443" s="103"/>
+      <c r="E443" s="102"/>
+      <c r="F443" s="102"/>
+      <c r="G443" s="102"/>
+      <c r="H443" s="93"/>
     </row>
     <row r="444" spans="2:8">
       <c r="B444" s="1"/>
       <c r="C444" s="64"/>
-      <c r="D444" s="105"/>
-      <c r="E444" s="104"/>
-      <c r="F444" s="104"/>
-      <c r="G444" s="104"/>
-      <c r="H444" s="95"/>
+      <c r="D444" s="103"/>
+      <c r="E444" s="102"/>
+      <c r="F444" s="102"/>
+      <c r="G444" s="102"/>
+      <c r="H444" s="93"/>
     </row>
     <row r="445" spans="2:8">
       <c r="B445" s="1"/>
       <c r="C445" s="64"/>
-      <c r="D445" s="105"/>
-      <c r="E445" s="104"/>
-      <c r="F445" s="104"/>
-      <c r="G445" s="104"/>
-      <c r="H445" s="95"/>
+      <c r="D445" s="103"/>
+      <c r="E445" s="102"/>
+      <c r="F445" s="102"/>
+      <c r="G445" s="102"/>
+      <c r="H445" s="93"/>
     </row>
     <row r="446" spans="2:8">
       <c r="B446" s="1"/>
       <c r="C446" s="64"/>
-      <c r="D446" s="105"/>
-      <c r="E446" s="104"/>
-      <c r="F446" s="104"/>
-      <c r="G446" s="104"/>
-      <c r="H446" s="95"/>
+      <c r="D446" s="103"/>
+      <c r="E446" s="102"/>
+      <c r="F446" s="102"/>
+      <c r="G446" s="102"/>
+      <c r="H446" s="93"/>
     </row>
     <row r="447" spans="2:8">
       <c r="B447" s="1"/>
       <c r="C447" s="64"/>
-      <c r="D447" s="105"/>
-      <c r="E447" s="104"/>
-      <c r="F447" s="104"/>
-      <c r="G447" s="104"/>
-      <c r="H447" s="95"/>
+      <c r="D447" s="103"/>
+      <c r="E447" s="102"/>
+      <c r="F447" s="102"/>
+      <c r="G447" s="102"/>
+      <c r="H447" s="93"/>
     </row>
     <row r="448" spans="2:8">
       <c r="B448" s="1"/>
       <c r="C448" s="64"/>
-      <c r="D448" s="105"/>
-      <c r="E448" s="104"/>
-      <c r="F448" s="104"/>
-      <c r="G448" s="104"/>
-      <c r="H448" s="95"/>
+      <c r="D448" s="103"/>
+      <c r="E448" s="102"/>
+      <c r="F448" s="102"/>
+      <c r="G448" s="102"/>
+      <c r="H448" s="93"/>
     </row>
     <row r="449" spans="2:8">
       <c r="B449" s="1"/>
       <c r="C449" s="64"/>
-      <c r="D449" s="105"/>
-      <c r="E449" s="104"/>
-      <c r="F449" s="104"/>
-      <c r="G449" s="104"/>
-      <c r="H449" s="95"/>
+      <c r="D449" s="103"/>
+      <c r="E449" s="102"/>
+      <c r="F449" s="102"/>
+      <c r="G449" s="102"/>
+      <c r="H449" s="93"/>
     </row>
     <row r="450" spans="2:8">
       <c r="B450" s="1"/>
       <c r="C450" s="64"/>
-      <c r="D450" s="105"/>
-      <c r="E450" s="104"/>
-      <c r="F450" s="104"/>
-      <c r="G450" s="104"/>
-      <c r="H450" s="95"/>
+      <c r="D450" s="103"/>
+      <c r="E450" s="102"/>
+      <c r="F450" s="102"/>
+      <c r="G450" s="102"/>
+      <c r="H450" s="93"/>
     </row>
     <row r="451" spans="2:8">
       <c r="B451" s="1"/>
       <c r="C451" s="64"/>
-      <c r="D451" s="105"/>
-      <c r="E451" s="104"/>
-      <c r="F451" s="104"/>
-      <c r="G451" s="104"/>
-      <c r="H451" s="95"/>
+      <c r="D451" s="103"/>
+      <c r="E451" s="102"/>
+      <c r="F451" s="102"/>
+      <c r="G451" s="102"/>
+      <c r="H451" s="93"/>
     </row>
     <row r="452" spans="2:8">
       <c r="B452" s="1"/>
       <c r="C452" s="64"/>
-      <c r="D452" s="105"/>
-      <c r="E452" s="104"/>
-      <c r="F452" s="104"/>
-      <c r="G452" s="104"/>
-      <c r="H452" s="95"/>
+      <c r="D452" s="103"/>
+      <c r="E452" s="102"/>
+      <c r="F452" s="102"/>
+      <c r="G452" s="102"/>
+      <c r="H452" s="93"/>
     </row>
     <row r="453" spans="2:8">
       <c r="B453" s="1"/>
       <c r="C453" s="64"/>
-      <c r="D453" s="105"/>
-      <c r="E453" s="104"/>
-      <c r="F453" s="104"/>
-      <c r="G453" s="104"/>
-      <c r="H453" s="95"/>
+      <c r="D453" s="103"/>
+      <c r="E453" s="102"/>
+      <c r="F453" s="102"/>
+      <c r="G453" s="102"/>
+      <c r="H453" s="93"/>
     </row>
     <row r="454" spans="2:8">
       <c r="B454" s="1"/>
       <c r="C454" s="64"/>
-      <c r="D454" s="105"/>
-      <c r="E454" s="104"/>
-      <c r="F454" s="104"/>
-      <c r="G454" s="104"/>
-      <c r="H454" s="95"/>
+      <c r="D454" s="103"/>
+      <c r="E454" s="102"/>
+      <c r="F454" s="102"/>
+      <c r="G454" s="102"/>
+      <c r="H454" s="93"/>
     </row>
     <row r="455" spans="2:8">
       <c r="B455" s="1"/>
       <c r="C455" s="64"/>
-      <c r="D455" s="105"/>
-      <c r="E455" s="104"/>
-      <c r="F455" s="104"/>
-      <c r="G455" s="104"/>
-      <c r="H455" s="95"/>
+      <c r="D455" s="103"/>
+      <c r="E455" s="102"/>
+      <c r="F455" s="102"/>
+      <c r="G455" s="102"/>
+      <c r="H455" s="93"/>
     </row>
     <row r="456" spans="2:8">
       <c r="B456" s="1"/>
       <c r="C456" s="64"/>
-      <c r="D456" s="105"/>
-      <c r="E456" s="104"/>
-      <c r="F456" s="104"/>
-      <c r="G456" s="104"/>
-      <c r="H456" s="95"/>
+      <c r="D456" s="103"/>
+      <c r="E456" s="102"/>
+      <c r="F456" s="102"/>
+      <c r="G456" s="102"/>
+      <c r="H456" s="93"/>
     </row>
     <row r="457" spans="2:8">
       <c r="B457" s="1"/>
       <c r="C457" s="64"/>
-      <c r="D457" s="105"/>
-      <c r="E457" s="104"/>
-      <c r="F457" s="104"/>
-      <c r="G457" s="104"/>
-      <c r="H457" s="95"/>
+      <c r="D457" s="103"/>
+      <c r="E457" s="102"/>
+      <c r="F457" s="102"/>
+      <c r="G457" s="102"/>
+      <c r="H457" s="93"/>
     </row>
     <row r="458" spans="2:8">
       <c r="B458" s="1"/>
       <c r="C458" s="64"/>
-      <c r="D458" s="105"/>
-      <c r="E458" s="104"/>
-      <c r="F458" s="104"/>
-      <c r="G458" s="104"/>
-      <c r="H458" s="95"/>
+      <c r="D458" s="103"/>
+      <c r="E458" s="102"/>
+      <c r="F458" s="102"/>
+      <c r="G458" s="102"/>
+      <c r="H458" s="93"/>
     </row>
     <row r="459" spans="2:8">
       <c r="B459" s="1"/>
       <c r="C459" s="64"/>
-      <c r="D459" s="105"/>
-      <c r="E459" s="104"/>
-      <c r="F459" s="104"/>
-      <c r="G459" s="104"/>
-      <c r="H459" s="95"/>
+      <c r="D459" s="103"/>
+      <c r="E459" s="102"/>
+      <c r="F459" s="102"/>
+      <c r="G459" s="102"/>
+      <c r="H459" s="93"/>
     </row>
     <row r="460" spans="2:8">
       <c r="B460" s="1"/>
       <c r="C460" s="64"/>
-      <c r="D460" s="105"/>
-      <c r="E460" s="104"/>
-      <c r="F460" s="104"/>
-      <c r="G460" s="104"/>
-      <c r="H460" s="95"/>
+      <c r="D460" s="103"/>
+      <c r="E460" s="102"/>
+      <c r="F460" s="102"/>
+      <c r="G460" s="102"/>
+      <c r="H460" s="93"/>
     </row>
     <row r="461" spans="2:8">
       <c r="B461" s="1"/>
       <c r="C461" s="64"/>
-      <c r="D461" s="105"/>
-      <c r="E461" s="104"/>
-      <c r="F461" s="104"/>
-      <c r="G461" s="104"/>
-      <c r="H461" s="95"/>
+      <c r="D461" s="103"/>
+      <c r="E461" s="102"/>
+      <c r="F461" s="102"/>
+      <c r="G461" s="102"/>
+      <c r="H461" s="93"/>
     </row>
     <row r="462" spans="2:8">
       <c r="B462" s="1"/>
       <c r="C462" s="64"/>
-      <c r="D462" s="105"/>
-      <c r="E462" s="104"/>
-      <c r="F462" s="104"/>
-      <c r="G462" s="104"/>
-      <c r="H462" s="95"/>
+      <c r="D462" s="103"/>
+      <c r="E462" s="102"/>
+      <c r="F462" s="102"/>
+      <c r="G462" s="102"/>
+      <c r="H462" s="93"/>
     </row>
     <row r="463" spans="2:8">
       <c r="B463" s="1"/>
       <c r="C463" s="64"/>
-      <c r="D463" s="105"/>
-      <c r="E463" s="104"/>
-      <c r="F463" s="104"/>
-      <c r="G463" s="104"/>
-      <c r="H463" s="95"/>
+      <c r="D463" s="103"/>
+      <c r="E463" s="102"/>
+      <c r="F463" s="102"/>
+      <c r="G463" s="102"/>
+      <c r="H463" s="93"/>
     </row>
     <row r="464" spans="2:8">
       <c r="B464" s="1"/>
       <c r="C464" s="64"/>
-      <c r="D464" s="105"/>
-      <c r="E464" s="104"/>
-      <c r="F464" s="104"/>
-      <c r="G464" s="104"/>
-      <c r="H464" s="95"/>
+      <c r="D464" s="103"/>
+      <c r="E464" s="102"/>
+      <c r="F464" s="102"/>
+      <c r="G464" s="102"/>
+      <c r="H464" s="93"/>
     </row>
     <row r="465" spans="2:8">
       <c r="B465" s="1"/>
       <c r="C465" s="64"/>
-      <c r="D465" s="105"/>
-      <c r="E465" s="104"/>
-      <c r="F465" s="104"/>
-      <c r="G465" s="104"/>
-      <c r="H465" s="95"/>
+      <c r="D465" s="103"/>
+      <c r="E465" s="102"/>
+      <c r="F465" s="102"/>
+      <c r="G465" s="102"/>
+      <c r="H465" s="93"/>
     </row>
     <row r="466" spans="2:8">
       <c r="B466" s="1"/>
       <c r="C466" s="64"/>
-      <c r="D466" s="105"/>
-      <c r="E466" s="104"/>
-      <c r="F466" s="104"/>
-      <c r="G466" s="104"/>
-      <c r="H466" s="95"/>
+      <c r="D466" s="103"/>
+      <c r="E466" s="102"/>
+      <c r="F466" s="102"/>
+      <c r="G466" s="102"/>
+      <c r="H466" s="93"/>
     </row>
     <row r="467" spans="2:8">
       <c r="B467" s="1"/>
       <c r="C467" s="64"/>
-      <c r="D467" s="105"/>
-      <c r="E467" s="104"/>
-      <c r="F467" s="104"/>
-      <c r="G467" s="104"/>
-      <c r="H467" s="95"/>
+      <c r="D467" s="103"/>
+      <c r="E467" s="102"/>
+      <c r="F467" s="102"/>
+      <c r="G467" s="102"/>
+      <c r="H467" s="93"/>
     </row>
     <row r="468" spans="2:8">
       <c r="B468" s="1"/>
       <c r="C468" s="64"/>
-      <c r="D468" s="105"/>
-      <c r="E468" s="104"/>
-      <c r="F468" s="104"/>
-      <c r="G468" s="104"/>
-      <c r="H468" s="95"/>
+      <c r="D468" s="103"/>
+      <c r="E468" s="102"/>
+      <c r="F468" s="102"/>
+      <c r="G468" s="102"/>
+      <c r="H468" s="93"/>
     </row>
     <row r="469" spans="2:8">
       <c r="B469" s="1"/>
       <c r="C469" s="64"/>
-      <c r="D469" s="105"/>
-      <c r="E469" s="104"/>
-      <c r="F469" s="104"/>
-      <c r="G469" s="104"/>
-      <c r="H469" s="95"/>
+      <c r="D469" s="103"/>
+      <c r="E469" s="102"/>
+      <c r="F469" s="102"/>
+      <c r="G469" s="102"/>
+      <c r="H469" s="93"/>
     </row>
     <row r="470" spans="2:8">
       <c r="B470" s="1"/>
       <c r="C470" s="64"/>
-      <c r="D470" s="105"/>
-      <c r="E470" s="104"/>
-      <c r="F470" s="104"/>
-      <c r="G470" s="104"/>
-      <c r="H470" s="95"/>
+      <c r="D470" s="103"/>
+      <c r="E470" s="102"/>
+      <c r="F470" s="102"/>
+      <c r="G470" s="102"/>
+      <c r="H470" s="93"/>
     </row>
     <row r="471" spans="2:8">
       <c r="B471" s="1"/>
       <c r="C471" s="64"/>
-      <c r="D471" s="105"/>
-      <c r="E471" s="104"/>
-      <c r="F471" s="104"/>
-      <c r="G471" s="104"/>
-      <c r="H471" s="95"/>
+      <c r="D471" s="103"/>
+      <c r="E471" s="102"/>
+      <c r="F471" s="102"/>
+      <c r="G471" s="102"/>
+      <c r="H471" s="93"/>
     </row>
     <row r="472" spans="2:8">
       <c r="B472" s="1"/>
       <c r="C472" s="64"/>
-      <c r="D472" s="105"/>
-      <c r="E472" s="104"/>
-      <c r="F472" s="104"/>
-      <c r="G472" s="104"/>
-      <c r="H472" s="95"/>
+      <c r="D472" s="103"/>
+      <c r="E472" s="102"/>
+      <c r="F472" s="102"/>
+      <c r="G472" s="102"/>
+      <c r="H472" s="93"/>
     </row>
     <row r="473" spans="2:8">
       <c r="B473" s="1"/>
       <c r="C473" s="64"/>
-      <c r="D473" s="105"/>
-      <c r="E473" s="104"/>
-      <c r="F473" s="104"/>
-      <c r="G473" s="104"/>
-      <c r="H473" s="95"/>
+      <c r="D473" s="103"/>
+      <c r="E473" s="102"/>
+      <c r="F473" s="102"/>
+      <c r="G473" s="102"/>
+      <c r="H473" s="93"/>
     </row>
     <row r="474" spans="2:8">
       <c r="B474" s="1"/>
       <c r="C474" s="64"/>
-      <c r="D474" s="105"/>
-      <c r="E474" s="104"/>
-      <c r="F474" s="104"/>
-      <c r="G474" s="104"/>
-      <c r="H474" s="95"/>
+      <c r="D474" s="103"/>
+      <c r="E474" s="102"/>
+      <c r="F474" s="102"/>
+      <c r="G474" s="102"/>
+      <c r="H474" s="93"/>
     </row>
     <row r="475" spans="2:8">
       <c r="B475" s="1"/>
       <c r="C475" s="64"/>
-      <c r="D475" s="105"/>
-      <c r="E475" s="104"/>
-      <c r="F475" s="104"/>
-      <c r="G475" s="104"/>
-      <c r="H475" s="95"/>
+      <c r="D475" s="103"/>
+      <c r="E475" s="102"/>
+      <c r="F475" s="102"/>
+      <c r="G475" s="102"/>
+      <c r="H475" s="93"/>
     </row>
     <row r="476" spans="2:8">
       <c r="B476" s="1"/>
       <c r="C476" s="64"/>
-      <c r="D476" s="105"/>
-      <c r="E476" s="104"/>
-      <c r="F476" s="104"/>
-      <c r="G476" s="104"/>
-      <c r="H476" s="95"/>
+      <c r="D476" s="103"/>
+      <c r="E476" s="102"/>
+      <c r="F476" s="102"/>
+      <c r="G476" s="102"/>
+      <c r="H476" s="93"/>
     </row>
     <row r="477" spans="2:8">
       <c r="B477" s="1"/>
       <c r="C477" s="64"/>
-      <c r="D477" s="105"/>
-      <c r="E477" s="104"/>
-      <c r="F477" s="104"/>
-      <c r="G477" s="104"/>
-      <c r="H477" s="95"/>
+      <c r="D477" s="103"/>
+      <c r="E477" s="102"/>
+      <c r="F477" s="102"/>
+      <c r="G477" s="102"/>
+      <c r="H477" s="93"/>
     </row>
     <row r="478" spans="2:8">
       <c r="B478" s="1"/>
       <c r="C478" s="64"/>
-      <c r="D478" s="105"/>
-      <c r="E478" s="104"/>
-      <c r="F478" s="104"/>
-      <c r="G478" s="104"/>
-      <c r="H478" s="95"/>
+      <c r="D478" s="103"/>
+      <c r="E478" s="102"/>
+      <c r="F478" s="102"/>
+      <c r="G478" s="102"/>
+      <c r="H478" s="93"/>
     </row>
     <row r="479" spans="2:8">
       <c r="B479" s="1"/>
       <c r="C479" s="64"/>
-      <c r="D479" s="105"/>
-      <c r="E479" s="104"/>
-      <c r="F479" s="104"/>
-      <c r="G479" s="104"/>
-      <c r="H479" s="95"/>
+      <c r="D479" s="103"/>
+      <c r="E479" s="102"/>
+      <c r="F479" s="102"/>
+      <c r="G479" s="102"/>
+      <c r="H479" s="93"/>
     </row>
     <row r="480" spans="2:8">
       <c r="B480" s="1"/>
       <c r="C480" s="64"/>
-      <c r="D480" s="105"/>
-      <c r="E480" s="104"/>
-      <c r="F480" s="104"/>
-      <c r="G480" s="104"/>
-      <c r="H480" s="95"/>
+      <c r="D480" s="103"/>
+      <c r="E480" s="102"/>
+      <c r="F480" s="102"/>
+      <c r="G480" s="102"/>
+      <c r="H480" s="93"/>
     </row>
     <row r="481" spans="2:8">
       <c r="B481" s="1"/>
       <c r="C481" s="64"/>
-      <c r="D481" s="105"/>
-      <c r="E481" s="104"/>
-      <c r="F481" s="104"/>
-      <c r="G481" s="104"/>
-      <c r="H481" s="95"/>
+      <c r="D481" s="103"/>
+      <c r="E481" s="102"/>
+      <c r="F481" s="102"/>
+      <c r="G481" s="102"/>
+      <c r="H481" s="93"/>
     </row>
     <row r="482" spans="2:8">
       <c r="B482" s="1"/>
       <c r="C482" s="64"/>
-      <c r="D482" s="105"/>
-      <c r="E482" s="104"/>
-      <c r="F482" s="104"/>
-      <c r="G482" s="104"/>
-      <c r="H482" s="95"/>
+      <c r="D482" s="103"/>
+      <c r="E482" s="102"/>
+      <c r="F482" s="102"/>
+      <c r="G482" s="102"/>
+      <c r="H482" s="93"/>
     </row>
     <row r="483" spans="2:8">
       <c r="B483" s="1"/>
       <c r="C483" s="64"/>
-      <c r="D483" s="105"/>
-      <c r="E483" s="104"/>
-      <c r="F483" s="104"/>
-      <c r="G483" s="104"/>
-      <c r="H483" s="95"/>
+      <c r="D483" s="103"/>
+      <c r="E483" s="102"/>
+      <c r="F483" s="102"/>
+      <c r="G483" s="102"/>
+      <c r="H483" s="93"/>
     </row>
     <row r="484" spans="2:8">
       <c r="B484" s="1"/>
       <c r="C484" s="64"/>
-      <c r="D484" s="105"/>
-      <c r="E484" s="104"/>
-      <c r="F484" s="104"/>
-      <c r="G484" s="104"/>
-      <c r="H484" s="95"/>
+      <c r="D484" s="103"/>
+      <c r="E484" s="102"/>
+      <c r="F484" s="102"/>
+      <c r="G484" s="102"/>
+      <c r="H484" s="93"/>
     </row>
     <row r="485" spans="2:8">
       <c r="B485" s="1"/>
       <c r="C485" s="64"/>
-      <c r="D485" s="105"/>
-      <c r="E485" s="104"/>
-      <c r="F485" s="104"/>
-      <c r="G485" s="104"/>
-      <c r="H485" s="95"/>
+      <c r="D485" s="103"/>
+      <c r="E485" s="102"/>
+      <c r="F485" s="102"/>
+      <c r="G485" s="102"/>
+      <c r="H485" s="93"/>
     </row>
     <row r="486" spans="2:8">
       <c r="B486" s="1"/>
       <c r="C486" s="64"/>
-      <c r="D486" s="105"/>
-      <c r="E486" s="104"/>
-      <c r="F486" s="104"/>
-      <c r="G486" s="104"/>
-      <c r="H486" s="95"/>
+      <c r="D486" s="103"/>
+      <c r="E486" s="102"/>
+      <c r="F486" s="102"/>
+      <c r="G486" s="102"/>
+      <c r="H486" s="93"/>
     </row>
     <row r="487" spans="2:8">
       <c r="B487" s="1"/>
       <c r="C487" s="64"/>
-      <c r="D487" s="105"/>
-      <c r="E487" s="104"/>
-      <c r="F487" s="104"/>
-      <c r="G487" s="104"/>
-      <c r="H487" s="95"/>
+      <c r="D487" s="103"/>
+      <c r="E487" s="102"/>
+      <c r="F487" s="102"/>
+      <c r="G487" s="102"/>
+      <c r="H487" s="93"/>
     </row>
     <row r="488" spans="2:8">
       <c r="B488" s="1"/>
       <c r="C488" s="64"/>
-      <c r="D488" s="105"/>
-      <c r="E488" s="104"/>
-      <c r="F488" s="104"/>
-      <c r="G488" s="104"/>
-      <c r="H488" s="95"/>
+      <c r="D488" s="103"/>
+      <c r="E488" s="102"/>
+      <c r="F488" s="102"/>
+      <c r="G488" s="102"/>
+      <c r="H488" s="93"/>
     </row>
     <row r="489" spans="2:8">
       <c r="B489" s="1"/>
       <c r="C489" s="64"/>
-      <c r="D489" s="105"/>
-      <c r="E489" s="104"/>
-      <c r="F489" s="104"/>
-      <c r="G489" s="104"/>
-      <c r="H489" s="95"/>
+      <c r="D489" s="103"/>
+      <c r="E489" s="102"/>
+      <c r="F489" s="102"/>
+      <c r="G489" s="102"/>
+      <c r="H489" s="93"/>
     </row>
     <row r="490" spans="2:8">
       <c r="B490" s="1"/>
       <c r="C490" s="64"/>
-      <c r="D490" s="105"/>
-      <c r="E490" s="104"/>
-      <c r="F490" s="104"/>
-      <c r="G490" s="104"/>
-      <c r="H490" s="95"/>
+      <c r="D490" s="103"/>
+      <c r="E490" s="102"/>
+      <c r="F490" s="102"/>
+      <c r="G490" s="102"/>
+      <c r="H490" s="93"/>
     </row>
     <row r="491" spans="2:8">
       <c r="B491" s="1"/>
       <c r="C491" s="64"/>
-      <c r="D491" s="105"/>
-      <c r="E491" s="104"/>
-      <c r="F491" s="104"/>
-      <c r="G491" s="104"/>
-      <c r="H491" s="95"/>
+      <c r="D491" s="103"/>
+      <c r="E491" s="102"/>
+      <c r="F491" s="102"/>
+      <c r="G491" s="102"/>
+      <c r="H491" s="93"/>
     </row>
     <row r="492" spans="2:8">
       <c r="B492" s="1"/>
       <c r="C492" s="64"/>
-      <c r="D492" s="105"/>
-      <c r="E492" s="104"/>
-      <c r="F492" s="104"/>
-      <c r="G492" s="104"/>
-      <c r="H492" s="95"/>
+      <c r="D492" s="103"/>
+      <c r="E492" s="102"/>
+      <c r="F492" s="102"/>
+      <c r="G492" s="102"/>
+      <c r="H492" s="93"/>
     </row>
     <row r="493" spans="2:8">
       <c r="B493" s="1"/>
       <c r="C493" s="64"/>
-      <c r="D493" s="105"/>
-      <c r="E493" s="104"/>
-      <c r="F493" s="104"/>
-      <c r="G493" s="104"/>
-      <c r="H493" s="95"/>
+      <c r="D493" s="103"/>
+      <c r="E493" s="102"/>
+      <c r="F493" s="102"/>
+      <c r="G493" s="102"/>
+      <c r="H493" s="93"/>
     </row>
     <row r="494" spans="2:8">
       <c r="B494" s="1"/>
       <c r="C494" s="64"/>
-      <c r="D494" s="105"/>
-      <c r="E494" s="104"/>
-      <c r="F494" s="104"/>
-      <c r="G494" s="104"/>
-      <c r="H494" s="95"/>
+      <c r="D494" s="103"/>
+      <c r="E494" s="102"/>
+      <c r="F494" s="102"/>
+      <c r="G494" s="102"/>
+      <c r="H494" s="93"/>
     </row>
     <row r="495" spans="2:8">
       <c r="B495" s="1"/>
       <c r="C495" s="64"/>
-      <c r="D495" s="105"/>
-      <c r="E495" s="104"/>
-      <c r="F495" s="104"/>
-      <c r="G495" s="104"/>
-      <c r="H495" s="95"/>
+      <c r="D495" s="103"/>
+      <c r="E495" s="102"/>
+      <c r="F495" s="102"/>
+      <c r="G495" s="102"/>
+      <c r="H495" s="93"/>
     </row>
     <row r="496" spans="2:8">
       <c r="B496" s="1"/>
       <c r="C496" s="64"/>
-      <c r="D496" s="105"/>
-      <c r="E496" s="104"/>
-      <c r="F496" s="104"/>
-      <c r="G496" s="104"/>
-      <c r="H496" s="95"/>
+      <c r="D496" s="103"/>
+      <c r="E496" s="102"/>
+      <c r="F496" s="102"/>
+      <c r="G496" s="102"/>
+      <c r="H496" s="93"/>
     </row>
     <row r="497" spans="2:8">
       <c r="B497" s="1"/>
       <c r="C497" s="64"/>
-      <c r="D497" s="105"/>
-      <c r="E497" s="104"/>
-      <c r="F497" s="104"/>
-      <c r="G497" s="104"/>
-      <c r="H497" s="95"/>
+      <c r="D497" s="103"/>
+      <c r="E497" s="102"/>
+      <c r="F497" s="102"/>
+      <c r="G497" s="102"/>
+      <c r="H497" s="93"/>
     </row>
     <row r="498" spans="2:8">
       <c r="B498" s="1"/>
